--- a/長文.xlsx
+++ b/長文.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,13 +32,21 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4EC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -53,8 +61,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,116 +439,132 @@
   </sheetPr>
   <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>タブ</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>カテゴリー</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>サブテーマ</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>形式</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>対象レベル(非表示)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>字数</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>英訳</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>キー表現</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ポイント</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>楽しさ・継続フック</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>備考(音声)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="210" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>L-K-001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>カイの物語</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>日本生活スタート</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>空港に着いた</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>（ナレーション）長（なが）い フライトの あと、カイは ついに 日本（にほん）に 着（つ）いた。空港（くうこう）は 人（ひと）で いっぱいだ。
 審査官（しんさかん）：パスポートを お願（ねが）いします。日本（にほん）には 何（なん）の ために 来（き）ましたか。
@@ -543,72 +576,72 @@
 （ナレーション）スタンプを もらって、カイは 大（おお）きく 息（いき）を ついた。「やっと 来た…。これから 新（あたら）しい 毎日（まいにち）が 始（はじ）まるんだ」。</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="2" t="n">
         <v>205</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>(Narration) After the long flight, Kai finally arrived in Japan. The airport is packed. / Officer: Passport, please. What did you come to Japan for? / Kai: Um, to study. I'll attend a Japanese language school. / Officer: How long will you stay? / Kai: About a year. / Officer: All right, go ahead. Good luck with your life in Japan. / Kai: Thank you! / (Narration) After getting the stamp, Kai let out a big breath. 'I'm finally here... A new daily life starts now.'</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>えっと／〜んです／がんばってください</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>入国の会話＋心情。会話表現「えっと/〜んです/〜んだ」。</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>新生活 第1話・ドキドキ。</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/審査官/カイ</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="225" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>L-K-002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>カイの物語</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>日本生活スタート</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>ゴミ出しでこまった</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>（ナレーション）引（ひ）っ越（こ）しの 次（つぎ）の 日（ひ）。カイは ゴミぶくろを 持（も）って、こまっていた。
 カイ：あれ？ ゴミは どこに 出（だ）せば いいんだろう…。
@@ -620,72 +653,72 @@
 （ナレーション）カイは ほっとした。「田中（たなか）さん、親切（しんせつ）だなあ。心強（こころづよ）いな」。</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="2" t="n">
         <v>231</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>(Narration) The day after moving. Kai stood there holding a trash bag, troubled. / Kai: Huh? Where am I supposed to put the trash...? / (Narration) Just then, Tanaka-san, the caring landlady of the area, passed by. / Kai: Um, excuse me. I don't know how to sort the trash... / Tanaka: Ah, burnable trash is Monday and Thursday. Put it at that corner by 8 a.m. / Kai: Oh, I see! Thank you, that helps. / Tanaka: Ask me anytime you're stuck. / (Narration) Kai felt relieved. 'Tanaka-san is so kind. That's reassuring.'</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>〜ばいいんだろう／そうなんですね／〜てね</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>近所のメンター田中さん デビュー。会話表現「あれ?/〜なんですね/〜てね」。</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>世話役 田中さん＝文化/本音への伏線。</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/カイ/田中さん</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="180" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>L-K-003</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>カイの物語</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>日本生活スタート</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>はじめての友だち（ミナ）</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>（ナレーション）学校（がっこう）が 始（はじ）まって 数日（すうじつ）。まだ クラスに なれない カイに、同（おな）じ クラスの ミナが 話（はな）しかけてきた。
 ミナ：あ、その ペン、いいね。どこで 買（か）ったの？
@@ -697,72 +730,72 @@
 （ナレーション）この 日（ひ）から、ミナは カイの いちばんの 友（とも）だちに なった。</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>(Narration) A few days after school started. To Kai, who still hadn't settled into class, Mina—a classmate—struck up a conversation. / Mina: Oh, that pen's nice. Where'd you buy it? / Kai: Huh, this? At the shop in front of the station. / Mina: Huh. Hey, if you'd like, want to have lunch together? / Kai: Really? I'd love to! / (Narration) That one phrase made him so happy. / Kai: (inner voice) I'm so glad I found the courage...! / (Narration) From this day, Mina became Kai's best friend.</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>どこで 買ったの？／いっしょに 〜ない？／よかったら</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>相棒ミナと仲よくなる回。会話表現「えっ/へえ/ねえ」。誘いの「〜ない?」。</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>相棒ミナ＝旅編への伏線。</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/カイ/ミナ</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="195" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>L-K-004</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>カイの物語</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>日本生活スタート</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>バイトを始める</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>（ナレーション）カイは、駅前（えきまえ）の カフェで バイトを 始（はじ）めた。初日（しょにち）、同（おな）じ シフトの 男（おとこ）の 子（こ）が 声（こえ）を かけてきた。
 ケンタ：あ、新（あたら）しい 人（ひと）？ おれ、ケンタ。よろしく！
@@ -773,72 +806,72 @@
 （ナレーション）ケンタの 明（あか）るさに、カイの きんちょうは すっと ほどけた。「日本人（にほんじん）の 友（とも）だち、第一号（だいいちごう）だ」。</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="2" t="n">
         <v>222</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>(Narration) Kai started a part-time job at a cafe by the station. On day one, a guy on the same shift spoke to him. / Kenta: Oh, the new person? I'm Kenta. Nice to meet you! / Kai: I'm Kai. Pleased to meet you. / Kenta: So formal, ha. You can be casual with me. If there's anything you don't get, just ask. / Kai: Thanks. Then... the register still scares me a bit. / Kenta: It's fine, it's fine. Everyone's like that at first. I've got your back! / (Narration) Kenta's brightness loosened Kai's nerves at once. 'My first Japanese friend.'</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>タメで いい／〜たら 聞いて／ついてる</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>日本人の友ケンタ デビュー。くだけた会話表現。</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>相棒その2＝フリートークへの伏線。</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/カイ/ケンタ</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="195" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>L-K-005</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>カイの物語</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>日本生活スタート</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>日本語学校の初日</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>（ナレーション）日本語（にほんご）学校（がっこう）の 初日（しょにち）。教室（きょうしつ）に 入（はい）ると、先生（せんせい）が にっこり わらった。
 さくら先生：みなさん、はじめまして。担任（たんにん）の さくらです。今日（きょう）から いっしょに がんばりましょう。
@@ -849,30 +882,30 @@
 （ナレーション）さくら先生（せんせい）の ていねいな 日本語（にほんご）と、ミナの 笑顔（えがお）。カイの 新（あたら）しい 毎日（まいにち）は、ここから 始（はじ）まった。</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="2" t="n">
         <v>194</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>(Narration) The first day at Japanese language school. When Kai entered the classroom, the teacher smiled warmly. / Sakura-sensei: Everyone, nice to meet you. I'm Sakura, your homeroom teacher. Let's do our best together starting today. / Kai: (inner voice) I'm glad the teacher seems kind... / Sakura-sensei: Now, let's greet the person next to you. / Mina: Nice to meet you, I'm Mina. / Kai: I'm Kai. Pleased to meet you. / (Narration) Sakura-sensei's polite Japanese and Mina's smile. Kai's new daily life began right here.</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>はじめまして／〜ましょう／よろしく お願いします</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>さくら先生 デビュー＋ミナと同級。ていねい語の手本。</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>学びの場のスタート。</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/さくら先生/カイ/ミナ</t>
         </is>
@@ -891,116 +924,132 @@
   </sheetPr>
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>タブ</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>カテゴリー</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>サブテーマ</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>形式</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>対象レベル(非表示)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>字数</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>英訳</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>キー表現</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ポイント</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>楽しさ・継続フック</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>備考(音声)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="210" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>L-J-001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>カイの物語</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>日本一人旅</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>京都へ行く</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>（ナレーション）連休（れんきゅう）、カイは はじめて 一人（ひとり）で 京都（きょうと）へ 来た。古（ふる）い お寺（てら）が 美（うつく）しい。
 カイ：わあ、きれい…。あの、すみません、写真（しゃしん）を 撮（と）って もらえますか。
@@ -1014,72 +1063,72 @@
 （ナレーション）わすれられない 一日（いちにち）に なった。</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="2" t="n">
         <v>181</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>(Narration) On the holidays, Kai came to Kyoto alone for the first time. The old temples are beautiful. / Kai: Wow, beautiful... Um, excuse me, could you take a photo? / Passerby: Sure. Okay, cheese! / Kai: Thank you! / (Narration) For lunch, he went into a small shop. / Clerk: Welcome. What'll you have? / Kai: Matcha ice cream, please. / Clerk: Coming up. How's Kyoto? / Kai: It's the best! I want to come again. / (Narration) It became an unforgettable day.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>撮って もらえますか／また 来たいなあ／〜はどう?</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>旅先の会話。会話表現「わあ/はいよ/〜なあ」。</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>旅情・写真・食。</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/カイ/通行人/店員</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="180" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>L-J-002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>カイの物語</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>日本一人旅</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>お祭りに行く</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>（ナレーション）夏（なつ）の 夜（よる）。カイは 友（とも）だちの ミナと お祭（まつ）りに 来た。
 ミナ：カイ、ゆかた 似合（にあ）ってる！
@@ -1092,30 +1141,30 @@
 （ナレーション）大（おお）きな 音（おと）と 光（ひかり）。カイの 胸（むね）は どきどきしていた。</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="2" t="n">
         <v>165</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>(Narration) A summer night. Kai came to a festival with his friend Mina. / Mina: Kai, the yukata looks good on you! / Kai: Really? Hehe, it's my first time wearing one. / Mina: Let's go to the stalls. I want takoyaki! / Kai: Nice. Oh, shaved ice too! / (Narration) As the two walked while eating, big fireworks rose into the sky. / Kai: Wow...! It's beautiful. / Mina: Yeah. I'm glad we came. / (Narration) The loud sound and light. Kai's heart was racing.</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>似合ってる／〜たんだ／来て よかったね</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>友だちとの祭り会話。会話表現「えへへ/〜よ/〜だね」。</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>夏祭りの高揚・友情。</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/カイ/ミナ</t>
         </is>
@@ -1134,116 +1183,132 @@
   </sheetPr>
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>タブ</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>カテゴリー</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>サブテーマ</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>形式</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>対象レベル(非表示)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>字数</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>英訳</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>キー表現</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ポイント</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>楽しさ・継続フック</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>備考(音声)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="225" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>L-L-001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>カイの物語</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>カイの日常</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>はじめての美容院</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>（ナレーション）カイは はじめて 一人（ひとり）で 美容院（びよういん）に 来た。日本語（にほんご）で 髪型（かみがた）を 言（い）うのは ドキドキする。
 美容師（びようし）：今日（きょう）は どうしますか。
@@ -1257,30 +1322,30 @@
 （ナレーション）少（すこ）し 短すぎたけれど、カイは なんだか うれしかった。</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>(Narration) Kai came to a hair salon alone for the first time. Saying his hairstyle in Japanese is nerve-racking. / Stylist: What would you like today? / Kai: Um, a bit shorter and lighter, please. / Stylist: What about your bangs? / Kai: Please leave the bangs as they are. / (Narration) The scissors snip away. When it was done and he looked in the mirror... it was much shorter than he expected! / Kai: (inner voice) Whoa, maybe too short... / Stylist: Yeah, it suits you. / Kai: Oh, thank you! / (Narration) A little too short, but Kai felt somehow happy.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>〜したいんです／どうしましょう／似合っています</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>美容院の会話＋心の声。会話表現「えっと/うわ/なんだか」。</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>カイの小さな挑戦。</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/カイ/美容師</t>
         </is>
@@ -1299,116 +1364,132 @@
   </sheetPr>
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>タブ</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>カテゴリー</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>サブテーマ</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>形式</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>対象レベル(非表示)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>字数</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>英訳</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>キー表現</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ポイント</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>楽しさ・継続フック</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>備考(音声)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="165" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>L-B-001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>カイの物語</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>カイの休憩室</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>好きな食べ物の話</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>カイ：みなさん、こんにちは、カイです。ちょっと 休憩（きゅうけい）の 時間（じかん）。今日（きょう）は ぼくの 好（す）きな 食（た）べ物（もの）の 話（はなし）。
 （ナレーション）実（じつ）は カイ、おにぎりが 大好物（だいこうぶつ）。
@@ -1417,30 +1498,30 @@
 カイ：みなさんの 好（す）きな 日本（にほん）の 食べ物は 何（なん）ですか？ また 教（おし）えてね。じゃあ、また！</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="2" t="n">
         <v>177</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Kai: Hi everyone, it's Kai. A little break time. Today, a talk about my favorite food. / (Narration) Actually, Kai loves onigiri. / Kai: Convenience-store onigiri are tasty, but making them yourself is fun too, you know. The other day I made some for a friend and they said 'Yum!'—it made me really happy. / (Narration) Kai laughed bashfully. / Kai: What's your favorite Japanese food? Let me know sometime. See you!</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>〜んだよね／うまっ／〜てね</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>カイの語りかけ＋ひとり言。くだけた会話表現「〜だよね/うまっ/さ」。</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>親近感・リスナーへの呼びかけ。</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>多声TTS:カイ/ナレーター</t>
         </is>
@@ -1459,536 +1540,552 @@
   </sheetPr>
   <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>タブ</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>カテゴリー</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>サブテーマ</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>形式</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>対象レベル(非表示)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>字数</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>英訳</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>キー表現</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ポイント</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>楽しさ・継続フック</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>備考(音声)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="120" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>L-R-001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>ラジオトーク</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>ニュース</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>桜が満開（国内）</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>ニュース</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>おはようございます。今朝（けさ）の ニュースです。昨日（きのう）、東京（とうきょう）の 公園（こうえん）で 桜（さくら）が 満開（まんかい）に なりました。週末（しゅうまつ）は たくさんの 家族（かぞく）連（づ）れで にぎわいそうです。天気（てんき）も よく、お花見（はなみ）に ぴったりの 一日（いちにち）に なるでしょう。一方（いっぽう）、来週（らいしゅう）からは 少（すこ）し 寒（さむ）く なるという 予報（よほう）も 出（で）ています。体調（たいちょう）に 気（き）を つけて お過（す）ごしください。では、今日（きょう）も よい 一日を。</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="2" t="n">
         <v>142</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Good morning. Here's this morning's news. Yesterday, the cherry blossoms reached full bloom in a Tokyo park. This weekend it should be crowded with families. The weather is good too—a perfect day for hanami. On the other hand, it's forecast to get a bit colder from next week. Please take care of your health. Have a good day.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>今朝の ニュース／満開／〜そうです／一方</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>ニュースの流れと話題転換「一方」。</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>季節感で“朝の習慣”に。</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>1話者・アナウンサー調</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="105" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>L-R-002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>ラジオトーク</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>ニュース</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>全国の天気（天気）</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>天気予報</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>全国（ぜんこく）の 天気（てんき）です。今日（きょう）は 西日本（にしにほん）で 晴（は）れますが、東日本（ひがしにほん）は 午後（ごご）から 雲（くも）が 多（おお）く なるでしょう。夜（よる）には 雨（あめ）が 降（ふ）る 所（ところ）も あります。傘（かさ）を 持（も）って 出（で）かけると 安心（あんしん）です。気温（きおん）は 各地（かくち）で 20度（ど）前後（ぜんご）、過（す）ごしやすい 一日（いちにち）に なりそうです。</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="2" t="n">
         <v>97</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Here's the nationwide weather. Today it's sunny in western Japan, but in eastern Japan clouds will increase from the afternoon. Some areas may see rain at night. It's safer to take an umbrella. Temperatures will be around 20 degrees—a comfortable day.</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>晴れます／雲が 多く なる／傘を 持って</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>全国天気の聞き取り（地域差）。</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>「傘いる?」毎朝役立つ。</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>1話者・予報士調</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="105" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>L-R-003</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>ラジオトーク</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>ニュース</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>海外のニュース（国際）</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>ニュース</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>こんにちは、国際（こくさい）ニュースです。アメリカで、新（あたら）しい 技術（ぎじゅつ）の 会議（かいぎ）が 開（ひら）かれました。世界中（せかいじゅう）から たくさんの 研究者（けんきゅうしゃ）が 集（あつ）まりました。日本（にほん）からも 多（おお）くの 企業（きぎょう）が 参加（さんか）し、注目（ちゅうもく）を 集（あつ）めています。来年（らいねん）は アジアでも 同（おな）じ 会議が 開かれる 予定（よてい）です。</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Hello, international news. In the U.S., a conference on new technology was held. Many researchers gathered from around the world. Many companies from Japan also took part and are drawing attention. Next year, the same conference is scheduled to be held in Asia too.</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>国際ニュース／〜が 開かれました／注目を 集めています</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>国際ニュースの定型表現。</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>世界とつながる話題。</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>1話者・アナウンサー調</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>L-R-004</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>ラジオトーク</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>ニュース</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>サッカーの試合（スポーツ）</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>ニュース</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>スポーツの ニュースです。昨日（きのう）、サッカーの 試合（しあい）が ありました。日本（にほん）チームは 2対（たい）1で 勝（か）ちました。最後（さいご）の ゴールは、とても すばらしかったです。スタジアムの ファンは 大（おお）きな 声（こえ）で 応援（おうえん）しました。次（つぎ）の 試合は 来週（らいしゅう）の 土曜日（どようび）です。楽（たの）しみですね。</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Sports news. Yesterday there was a soccer match. The Japan team won 2 to 1. The final goal was wonderful. Fans in the stadium cheered loudly. The next match is next Saturday. Something to look forward to.</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>2対1で 勝ちました／応援しました／楽しみですね</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>スポーツ結果(点数/勝敗)の聞き取り。</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>勝利の興奮。</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>1話者・アナウンサー調</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="120" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>L-R-005</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>ラジオトーク</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>お便り相談室</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>勉強が続かない</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>トーク</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>こんばんは、パーソナリティの ユウキです。今日（きょう）も 一日（いちにち）お疲（つか）れさまでした。さて、リスナーの みなさんから お便（たよ）りを いただきました。「最近（さいきん）、日本語（にほんご）の 勉強（べんきょう）が 続（つづ）かなくて 困（こま）っています」。わかります〜。でも、大丈夫（だいじょうぶ）。毎日（まいにち）5分（ふん）でも いいんです。好（す）きな ドラマや 歌（うた）で 楽（たの）しく 続（つづ）けましょう。それでは、今夜（こんや）の 一曲（いっきょく）です。</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="2" t="n">
         <v>142</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Good evening, this is your host, Yuki. Thanks for your hard work today. Now, a message from a listener: 'Lately I can't keep up my Japanese study and I'm troubled.' I understand! But it's okay. Even 5 minutes a day is fine. Keep it up enjoyably with dramas or songs you like. Now, tonight's song.</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>お疲れさまでした／お便り／〜ましょう</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>相談＋励ましの語り口。</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>共感＝続けたくなる。</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>1話者・パーソナリティ調</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>L-R-006</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>ラジオトーク</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>お便り相談室</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>漢字が覚えられない</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>トーク</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>今日（きょう）の お便（たよ）りです。「漢字（かんじ）が なかなか 覚（おぼ）えられません」。わかります。漢字は 数（かず）が 多（おお）いですからね。おすすめは、毎日（まいにち）少（すこ）しずつ、生活（せいかつ）の 中（なか）で 見（み）た 漢字を 覚（おぼ）えることです。看板（かんばん）や メニューも いい 教材（きょうざい）ですよ。あせらず 続（つづ）けましょう。</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="2" t="n">
         <v>103</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>Today's listener message: 'I just can't memorize kanji.' I understand—there are so many. My tip: learn a little every day, from kanji you see in daily life. Signs and menus make good study material too. Don't rush—keep at it.</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>なかなか 〜られません／少しずつ／あせらず 続けましょう</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>相談＋アドバイスの語り。</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>共感＆励ましで続く。</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>1話者・パーソナリティ調</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>L-R-007</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>ラジオトーク</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>ゲストインタビュー</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>ゲストのカイさん</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>対話</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>司会（しかい）：今日（きょう）の ゲストは、日本（にほん）で 勉強（べんきょう）している カイさんです。日本に 来て どのくらいですか。
 カイ：半年（はんとし）くらいです。
@@ -1999,72 +2096,72 @@
 司会：いいですね！ がんばってください。</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="2" t="n">
         <v>142</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>Host: Today's guest is Kai, who is studying in Japan. How long have you been in Japan? / Kai: About half a year. / Host: What's your favorite thing in Japan? / Kai: Hot springs. They feel so good. / Host: What do you want to do from now on? / Kai: I want to get better at Japanese. / Host: Nice! Keep it up.</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>どのくらいですか／一番 好きな ものは？／がんばってください</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>インタビューの定番質問。</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>多様な人の声・人間味。</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>多声TTS:司会/ゲスト</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="9" ht="135" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>L-R-008</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>ラジオトーク</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>2人のフリートーク</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>週末どうだった？</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>対話</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>ケンタ：週末（しゅうまつ）、どうだった？
 カイ：友（とも）だちの ミナと 海（うみ）に 行（い）ったよ。すごく きれいだった！
@@ -2074,30 +2171,30 @@
 カイ：へえ、いいね！</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="2" t="n">
         <v>122</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>Kenta: How was your weekend? / Kai: I went to the beach with my friend Mina. It was so beautiful! / Kenta: Nice. I watched dramas at home all day. / Kai: That's good too. What drama? / Kenta: A Japanese romance drama. Actually it's good Japanese study too. / Kai: Oh, nice!</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>どうだった?／〜に 行ったよ／勉強にも なる</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>相棒ケンタとカイのゆるい雑談(再登場)。</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>くだけた会話＝多聴に最適。</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>多声TTS:ケンタ/カイ</t>
         </is>
@@ -2116,111 +2213,128 @@
   </sheetPr>
   <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>タブ</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>カテゴリー</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>サブテーマ</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>形式</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>対象レベル(非表示)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>字数</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>英訳</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>キー表現</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ポイント</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>楽しさ・継続フック</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>備考(音声)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="150" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>L-M-001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>ミステリー</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>消えた駅弁の謎 第1話：駅で事件発生</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>（ナレーション）東京駅（とうきょうえき）の 有名（ゆうめい）な 駅弁屋（えきべんや）で 事件（じけん）が 起（お）きた。
 店長（てんちょう）：たいへんだ！ 一番（いちばん）人気（にんき）の「うみの幸（さち）弁当（べんとう）」が、10個（こ）も 消（き）えてる！
@@ -2230,67 +2344,68 @@
 （ナレーション）田中（たなか）さんは 考（かんが）えた。これは ただの どろぼうでは ないかもしれない。</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="2" t="n">
         <v>143</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>(Narration) An incident occurred at a famous ekiben shop in Tokyo Station. / Manager: This is terrible! Ten of our most popular 'Sea Bounty Bento' have vanished! / Tanaka (staff): The door was locked, right? / Manager: Yes, firmly until morning... / Tanaka: Strange. The door was locked, so how...? / (Narration) Tanaka thought. This might not be an ordinary thief.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>たいへんだ／〜んですよね／どうやって…?</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>事件の発端を会話で（密室の謎）。</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>続きが気になる第1話。</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/店長/田中</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="165" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>L-M-002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>ミステリー</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>消えた駅弁の謎 第2話：証言を聞く</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>対話</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>田中（たなか）：すみません、今朝（けさ）、何（なに）か 見（み）ませんでしたか。
 掃除（そうじ）の人：5時（じ）ごろ、白（しろ）い 服（ふく）の 人（ひと）を 見（み）ましたよ。
@@ -2301,67 +2416,68 @@
 田中：（首（くび）を かしげて）うーん、おかしいなあ…。</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="2" t="n">
         <v>144</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Tanaka: Excuse me, did you see anything this morning? / Cleaner: Around 5, I saw someone in white clothes. / Tanaka: White clothes... Thank you. / Coffee-shop worker: Come to think of it, there was a strange sound. A flapping sound. / Tanaka: Flapping? / (Narration) But the security camera showed no one. / Tanaka: (tilting his head) Hmm, that's strange...</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>見ませんでしたか／そういえば／うーん</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>証言の会話と矛盾。会話表現「そういえば/うーん」。</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>謎が深まる。</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>多声TTS:田中/証人たち/ナレーター</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="135" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>L-M-003</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>ミステリー</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>消えた駅弁の謎 第3話：容疑者登場</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>対話</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>（ナレーション）次（つぎ）の 日（ひ）、田中（たなか）さんは 白（しろ）い 服（ふく）の 男（おとこ）を 見（み）つけた。駅（えき）の 清掃員（せいそういん）だ。
 田中：あの 朝（あさ）、何（なに）を していましたか。
@@ -2371,67 +2487,68 @@
 清掃員：えっ、いや、これは…！</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="2" t="n">
         <v>124</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>(Narration) The next day, Tanaka found the man in white—a station cleaner. / Tanaka: What were you doing that morning? / Cleaner: I was just collecting trash. / (Narration) Just then, a bento wrapper fluttered out of the man's bag. / Tanaka: (eyes flashing) ...What's this? / Cleaner: Huh, no, this is...!</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>〜だけですよ／これは？／えっ、いや</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>容疑者への会話と証拠。会話表現「〜だけですよ/えっ、いや」。</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>犯人か?の緊張。</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/田中/清掃員</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="150" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>L-M-004</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>ミステリー</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>消えた駅弁の謎 第4話：真犯人は？</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>清掃員：それは、私（わたし）が 拾（ひろ）った ゴミです。本当（ほんとう）です！
 （ナレーション）田中（たなか）さんは 防犯（ぼうはん）カメラを もう一度（いちど）見（み）た。すると、屋根（やね）の すきまから…
@@ -2441,67 +2558,68 @@
 田中：はは、事件（じけん）は 無事（ぶじ）解決（かいけつ）、ですね。</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Cleaner: That's trash I picked up. It's true! / (Narration) Tanaka watched the security camera again. Then, through a gap in the roof... / Tanaka: Ah! Look! A big crow is carrying the bento! / Manager: Whaaat! The culprit was a crow?! / (Narration) Everyone burst out laughing. The mystery of the lock was a small window in the roof. / Tanaka: Haha, case closed.</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>見て ください／〜だったの!?／無事 解決</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>真相を会話で。会話表現「あっ/えーっ/はは」。</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>犯人はカラス＝意外な落ち。</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/田中/清掃員/店長</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="165" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>L-M-005</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>ミステリー</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>消えた最終電車</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>夜（よる）11時（じ）50分（ぷん）、駅員（えきいん）の 木村（きむら）さんは おかしな ことに 気（き）づいた。
 木村：あれ？ さっきまで ホームに いた 女（おんな）の 人（ひと）、どこへ 行（い）ったんだ…。
@@ -2511,30 +2629,30 @@
 （つづく）</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="2" t="n">
         <v>154</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>11:50 p.m. Station attendant Kimura noticed something strange. Kimura: Huh? The woman who was on the platform just now—where did she go...? The last train hasn't come yet. She didn't pass the gate. And yet, no one is on the platform. Kimura: Only a bag is left on the bench... The next morning, an old ticket was found inside the bag. The date was—30 years ago. (To be continued)</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>〜に 気づいた／なのに／〜だった</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>続きが気になる導入。</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>30年前の切符の謎。</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>多声TTS:ナレーション/駅員</t>
         </is>
@@ -2553,111 +2671,128 @@
   </sheetPr>
   <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>タブ</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>カテゴリー</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>サブテーマ</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>形式</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>対象レベル(非表示)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>字数</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>英訳</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>キー表現</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ポイント</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>楽しさ・継続フック</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>備考(音声)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="300" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>L-D-001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>カップラーメンの誕生</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>（ナレーション）戦後（せんご）の 日本（にほん）。町（まち）には 食（た）べ物（もの）を 求（もと）める 人々（ひとびと）の 長（なが）い 行列（ぎょうれつ）が あった。それを 見（み）て、一人（ひとり）の 男（おとこ）、安藤（あんどう）さんは 強（つよ）く 思（おも）った。
 安藤：お湯（ゆ）を 入（い）れるだけで すぐ 食（た）べられる めんが あれば、みんなが 助（たす）かるはずだ。
@@ -2669,67 +2804,68 @@
 （ナレーション）こうして、世界（せかい）で はじめての インスタントラーメンが 生（う）まれた。今（いま）では 世界中（せかいじゅう）で 一年（いちねん）に 1000億（おく）食（しょく）。小（ちい）さな ひらめきが、本当（ほんとう）に 世界（せかい）を 変（か）えたのだ。</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="2" t="n">
         <v>293</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>(Narration) Postwar Japan. In the towns were long lines of people seeking food. Seeing that, one man, Mr. Ando, thought strongly: / Ando: If there were noodles you could eat right away just by adding hot water, it would help everyone. / (Narration) From that day, days of shutting himself in a small shed began. / Wife: Dear, an all-nighter again? You'll ruin your health. / Ando: Just a little more. I can't give up. / (Narration) The failures were countless—the noodles spoiled quickly. One day, watching his wife make tempura— / Ando: That's it! If you fry them in oil, the water evaporates and the noodles dry! / (Narration) Thus the world's first instant ramen was born. Today, 100 billion servings a year worldwide. A small spark truly changed the world.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>〜はずだ／あきらめるわけには いかない／そうか！</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>困難→不屈→ひらめき→成功。会話で臨場感。</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>身近なカップ麺の感動秘話・濃い内容。</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/安藤/妻</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="315" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>L-D-002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>はやぶさの帰還</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>（ナレーション）小（ちい）さな 宇宙船（うちゅうせん）「はやぶさ」は、地球（ちきゅう）から 3億（おく）キロ 離（はな）れた 小惑星（しょうわくせい）を 目指（めざ）した。星（ほし）の 石（いし）を 取（と）って 帰（かえ）る——だれも 成功（せいこう）した ことの ない 挑戦（ちょうせん）だった。
 （ナレーション）しかし、旅（たび）は 苦難（くなん）の 連続（れんぞく）。エンジンは こわれ、ついに 通信（つうしん）も 切（き）れた。
@@ -2740,225 +2876,228 @@
 （ナレーション）7年（ねん）、60億（おく）キロの 旅（たび）の すえ、はやぶさは 帰（かえ）ってきた。最後（さいご）は 自分（じぶん）の 体（からだ）を 燃（も）やしながら、石（いし）の カプセルだけを そっと 送（おく）り届（とど）けた。その 光（ひかり）に、世界中（せかいじゅう）が 涙（なみだ）した。</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="2" t="n">
         <v>283</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>(Narration) The small spacecraft 'Hayabusa' aimed for an asteroid 300 million km from Earth. To collect rocks from a star and return—a challenge no one had ever succeeded at. / (Narration) But the journey was one hardship after another. The engines broke, and finally communication was lost. / Researcher A: There's... no signal. Hayabusa is gone. / Researcher B: Don't give up. It's surely alive somewhere. Let's keep calling. / (Narration) The control room kept sending signals day after day. Then, seven weeks later— / Researcher A: ...A reply came! Hayabusa is alive! / (Narration) After seven years and 6 billion km, Hayabusa came home. At the end, burning up its own body, it gently delivered only the capsule of rocks. The whole world wept at that light.</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>あきらめるな／返事が 来ました／〜のすえ</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>苦難→不屈→奇跡の帰還。管制室の会話で手に汗。</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>実話の大感動・濃い内容。</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/研究者A/研究者B</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="165" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>L-D-003</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>黒部ダムをつくった男たち</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>昭和（しょうわ）の 時代（じだい）、富山（とやま）の 山（やま）おくに、巨大（きょだい）な ダムを つくる 計画（けいかく）が あった。黒部（くろべ）ダムである。けわしい 山（やま）、冷（つめ）たい 水（みず）、そして 固（かた）い 岩（いわ）。工事（こうじ）は 想像（そうぞう）を こえる 困難（こんなん）の 連続（れんぞく）だった。とくに トンネルを ほる 作業（さぎょう）では、地下水（ちかすい）が ふき出（だ）し、何度（なんど）も 工事（こうじ）が 止（と）まった。それでも 作業員（さぎょういん）たちは あきらめなかった。7年（ねん）の 月日（つきひ）と、のべ 1000万人（まんにん）の 力（ちから）で、ダムは ついに 完成（かんせい）した。今（いま）も 黒部（くろべ）の 水（みず）は、人々（ひとびと）の 暮（く）らしを ささえている。</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>In the Showa era, there was a plan to build a huge dam deep in the mountains of Toyama: the Kurobe Dam. Steep mountains, cold water, and hard rock—construction was a series of difficulties beyond imagination. Especially when digging the tunnel, groundwater gushed out and work stopped many times. Still, the workers never gave up. With seven years and the effort of ten million people in total, the dam was finally completed. Even now, Kurobe's water supports people's lives.</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>〜を こえる／何度も／それでも</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>困難に挑む実話。</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>不可能を可能にした執念。</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>1話者・朗読</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="165" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>L-D-004</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>新幹線――夢の超特急</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>1964年（ねん）、東京（とうきょう）と 大阪（おおさか）を むすぶ「新幹線（しんかんせん）」が 走（はし）り はじめた。当時（とうじ）、時速（じそく）200キロを こえる 電車（でんしゃ）は、世界（せかい）の どこにも なかった。『そんな スピードは あぶない』と 多（おお）くの 人（ひと）が 反対（はんたい）した。技術者（ぎじゅつしゃ）たちは、空気（くうき）の 力（ちから）や 線路（せんろ）の カーブを 何度（なんど）も 計算（けいさん）し、安全（あんぜん）の ために 知恵（ちえ）を しぼった。開業（かいぎょう）の 日（ひ）、新幹線（しんかんせん）は 一度（いちど）の 事故（じこ）も なく 走（はし）りきった。夢（ゆめ）の 超特急（ちょうとっきゅう）は、日本（にほん）の 誇（ほこ）りに なった。</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="2" t="n">
         <v>163</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>In 1964, the Shinkansen connecting Tokyo and Osaka began running. At the time, no train anywhere in the world exceeded 200 km/h. 'Such speed is dangerous,' many people opposed. Engineers calculated air resistance and track curves again and again, racking their brains for safety. On opening day, the Shinkansen ran the whole way without a single accident. The dream super-express became a source of pride for Japan.</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>〜を こえる／〜の ために／〜きった</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>世界初の高速鉄道。</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>反対を覆した技術の結晶。</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>1話者・朗読</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="165" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>L-D-005</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>青い光をもとめて</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>赤（あか）と 緑（みどり）の 光（ひかり）は できても、「青（あお）い 光（ひかり）」を 出（だ）す LEDだけは、だれにも 作（つく）れなかった。『20世紀（せいき）中（じゅう）には 無理（むり）だ』とも 言（い）われた。日本（にほん）の ある 研究者（けんきゅうしゃ）は、小（ちい）さな 会社（かいしゃ）で、たった 一人（ひとり）、何千回（なんぜんかい）も 実験（じっけん）を くりかえした。失敗（しっぱい）、また 失敗（しっぱい）。それでも 手（て）を 止（と）めなかった。ついに 青（あお）い 光（ひかり）が ともった 瞬間（しゅんかん）、世界（せかい）の 明（あ）かりは 変（か）わった。白（しろ）い LEDが 生（う）まれ、街（まち）も 家（いえ）も 明（あか）るく なった。その 功績（こうせき）は、のちに ノーベル賞（しょう）に かがやいた。</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="2" t="n">
         <v>182</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Red and green light were possible, but a blue-light LED was something no one could make. 'It's impossible within the 20th century,' they said. One Japanese researcher, alone at a small company, repeated experiments thousands of times. Failure, and failure again. Still he never stopped. The moment blue light finally lit up, the world's lighting changed. White LEDs were born, brightening streets and homes. The achievement later shone with a Nobel Prize.</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>〜だけは／くりかえした／〜瞬間</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>青色LEDの挑戦。</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>孤独な執念がノーベル賞に。</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>1話者・朗読</t>
         </is>
@@ -2977,111 +3116,128 @@
   </sheetPr>
   <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>タブ</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>カテゴリー</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>サブテーマ</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>形式</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>対象レベル(非表示)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>字数</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>英訳</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>キー表現</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ポイント</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>楽しさ・継続フック</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>備考(音声)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="210" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>L-T-001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>昔話</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>桃太郎</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>（ナレーション）むかしむかし、ある ところに、おじいさんと おばあさんが いました。ある日（ひ）、川（かわ）から 大（おお）きな 桃（もも）が どんぶらこ、どんぶらこ、と 流（なが）れて きました。
 おばあさん：おや、なんて 大（おお）きな 桃（もも）だろう！ 家（いえ）に 持（も）って 帰（かえ）りましょう。
@@ -3091,290 +3247,294 @@
 桃太郎：おじいさん、おばあさん。鬼（おに）を 退治（たいじ）しに 行（い）ってきます！</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="2" t="n">
         <v>204</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>(Narration) Long ago, an old man and an old woman lived in a certain place. One day, a big peach came floating down the river, donburako, donburako. / Old woman: Oh my, what a big peach! Let's take it home. / (Narration) When they tried to cut the peach at home... crack! A healthy boy was born from inside. / Old man: Oh, a lively boy! Let's name him Momotaro. / (Narration) When Momotaro grew up, one day he said: / Momotaro: Grandpa, Grandma. I'm going off to defeat the ogres!</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>なんて 〜だろう／〜ましょう／〜てきます</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>昔話の会話＋擬音(どんぶらこ/パカッ)。</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>有名な昔話を会話で。</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/おばあさん/おじいさん/桃太郎</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="135" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>L-T-002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>昔話</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>浦島太郎</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>むかしむかし、浦島太郎（うらしまたろう）という 若者（わかもの）が いました。ある 日（ひ）、いじめられている 亀（かめ）を 助（たす）けて あげました。お礼（れい）に、亀（かめ）は 太郎（たろう）を 海（うみ）の 中（なか）の「竜宮城（りゅうぐうじょう）」へ つれて 行（い）きました。そこは 美（うつく）しい おとめ「乙姫（おとひめ）」が すむ、ゆめのような 場所（ばしょ）でした。楽（たの）しい 日々（ひび）を すごし、太郎（たろう）が 家（いえ）に 帰（かえ）ると——村（むら）は すっかり 変（か）わって いました。なんと、何百年（なんびゃくねん）もの 時（とき）が すぎて いたのです。</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="2" t="n">
         <v>157</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Long ago, there was a young man named Urashima Taro. One day, he rescued a turtle that was being bullied. In return, the turtle took Taro to the 'Dragon Palace' beneath the sea. It was a dreamlike place where the beautiful maiden 'Otohime' lived. After spending happy days there, Taro returned home—but the village had completely changed. Astonishingly, hundreds of years had passed.</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>〜て あげる／〜のような／なんと</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>助けた恩と時の流れ。</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>玉手箱の結末は…?</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>1話者・朗読</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="150" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>L-T-003</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>昔話</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>かぐや姫</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>むかし、竹（たけ）を とって 暮（く）らす おじいさんが いました。ある 日（ひ）、光（ひか）る 竹（たけ）の 中（なか）から、小（ちい）さな 女（おんな）の 子（こ）が 生（う）まれました。「かぐや姫（ひめ）」と 名（な）づけられた その 子（こ）は、月（つき）のように 美（うつく）しく 育（そだ）ちました。やがて、たくさんの 男（おとこ）たちが 結婚（けっこん）を もうし込（こ）みましたが、姫（ひめ）は 首（くび）を たてに ふりません。実（じつ）は、かぐや姫（ひめ）は 月（つき）の 世界（せかい）から 来（き）た 人（ひと）でした。満月（まんげつ）の 夜（よる）、姫（ひめ）は 月（つき）へ 帰（かえ）って いきました。</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="2" t="n">
         <v>159</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Long ago, there was an old man who made his living cutting bamboo. One day, a tiny girl was born from a glowing stalk of bamboo. Named 'Kaguya-hime,' she grew as beautiful as the moon. In time, many men proposed marriage, but the princess would not nod yes. In fact, Kaguya-hime was a person from the world of the moon. On the night of the full moon, she returned to the moon.</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>〜の中から／〜のように／やがて</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>竹から生まれた姫。</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>日本最古の物語の一つ。</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>1話者・朗読</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="150" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>L-T-004</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>昔話</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>鶴の恩返し</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>さむい 冬（ふゆ）の 日（ひ）、ある 男（おとこ）が、わなに かかった 鶴（つる）を 助（たす）けました。その 夜（よる）、美（うつく）しい 女（おんな）の 人（ひと）が 家（いえ）を たずねて きて、男（おとこ）の 妻（つま）に なりました。妻（つま）は『けっして 見（み）ないで ください』と 言（い）って、部屋（へや）で 布（ぬの）を おりました。その 布（ぬの）は とても 高（たか）く 売（う）れました。ある 日（ひ）、男（おとこ）が こっそり のぞくと——そこには、自分（じぶん）の 羽根（はね）を ぬいて 布（ぬの）を おる 鶴（つる）の 姿（すがた）が ありました。正体（しょうたい）を 知（し）られた 妻（つま）は、空（そら）へ 飛（と）んで 行（い）きました。</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="2" t="n">
         <v>169</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>On a cold winter day, a man rescued a crane caught in a trap. That night, a beautiful woman visited his house and became his wife. She said, 'Please never look,' and wove cloth in a room. The cloth sold for a very high price. One day, when the man secretly peeked—there was the crane, plucking its own feathers to weave the cloth. Once her true form was known, the wife flew away into the sky.</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>〜を 助ける／けっして〜ないで／〜と …が ある</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>約束と恩返し。</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>見てはいけない約束の結末。</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>1話者・朗読</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="135" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>L-T-005</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>昔話</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>笠地蔵</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>年（とし）の くれ、まずしい おじいさんが、町（まち）へ 笠（かさ）を 売（う）りに 行（い）きました。でも、一（ひと）つも 売（う）れません。帰（かえ）り道（みち）、雪（ゆき）の 中（なか）に 立（た）つ 六（む）つの お地蔵（じぞう）さまを 見（み）つけました。『さむそうだ』と、おじいさんは 売（う）り物（もの）の 笠（かさ）を お地蔵（じぞう）さまに かぶせて あげました。一（ひと）つ 足（た）りないので、自分（じぶん）の 手（て）ぬぐいを かけました。その 夜（よる）、ふしぎな ことが おきました。朝（あさ）、戸（と）を 開（あ）けると、米（こめ）や もちが 山（やま）のように 置（お）いて あったのです。</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="2" t="n">
         <v>173</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>At year's end, a poor old man went to town to sell straw hats. But not one sold. On the way home, he found six Jizo statues standing in the snow. 'They look cold,' he said, and placed the hats he had been selling on the statues. One was short, so he used his own hand towel. That night, something mysterious happened. In the morning, when he opened the door, rice and mochi were piled up like a mountain.</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>〜そうだ／〜て あげる／〜のように</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>親切が返ってくる話。</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>心温まる年越しの奇跡。</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>1話者・朗読</t>
         </is>

--- a/長文.xlsx
+++ b/長文.xlsx
@@ -61,7 +61,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -71,6 +71,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -529,12 +532,12 @@
       </c>
     </row>
     <row r="2" ht="210" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>L-K-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -554,12 +557,12 @@
           <t>空港に着いた</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
@@ -576,7 +579,7 @@
 （ナレーション）スタンプを もらって、カイは 大（おお）きく 息（いき）を ついた。「やっと 来た…。これから 新（あたら）しい 毎日（まいにち）が 始（はじ）まるんだ」。</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="4" t="n">
         <v>205</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -606,12 +609,12 @@
       </c>
     </row>
     <row r="3" ht="225" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>L-K-002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -631,12 +634,12 @@
           <t>ゴミ出しでこまった</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -653,7 +656,7 @@
 （ナレーション）カイは ほっとした。「田中（たなか）さん、親切（しんせつ）だなあ。心強（こころづよ）いな」。</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="4" t="n">
         <v>231</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -683,12 +686,12 @@
       </c>
     </row>
     <row r="4" ht="180" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>L-K-003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -708,12 +711,12 @@
           <t>はじめての友だち（ミナ）</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -730,7 +733,7 @@
 （ナレーション）この 日（ひ）から、ミナは カイの いちばんの 友（とも）だちに なった。</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="4" t="n">
         <v>180</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -760,12 +763,12 @@
       </c>
     </row>
     <row r="5" ht="195" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>L-K-004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -785,12 +788,12 @@
           <t>バイトを始める</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -806,7 +809,7 @@
 （ナレーション）ケンタの 明（あか）るさに、カイの きんちょうは すっと ほどけた。「日本人（にほんじん）の 友（とも）だち、第一号（だいいちごう）だ」。</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="4" t="n">
         <v>222</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -836,12 +839,12 @@
       </c>
     </row>
     <row r="6" ht="195" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>L-K-005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -861,12 +864,12 @@
           <t>日本語学校の初日</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -882,7 +885,7 @@
 （ナレーション）さくら先生（せんせい）の ていねいな 日本語（にほんご）と、ミナの 笑顔（えがお）。カイの 新（あたら）しい 毎日（まいにち）は、ここから 始（はじ）まった。</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="4" t="n">
         <v>194</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -1014,12 +1017,12 @@
       </c>
     </row>
     <row r="2" ht="210" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>L-J-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1039,12 +1042,12 @@
           <t>京都へ行く</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -1063,7 +1066,7 @@
 （ナレーション）わすれられない 一日（いちにち）に なった。</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="4" t="n">
         <v>181</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -1093,12 +1096,12 @@
       </c>
     </row>
     <row r="3" ht="180" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>L-J-002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1118,12 +1121,12 @@
           <t>お祭りに行く</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -1141,7 +1144,7 @@
 （ナレーション）大（おお）きな 音（おと）と 光（ひかり）。カイの 胸（むね）は どきどきしていた。</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="4" t="n">
         <v>165</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -1273,12 +1276,12 @@
       </c>
     </row>
     <row r="2" ht="225" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>L-L-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1298,12 +1301,12 @@
           <t>はじめての美容院</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -1322,7 +1325,7 @@
 （ナレーション）少（すこ）し 短すぎたけれど、カイは なんだか うれしかった。</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="4" t="n">
         <v>210</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -1454,12 +1457,12 @@
       </c>
     </row>
     <row r="2" ht="165" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>L-B-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1479,12 +1482,12 @@
           <t>好きな食べ物の話</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -1498,7 +1501,7 @@
 カイ：みなさんの 好（す）きな 日本（にほん）の 食べ物は 何（なん）ですか？ また 教（おし）えてね。じゃあ、また！</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="4" t="n">
         <v>177</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -1630,12 +1633,12 @@
       </c>
     </row>
     <row r="2" ht="120" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>L-R-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1655,12 +1658,12 @@
           <t>桜が満開（国内）</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>ニュース</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -1670,7 +1673,7 @@
           <t>おはようございます。今朝（けさ）の ニュースです。昨日（きのう）、東京（とうきょう）の 公園（こうえん）で 桜（さくら）が 満開（まんかい）に なりました。週末（しゅうまつ）は たくさんの 家族（かぞく）連（づ）れで にぎわいそうです。天気（てんき）も よく、お花見（はなみ）に ぴったりの 一日（いちにち）に なるでしょう。一方（いっぽう）、来週（らいしゅう）からは 少（すこ）し 寒（さむ）く なるという 予報（よほう）も 出（で）ています。体調（たいちょう）に 気（き）を つけて お過（す）ごしください。では、今日（きょう）も よい 一日を。</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="4" t="n">
         <v>142</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -1700,12 +1703,12 @@
       </c>
     </row>
     <row r="3" ht="105" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>L-R-002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1725,12 +1728,12 @@
           <t>全国の天気（天気）</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>天気予報</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -1740,7 +1743,7 @@
           <t>全国（ぜんこく）の 天気（てんき）です。今日（きょう）は 西日本（にしにほん）で 晴（は）れますが、東日本（ひがしにほん）は 午後（ごご）から 雲（くも）が 多（おお）く なるでしょう。夜（よる）には 雨（あめ）が 降（ふ）る 所（ところ）も あります。傘（かさ）を 持（も）って 出（で）かけると 安心（あんしん）です。気温（きおん）は 各地（かくち）で 20度（ど）前後（ぜんご）、過（す）ごしやすい 一日（いちにち）に なりそうです。</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="4" t="n">
         <v>97</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -1770,12 +1773,12 @@
       </c>
     </row>
     <row r="4" ht="105" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>L-R-003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1795,12 +1798,12 @@
           <t>海外のニュース（国際）</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>ニュース</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -1810,7 +1813,7 @@
           <t>こんにちは、国際（こくさい）ニュースです。アメリカで、新（あたら）しい 技術（ぎじゅつ）の 会議（かいぎ）が 開（ひら）かれました。世界中（せかいじゅう）から たくさんの 研究者（けんきゅうしゃ）が 集（あつ）まりました。日本（にほん）からも 多（おお）くの 企業（きぎょう）が 参加（さんか）し、注目（ちゅうもく）を 集（あつ）めています。来年（らいねん）は アジアでも 同（おな）じ 会議が 開かれる 予定（よてい）です。</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="4" t="n">
         <v>105</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -1840,12 +1843,12 @@
       </c>
     </row>
     <row r="5" ht="90" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>L-R-004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1865,12 +1868,12 @@
           <t>サッカーの試合（スポーツ）</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>ニュース</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -1880,7 +1883,7 @@
           <t>スポーツの ニュースです。昨日（きのう）、サッカーの 試合（しあい）が ありました。日本（にほん）チームは 2対（たい）1で 勝（か）ちました。最後（さいご）の ゴールは、とても すばらしかったです。スタジアムの ファンは 大（おお）きな 声（こえ）で 応援（おうえん）しました。次（つぎ）の 試合は 来週（らいしゅう）の 土曜日（どようび）です。楽（たの）しみですね。</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="4" t="n">
         <v>109</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -1910,12 +1913,12 @@
       </c>
     </row>
     <row r="6" ht="120" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>L-R-005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1935,12 +1938,12 @@
           <t>勉強が続かない</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>トーク</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -1950,7 +1953,7 @@
           <t>こんばんは、パーソナリティの ユウキです。今日（きょう）も 一日（いちにち）お疲（つか）れさまでした。さて、リスナーの みなさんから お便（たよ）りを いただきました。「最近（さいきん）、日本語（にほんご）の 勉強（べんきょう）が 続（つづ）かなくて 困（こま）っています」。わかります〜。でも、大丈夫（だいじょうぶ）。毎日（まいにち）5分（ふん）でも いいんです。好（す）きな ドラマや 歌（うた）で 楽（たの）しく 続（つづ）けましょう。それでは、今夜（こんや）の 一曲（いっきょく）です。</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="4" t="n">
         <v>142</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -1980,12 +1983,12 @@
       </c>
     </row>
     <row r="7" ht="90" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>L-R-006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2005,12 +2008,12 @@
           <t>漢字が覚えられない</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>トーク</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -2020,7 +2023,7 @@
           <t>今日（きょう）の お便（たよ）りです。「漢字（かんじ）が なかなか 覚（おぼ）えられません」。わかります。漢字は 数（かず）が 多（おお）いですからね。おすすめは、毎日（まいにち）少（すこ）しずつ、生活（せいかつ）の 中（なか）で 見（み）た 漢字を 覚（おぼ）えることです。看板（かんばん）や メニューも いい 教材（きょうざい）ですよ。あせらず 続（つづ）けましょう。</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="4" t="n">
         <v>103</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -2050,12 +2053,12 @@
       </c>
     </row>
     <row r="8" ht="120" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>L-R-007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2075,12 +2078,12 @@
           <t>ゲストのカイさん</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>対話</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -2096,7 +2099,7 @@
 司会：いいですね！ がんばってください。</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="4" t="n">
         <v>142</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -2126,12 +2129,12 @@
       </c>
     </row>
     <row r="9" ht="135" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>L-R-008</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2151,12 +2154,12 @@
           <t>週末どうだった？</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>対話</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -2171,7 +2174,7 @@
 カイ：へえ、いいね！</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="I9" s="4" t="n">
         <v>122</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -2303,12 +2306,12 @@
       </c>
     </row>
     <row r="2" ht="150" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>L-M-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2324,12 +2327,12 @@
           <t>消えた駅弁の謎 第1話：駅で事件発生</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -2344,7 +2347,7 @@
 （ナレーション）田中（たなか）さんは 考（かんが）えた。これは ただの どろぼうでは ないかもしれない。</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="4" t="n">
         <v>143</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -2374,12 +2377,12 @@
       </c>
     </row>
     <row r="3" ht="165" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>L-M-002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2395,12 +2398,12 @@
           <t>消えた駅弁の謎 第2話：証言を聞く</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>対話</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -2416,7 +2419,7 @@
 田中：（首（くび）を かしげて）うーん、おかしいなあ…。</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="4" t="n">
         <v>144</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -2446,12 +2449,12 @@
       </c>
     </row>
     <row r="4" ht="135" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>L-M-003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2467,12 +2470,12 @@
           <t>消えた駅弁の謎 第3話：容疑者登場</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>対話</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -2487,7 +2490,7 @@
 清掃員：えっ、いや、これは…！</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="4" t="n">
         <v>124</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -2517,12 +2520,12 @@
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>L-M-004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2538,12 +2541,12 @@
           <t>消えた駅弁の謎 第4話：真犯人は？</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -2558,7 +2561,7 @@
 田中：はは、事件（じけん）は 無事（ぶじ）解決（かいけつ）、ですね。</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="4" t="n">
         <v>145</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -2588,12 +2591,12 @@
       </c>
     </row>
     <row r="6" ht="165" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>L-M-005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2609,12 +2612,12 @@
           <t>消えた最終電車</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -2629,7 +2632,7 @@
 （つづく）</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="4" t="n">
         <v>154</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -2760,13 +2763,13 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="300" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="420" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>L-D-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2776,55 +2779,55 @@
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n"/>
+      <c r="D2" s="3" t="inlineStr"/>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>カップラーメンの誕生</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>（ナレーション）戦後（せんご）の 日本（にほん）。町（まち）には 食（た）べ物（もの）を 求（もと）める 人々（ひとびと）の 長（なが）い 行列（ぎょうれつ）が あった。それを 見（み）て、一人（ひとり）の 男（おとこ）、安藤（あんどう）さんは 強（つよ）く 思（おも）った。
-安藤：お湯（ゆ）を 入（い）れるだけで すぐ 食（た）べられる めんが あれば、みんなが 助（たす）かるはずだ。
-（ナレーション）その日（ひ）から、小（ちい）さな 小屋（こや）に こもる 毎日（まいにち）が 始（はじ）まった。
-妻（つま）：あなた、また 徹夜（てつや）ですか。体（からだ）を こわしますよ。
-安藤：あと 少（すこ）しなんだ。あきらめるわけには いかない。
-（ナレーション）失敗（しっぱい）は 数（かぞ）えきれない。めんが すぐ 悪（わる）くなって しまう。ある日（ひ）、妻（つま）が 作（つく）る 天（てん）ぷらを 見（み）て——
-安藤：そうか！ 油（あぶら）で あげれば、水分（すいぶん）が とんで、めんが かわく！
-（ナレーション）こうして、世界（せかい）で はじめての インスタントラーメンが 生（う）まれた。今（いま）では 世界中（せかいじゅう）で 一年（いちねん）に 1000億（おく）食（しょく）。小（ちい）さな ひらめきが、本当（ほんとう）に 世界（せかい）を 変（か）えたのだ。</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>293</v>
+          <t>（ナレーション）戦後（せんご）の日本（にほん）。焼（や）け野原（のはら）が広（ひろ）がる寒（さむ）い夜（よる）、一軒（いっけん）の屋台（やたい）に長（なが）い行列（ぎょうれつ）ができていた。人々（ひとびと）は、温（あたた）かいラーメン一杯（いっぱい）を、ふるえながら待（ま）っていた。その光景（こうけい）を、安藤（あんどう）はじっと見（み）つめていた。
+安藤：「これほど多（おお）くの人（ひと）が、一杯（いっぱい）のラーメンを求（もと）めている。家（いえ）で、すぐに、手軽（てがる）に食（た）べられるラーメンを作（つく）れないだろうか」。
+（ナレーション）安藤（あんどう）は、自宅（じたく）の裏（うら）に小（ちい）さな小屋（こや）を建（た）て、たった一人（ひとり）で研究（けんきゅう）を始（はじ）めた。来（く）る日（ひ）も来（く）る日（ひ）も、麺（めん）づくりに明（あ）け暮（く）れる。だが、ゆでた麺（めん）はすぐにのびて、味（あじ）も落（お）ちてしまう。失敗（しっぱい）は何百回（なんびゃっかい）も続（つづ）いた。
+安藤：「どうすれば、長（なが）く保存（ほぞん）でき、湯（ゆ）をかけるだけで元（もと）に戻（もど）るんだ…」。
+（ナレーション）眠（ねむ）る時間（じかん）も惜（お）しんだ。見（み）かねた妻（つま）が、夜（よる）おそく台所（だいどころ）から声（こえ）をかけた。
+妻：「あなた、少（すこ）し休（やす）んだら？ 今日（きょう）は天（てん）ぷらを揚（あ）げましたよ」。
+（ナレーション）その時（とき）だった。安藤（あんどう）の目（め）が、油（あぶら）の中（なか）の天（てん）ぷらに釘付（くぎづ）けになった。衣（ころも）から、無数（むすう）の泡（あわ）が立（た）ちのぼっている。水分（すいぶん）が一気（いっき）に飛（と）んでいく――。「これだ！ 油（あぶら）で揚（あ）げれば麺（めん）は乾（かわ）き、無数（むすう）の穴（あな）に湯（ゆ）がしみ込（こ）めば、麺（めん）は元（もと）に戻（もど）る！」。
+（ナレーション）こうして一杯（いっぱい）のインスタントラーメンが生（う）まれた。さらに安藤（あんどう）は、世界（せかい）へ届（とど）けるため、器（うつわ）ごと食（た）べられる「カップ」を発明（はつめい）する。発売（はつばい）の日（ひ）、半信半疑（はんしんはんぎ）だった人々（ひとびと）は、湯（ゆ）を注（そそ）いで三分（さんぷん）、ふたを開（あ）けて笑顔（えがお）になった。一人（ひとり）の執念（しゅうねん）が、世界（せかい）の食卓（しょくたく）を永遠（えいえん）に変（か）えたのである。</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>537</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>(Narration) Postwar Japan. In the towns were long lines of people seeking food. Seeing that, one man, Mr. Ando, thought strongly: / Ando: If there were noodles you could eat right away just by adding hot water, it would help everyone. / (Narration) From that day, days of shutting himself in a small shed began. / Wife: Dear, an all-nighter again? You'll ruin your health. / Ando: Just a little more. I can't give up. / (Narration) The failures were countless—the noodles spoiled quickly. One day, watching his wife make tempura— / Ando: That's it! If you fry them in oil, the water evaporates and the noodles dry! / (Narration) Thus the world's first instant ramen was born. Today, 100 billion servings a year worldwide. A small spark truly changed the world.</t>
+          <t>Postwar Japan. On a cold night amid the burnt ruins, a long line formed at a single food stall. People waited, shivering, for one warm bowl of ramen. Ando watched intently. 'So many people long for a single bowl. Could I make ramen you can eat at home, quickly and easily?' He built a small shed behind his house and began researching alone. Day after day he toiled over noodles, but boiled noodles soon went soft and lost flavor. He failed hundreds of times. 'How can I make it keep, and return to normal with just hot water?' He begrudged even sleep. His worried wife called out late at night: 'Dear, why not rest? I fried tempura today.' That was the moment. Ando's eyes fixed on the tempura in the oil—countless bubbles rising from the batter, the moisture flying off. 'That's it! Fry the noodles and they dry; pour hot water into the tiny holes and they return.' Thus instant ramen was born. To reach the world, he also invented the edible 'cup.' On launch day, doubtful people poured hot water, waited three minutes, lifted the lid, and smiled. One man's tenacity changed dinner tables worldwide forever.</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>〜はずだ／あきらめるわけには いかない／そうか！</t>
+          <t>〜ないだろうか／〜だけで／〜ば 元に戻る</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>困難→不屈→ひらめき→成功。会話で臨場感。</t>
+          <t>執念が世界を変えた発明。</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>身近なカップ麺の感動秘話・濃い内容。</t>
+          <t>失敗の先のひらめき。</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -2833,13 +2836,13 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="315" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="420" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>L-D-002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2849,69 +2852,69 @@
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n"/>
+      <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>はやぶさの帰還</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+          <t>新幹線――夢の超特急</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>（ナレーション）小（ちい）さな 宇宙船（うちゅうせん）「はやぶさ」は、地球（ちきゅう）から 3億（おく）キロ 離（はな）れた 小惑星（しょうわくせい）を 目指（めざ）した。星（ほし）の 石（いし）を 取（と）って 帰（かえ）る——だれも 成功（せいこう）した ことの ない 挑戦（ちょうせん）だった。
-（ナレーション）しかし、旅（たび）は 苦難（くなん）の 連続（れんぞく）。エンジンは こわれ、ついに 通信（つうしん）も 切（き）れた。
-研究者（けんきゅうしゃ）A：信号（しんごう）が…ありません。はやぶさが、いません。
-研究者B：あきらめるな。きっと どこかで 生（い）きている。呼（よ）び続（つづ）けよう。
-（ナレーション）管制室（かんせいしつ）の 人々（ひとびと）は、来（く）る日（ひ）も 来る日も 信号（しんごう）を 送（おく）り続（つづ）けた。そして 7週間後（しゅうかんご）——
-研究者A：…返事（へんじ）が、来（き）ました！ はやぶさ、生（い）きてます！
-（ナレーション）7年（ねん）、60億（おく）キロの 旅（たび）の すえ、はやぶさは 帰（かえ）ってきた。最後（さいご）は 自分（じぶん）の 体（からだ）を 燃（も）やしながら、石（いし）の カプセルだけを そっと 送（おく）り届（とど）けた。その 光（ひかり）に、世界中（せかいじゅう）が 涙（なみだ）した。</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>283</v>
+          <t>（ナレーション）1964年（ねん）、東京（とうきょう）と大阪（おおさか）を結（むす）ぶ新幹線（しんかんせん）が走（はし）り始（はじ）めた。当時（とうじ）、時速（じそく）200キロを超（こ）える電車（でんしゃ）は、世界（せかい）のどこにも存在（そんざい）しなかった。
+技術者（ぎじゅつしゃ）：「そんなスピードは危険（きけん）だ。脱線（だっせん）したら、大事故（だいじこ）になる」。
+（ナレーション）多（おお）くの人（ひと）が、無理（むり）だと反対（はんたい）した。けれど、技術者（ぎじゅつしゃ）たちはあきらめなかった。彼（かれ）らは、空気（くうき）の力（ちから）、線路（せんろ）のカーブ、車輪（しゃりん）の揺（ゆ）れを、何度（なんど）も何度（なんど）も計算（けいさん）し直（なお）した。安全（あんぜん）のためなら、どんな小（ちい）さな問題（もんだい）も見逃（みのが）さなかった。
+技術者：「ここで妥協（だきょう）すれば、必（かなら）ず後（あと）で事故（じこ）が起（お）きる。とことんやろう」。
+（ナレーション）試験（しけん）と改良（かいりょう）の日々（ひび）。眠（ねむ）れない長（なが）い夜（よる）が続（つづ）いた。仲間（なかま）と知恵（ちえ）を出（だ）し合（あ）い、一（ひと）つずつ壁（かべ）を越（こ）えていく。そして迎（むか）えた開業（かいぎょう）の日（ひ）。白（しろ）と青（あお）の車両（しゃりょう）が、静（しず）かに、しかし力強（ちからづよ）くホームをすべり出（で）た。
+（ナレーション）新幹線（しんかんせん）は、一度（いちど）の事故（じこ）もなく、東京（とうきょう）から大阪（おおさか）まで走（はし）りきった。「夢（ゆめ）の超特急（ちょうとっきゅう）」は、日本（にほん）の誇（ほこ）りとなった。それは単（たん）なる速（はや）い電車（でんしゃ）ではない。不可能（ふかのう）を可能（かのう）に変（か）えた、技術者（ぎじゅつしゃ）たちの執念（しゅうねん）の結晶（けっしょう）だった。
+（ナレーション）かつて長（なが）い時間（じかん）がかかった東京（とうきょう）と大阪（おおさか）の間（あいだ）が、ぐっと近（ちか）くなった。仕事（しごと）でも旅行（りょこう）でも、日帰（ひがえ）りができる。新幹線（しんかんせん）は、人（ひと）と人（ひと）、町（まち）と町（まち）の距離（きょり）を、大（おお）きく縮（ちぢ）めたのだ。今（いま）も世界中（せかいじゅう）の高速鉄道（こうそくてつどう）が、この一本（いっぽん）の線路（せんろ）を手本（てほん）にし続（つづ）けている。</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>491</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>(Narration) The small spacecraft 'Hayabusa' aimed for an asteroid 300 million km from Earth. To collect rocks from a star and return—a challenge no one had ever succeeded at. / (Narration) But the journey was one hardship after another. The engines broke, and finally communication was lost. / Researcher A: There's... no signal. Hayabusa is gone. / Researcher B: Don't give up. It's surely alive somewhere. Let's keep calling. / (Narration) The control room kept sending signals day after day. Then, seven weeks later— / Researcher A: ...A reply came! Hayabusa is alive! / (Narration) After seven years and 6 billion km, Hayabusa came home. At the end, burning up its own body, it gently delivered only the capsule of rocks. The whole world wept at that light.</t>
+          <t>In 1964, the Shinkansen linking Tokyo and Osaka began to run. At the time, no train anywhere in the world exceeded 200 km/h. 'Such speed is dangerous. If it derails, there will be a terrible accident.' Many opposed it as impossible. But the engineers did not give up. They recalculated air resistance, track curves, and wheel vibration again and again. For safety, they overlooked no problem, however small. 'If we compromise here, an accident will surely come later. Let's see it through.' Days of testing and improvement; long sleepless nights. Sharing wisdom with colleagues, they cleared the walls one by one. Then came opening day. The white-and-blue cars slid quietly but powerfully from the platform. The Shinkansen ran the whole way from Tokyo to Osaka without a single accident. The 'dream super-express' became Japan's pride—not merely a fast train, but the crystallization of engineers' tenacity that turned the impossible into the possible. Even now, high-speed railways around the world look to this one line as their model.</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>あきらめるな／返事が 来ました／〜のすえ</t>
+          <t>〜を超える／〜のためなら／〜きった</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>苦難→不屈→奇跡の帰還。管制室の会話で手に汗。</t>
+          <t>不可能を可能にした執念。</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>実話の大感動・濃い内容。</t>
+          <t>反対を覆した技術の結晶。</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>多声TTS:ナレーター/研究者A/研究者B</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="165" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+          <t>多声TTS:ナレーター/技術者</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="420" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>L-D-003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2921,63 +2924,69 @@
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n"/>
+      <c r="D4" s="3" t="inlineStr"/>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>黒部ダムをつくった男たち</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+          <t>ライト兄弟、空へ</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>昭和（しょうわ）の 時代（じだい）、富山（とやま）の 山（やま）おくに、巨大（きょだい）な ダムを つくる 計画（けいかく）が あった。黒部（くろべ）ダムである。けわしい 山（やま）、冷（つめ）たい 水（みず）、そして 固（かた）い 岩（いわ）。工事（こうじ）は 想像（そうぞう）を こえる 困難（こんなん）の 連続（れんぞく）だった。とくに トンネルを ほる 作業（さぎょう）では、地下水（ちかすい）が ふき出（だ）し、何度（なんど）も 工事（こうじ）が 止（と）まった。それでも 作業員（さぎょういん）たちは あきらめなかった。7年（ねん）の 月日（つきひ）と、のべ 1000万人（まんにん）の 力（ちから）で、ダムは ついに 完成（かんせい）した。今（いま）も 黒部（くろべ）の 水（みず）は、人々（ひとびと）の 暮（く）らしを ささえている。</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>180</v>
+          <t>（ナレーション）100年（ねん）以上（いじょう）前（まえ）、アメリカの小（ちい）さな町（まち）に、自転車屋（じてんしゃや）を営（いとな）む二人（ふたり）の兄弟（きょうだい）がいた。ライト兄弟（きょうだい）である。当時（とうじ）、「人間（にんげん）が空（そら）を飛（と）ぶ」など、だれもが笑（わら）う夢物語（ゆめものがたり）だった。
+兄（あに）：「鳥（とり）は、どうやって風（かぜ）を受（う）け、体（からだ）を傾（かたむ）けて曲（ま）がっているんだろう」。
+（ナレーション）二人（ふたり）は来（く）る日（ひ）も来（く）る日（ひ）も、空（そら）をとぶ鳥（とり）を観察（かんさつ）した。翼（つばさ）の形（かたち）を作（つく）っては試（ため）し、こわれては、また作（つく）り直（なお）す。風（かぜ）の強（つよ）い丘（おか）で、何度（なんど）も地面（じめん）に たたきつけられた。それでも、二人（ふたり）の目（め）は、いつも空（そら）を見（み）ていた。
+弟（おとうと）：「兄（あに）さん、今度（こんど）こそ、風（かぜ）に乗（の）れる気（き）がする」。
+（ナレーション）1903年（ねん）の冷（つめ）たい冬（ふゆ）の朝（あさ）。強（つよ）い風（かぜ）の中（なか）、手作（てづく）りの飛行機（ひこうき）がエンジンの音（おと）を響（ひび）かせた。プロペラが回（まわ）り、機体（きたい）がゆっくりと動（うご）き出（だ）す。そして――ふわりと、車輪（しゃりん）が地面（じめん）を離（はな）れた。
+（ナレーション）飛（と）んだ時間（じかん）は、わずか12秒（びょう）。距離（きょり）は、たった36メートル。けれどそれは、人類（じんるい）が自分（じぶん）の力（ちから）で初（はじ）めて空（そら）を飛（と）んだ、歴史（れきし）が変（か）わった瞬間（しゅんかん）だった。
+（ナレーション）成功（せいこう）の裏（うら）には、何年（なんねん）もの地道（じみち）な努力（どりょく）があった。二人（ふたり）は、失敗（しっぱい）の記録（きろく）を一（ひと）つ残（のこ）らずノートに書（か）きとめ、つぎの工夫（くふう）に生（い）かしていったのだ。だれもが笑（わら）った夢（ゆめ）を、あきらめなかった二人（ふたり）。その小（ちい）さな12秒（びょう）から、世界中（せかいじゅう）の空（そら）の旅（たび）が始（はじ）まったのである。</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>473</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>In the Showa era, there was a plan to build a huge dam deep in the mountains of Toyama: the Kurobe Dam. Steep mountains, cold water, and hard rock—construction was a series of difficulties beyond imagination. Especially when digging the tunnel, groundwater gushed out and work stopped many times. Still, the workers never gave up. With seven years and the effort of ten million people in total, the dam was finally completed. Even now, Kurobe's water supports people's lives.</t>
+          <t>More than a century ago, in a small American town, two brothers ran a bicycle shop: the Wright brothers. Back then, 'humans flying' was a fairy tale everyone laughed at. 'How do birds catch the wind and tilt their bodies to turn?' Day after day they watched birds in flight. They built wing shapes and tested them; when they broke, they rebuilt. On a windy hill they were dashed to the ground again and again. Yet their eyes were always on the sky. 'Brother, this time I feel we can ride the wind.' On a cold winter morning in 1903, in a strong wind, their handmade airplane roared. The propeller turned, the craft slowly moved—and then, gently, the wheels left the ground. The flight lasted just 12 seconds, only 36 meters. But it was the moment humanity first flew by its own power, and history changed. Two brothers who never gave up on a dream everyone mocked. From that tiny 12 seconds, the world's journeys through the sky began.</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>〜を こえる／何度も／それでも</t>
+          <t>〜だろう／〜ては 〜直す／それでも</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>困難に挑む実話。</t>
+          <t>笑われた夢への挑戦。</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>不可能を可能にした執念。</t>
+          <t>12秒が歴史を変えた。</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>1話者・朗読</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="165" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+          <t>多声TTS:ナレーター/兄/弟</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="420" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>L-D-004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2987,63 +2996,69 @@
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n"/>
+      <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>新幹線――夢の超特急</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+          <t>エジソンと電球</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>1964年（ねん）、東京（とうきょう）と 大阪（おおさか）を むすぶ「新幹線（しんかんせん）」が 走（はし）り はじめた。当時（とうじ）、時速（じそく）200キロを こえる 電車（でんしゃ）は、世界（せかい）の どこにも なかった。『そんな スピードは あぶない』と 多（おお）くの 人（ひと）が 反対（はんたい）した。技術者（ぎじゅつしゃ）たちは、空気（くうき）の 力（ちから）や 線路（せんろ）の カーブを 何度（なんど）も 計算（けいさん）し、安全（あんぜん）の ために 知恵（ちえ）を しぼった。開業（かいぎょう）の 日（ひ）、新幹線（しんかんせん）は 一度（いちど）の 事故（じこ）も なく 走（はし）りきった。夢（ゆめ）の 超特急（ちょうとっきゅう）は、日本（にほん）の 誇（ほこ）りに なった。</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>163</v>
+          <t>（ナレーション）まだ電気（でんき）のない時代（じだい）。夜（よる）の暗（くら）やみを照（て）らすのは、ろうそくやランプの、小（ちい）さくゆれる炎（ほのお）だけだった。アメリカの発明家（はつめいか）エジソンは、決心（けっしん）した。「だれもが使（つか）える、長（なが）く明（あか）るい電球（でんきゅう）を作（つく）る」と。
+（ナレーション）光（ひか）る糸（いと）の材料（ざいりょう）を探（さが）して、エジソンは実験（じっけん）をくり返（かえ）した。木綿（もめん）、紙（かみ）、髪（かみ）の毛（け）――ありとあらゆるものを試（ため）したが、糸（いと）はすぐに燃（も）えつきてしまう。失敗（しっぱい）の数（かず）は、千回（せんかい）をこえた。
+助手（じょしゅ）：「先生（せんせい）、また失敗（しっぱい）です。もう、あきらめませんか」。
+エジソン：「いや。これは失敗（しっぱい）じゃない。『うまくいかない方法（ほうほう）』を、また一（ひと）つ見（み）つけただけさ」。
+（ナレーション）エジソンは、最後（さいご）まで信（しん）じることをやめなかった。やがて、日本（にほん）の竹（たけ）から作（つく）った細（ほそ）い糸（いと）が、なんと40時間（じかん）以上（いじょう）も光（ひか）り続（つづ）けた。研究室（けんきゅうしつ）に、あたたかな明（あ）かりがともった。
+（ナレーション）その夜（よる）、世界（せかい）の暗（くら）やみは、少（すこ）しずつ明（あか）るく照（て）らされていった。電球（でんきゅう）だけではない。エジソンは生涯（しょうがい）に千以上（せんいじょう）もの発明（はつめい）を世（よ）に残（のこ）した。その原動力（げんどうりょく）は、子（こ）どものころから変（か）わらない「なぜ？」という強（つよ）い好奇心（こうきしん）だった。
+（ナレーション）「天才（てんさい）とは、1パーセントのひらめきと、99パーセントの努力（どりょく）である」。失敗（しっぱい）を恐（おそ）れず、努力（どりょく）を続（つづ）けたエジソンの言葉（ことば）は、今（いま）も世界中（せかいじゅう）の人（ひと）の胸（むね）に生（い）きている。</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>479</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>In 1964, the Shinkansen connecting Tokyo and Osaka began running. At the time, no train anywhere in the world exceeded 200 km/h. 'Such speed is dangerous,' many people opposed. Engineers calculated air resistance and track curves again and again, racking their brains for safety. On opening day, the Shinkansen ran the whole way without a single accident. The dream super-express became a source of pride for Japan.</t>
+          <t>In an age without electricity, the only thing lighting the darkness of night was the small, flickering flame of candles and lamps. The American inventor Edison resolved: 'I will make a long-lasting, bright bulb that anyone can use.' Searching for a glowing filament, Edison repeated experiments—cotton, paper, hair—he tried everything, but the thread burned out at once. His failures passed a thousand. 'Sir, another failure. Shouldn't we give up?' 'No. This isn't failure. I've just found one more way that doesn't work.' Edison never stopped believing. Eventually, a thin filament made from Japanese bamboo glowed for over 40 hours. A warm light came on in the lab. That night, the world's darkness was lit, little by little. 'Genius is 1% inspiration and 99% perspiration.' The words of Edison, who feared no failure and kept on striving, still live in people's hearts around the world.</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>〜を こえる／〜の ために／〜きった</t>
+          <t>〜と決心した／くり返した／〜じゃない</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>世界初の高速鉄道。</t>
+          <t>失敗を恐れぬ努力。</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>反対を覆した技術の結晶。</t>
+          <t>世界の夜を明るくした。</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>1話者・朗読</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="165" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+          <t>多声TTS:ナレーター/エジソン/助手</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="420" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>L-D-005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -3053,53 +3068,59 @@
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n"/>
+      <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>青い光をもとめて</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
+          <t>ヘレン・ケラーと先生</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>赤（あか）と 緑（みどり）の 光（ひかり）は できても、「青（あお）い 光（ひかり）」を 出（だ）す LEDだけは、だれにも 作（つく）れなかった。『20世紀（せいき）中（じゅう）には 無理（むり）だ』とも 言（い）われた。日本（にほん）の ある 研究者（けんきゅうしゃ）は、小（ちい）さな 会社（かいしゃ）で、たった 一人（ひとり）、何千回（なんぜんかい）も 実験（じっけん）を くりかえした。失敗（しっぱい）、また 失敗（しっぱい）。それでも 手（て）を 止（と）めなかった。ついに 青（あお）い 光（ひかり）が ともった 瞬間（しゅんかん）、世界（せかい）の 明（あ）かりは 変（か）わった。白（しろ）い LEDが 生（う）まれ、街（まち）も 家（いえ）も 明（あか）るく なった。その 功績（こうせき）は、のちに ノーベル賞（しょう）に かがやいた。</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>182</v>
+          <t>（ナレーション）目（め）が見（み）えず、耳（みみ）も聞（き）こえない少女（しょうじょ）がいた。ヘレン・ケラー。言葉（ことば）を知（し）らない彼女（かのじょ）の心（こころ）は、出口（でぐち）のない暗（くら）い闇（やみ）の中（なか）にあった。思（おも）い通（どお）りにならず、ヘレンは毎日（まいにち）あばれ、家族（かぞく）も困（こま）りはてていた。
+（ナレーション）そんなある日（ひ）、一人（ひとり）の家庭教師（かていきょうし）がやって来（き）た。サリバン先生（せんせい）である。
+サリバン：「あきらめません。わたしが、あなたに世界（せかい）の名前（なまえ）を教（おし）えます」。
+（ナレーション）先生（せんせい）は、ヘレンの手（て）のひらに、指（ゆび）で何度（なんど）も文字（もじ）を書（か）いた。コップ、人形（にんぎょう）、いす……。けれどヘレンには、それが「名前（なまえ）」だとわからない。根気（こんき）のいる日々（ひび）が続（つづ）いた。
+（ナレーション）ある朝（あさ）、二人（ふたり）は井戸（いど）のそばにいた。先生（せんせい）がヘレンの手（て）に、冷（つめ）たい水（みず）を流（なが）しながら、もう一方（いっぽう）の手（て）に「W-A-T-E-R」と書（か）いた。その瞬間（しゅんかん）、ヘレンの体（からだ）に電気（でんき）が走（はし）ったように、はっと動（うご）きが止（と）まった。「そうか……これが『水（みず）』なんだ！」。
+（ナレーション）世界（せかい）のすべてに名前（なまえ）があると知（し）った、その日（ひ）。ヘレンの暗（くら）い世界（せかい）に、光（ひかり）がさした。やがて彼女（かのじょ）は懸命（けんめい）に学（まな）び、大学（だいがく）を卒業（そつぎょう）した。
+（ナレーション）後（のち）にヘレンは、世界中（せかいじゅう）を旅（たび）して講演（こうえん）し、目（め）や耳（みみ）の不自由（ふじゆう）な人々（ひとびと）のために力（ちから）をつくした。「世界（せかい）は苦（くる）しみに満（み）ちているが、それを乗（の）りこえる力（ちから）にも満（み）ちている」。サリバン先生（せんせい）とヘレンの物語（ものがたり）は、同（おな）じ苦（くる）しみを持（も）つ世界中（せかいじゅう）の人々（ひとびと）に、今（いま）も希望（きぼう）を与（あた）え続（つづ）けている。</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>508</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Red and green light were possible, but a blue-light LED was something no one could make. 'It's impossible within the 20th century,' they said. One Japanese researcher, alone at a small company, repeated experiments thousands of times. Failure, and failure again. Still he never stopped. The moment blue light finally lit up, the world's lighting changed. White LEDs were born, brightening streets and homes. The achievement later shone with a Nobel Prize.</t>
+          <t>There was a girl who could neither see nor hear: Helen Keller. Knowing no words, her heart was in a dark gloom with no exit. Unable to make herself understood, Helen raged every day, and her family was at a loss. Then one day a tutor came—Miss Sullivan. 'I won't give up. I will teach you the names of the world.' The teacher wrote letters with her finger on Helen's palm, again and again—cup, doll, chair. But Helen couldn't grasp that these were 'names.' Patient days continued. One morning, the two were by a well. As the teacher let cold water flow over one of Helen's hands, she spelled 'W-A-T-E-R' on the other. In that instant, as if electricity ran through her, Helen froze. 'I see... this is water!' The day she learned that everything in the world has a name, light shone into her dark world. In time she studied hard, graduated from university, and became someone who gave hope to people worldwide who shared her struggle.</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>〜だけは／くりかえした／〜瞬間</t>
+          <t>〜ません／〜ながら／〜と知った</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>青色LEDの挑戦。</t>
+          <t>闇に光がさした瞬間。</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>孤独な執念がノーベル賞に。</t>
+          <t>学ぶ喜びと希望。</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>1話者・朗読</t>
+          <t>多声TTS:ナレーター/サリバン</t>
         </is>
       </c>
     </row>
@@ -3205,13 +3226,13 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="210" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="300" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>L-T-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -3221,68 +3242,66 @@
           <t>昔話</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n"/>
+      <c r="D2" s="3" t="inlineStr"/>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>桃太郎</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>（ナレーション）むかしむかし、ある ところに、おじいさんと おばあさんが いました。ある日（ひ）、川（かわ）から 大（おお）きな 桃（もも）が どんぶらこ、どんぶらこ、と 流（なが）れて きました。
-おばあさん：おや、なんて 大（おお）きな 桃（もも）だろう！ 家（いえ）に 持（も）って 帰（かえ）りましょう。
-（ナレーション）家（いえ）で 桃（もも）を 切（き）ろうとすると…パカッ！ 中（なか）から 元気（げんき）な 男（おとこ）の子（こ）が 生（う）まれました。
-おじいさん：おお、元気（げんき）な 子（こ）だ！ 名前（なまえ）は 桃太郎（ももたろう）に しよう。
-（ナレーション）大（おお）きく なった 桃太郎（ももたろう）は、ある日（ひ） 言（い）いました。
-桃太郎：おじいさん、おばあさん。鬼（おに）を 退治（たいじ）しに 行（い）ってきます！</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>204</v>
+          <t>（ナレーション）むかしむかし、あるところに、おじいさんとおばあさんが住（す）んでいました。ある日（ひ）、川（かわ）で大（おお）きな桃（もも）を拾（ひろ）い、家（いえ）で割（わ）ると、中（なか）から元気（げんき）な男（おとこ）の子（こ）が飛（と）び出（だ）しました。二人（ふたり）はその子（こ）を桃太郎（ももたろう）と名（な）づけ、大切（たいせつ）に育（そだ）てました。
+（ナレーション）やがて、村（むら）を荒（あ）らす鬼（おに）の話（はなし）を聞（き）いた桃太郎（ももたろう）は、鬼（おに）ヶ島（しま）へ向（む）かう決心（けっしん）をします。
+桃太郎：「おばあさんのきびだんごをあげるから、いっしょに来（き）てくれないか」。
+（ナレーション）道（みち）の途中（とちゅう）で、犬（いぬ）、猿（さる）、きじが仲間（なかま）になりました。鬼（おに）ヶ島（しま）に着（つ）くと、おそろしい鬼（おに）たちが暴（あば）れています。桃太郎（ももたろう）たちは力（ちから）を合（あ）わせて勇敢（ゆうかん）に戦（たたか）い、ついに鬼（おに）を降参（こうさん）させました。鬼（おに）は奪（うば）った宝物（たからもの）を返（かえ）し、二度（にど）と悪（わる）いことをしないと約束（やくそく）しました。桃太郎（ももたろう）は宝物（たからもの）を持（も）ち帰（かえ）り、村（むら）のみんなと幸（しあわ）せに暮（く）らしました。</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>303</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>(Narration) Long ago, an old man and an old woman lived in a certain place. One day, a big peach came floating down the river, donburako, donburako. / Old woman: Oh my, what a big peach! Let's take it home. / (Narration) When they tried to cut the peach at home... crack! A healthy boy was born from inside. / Old man: Oh, a lively boy! Let's name him Momotaro. / (Narration) When Momotaro grew up, one day he said: / Momotaro: Grandpa, Grandma. I'm going off to defeat the ogres!</t>
+          <t>Long ago, an old man and woman lived in a certain place. One day they found a huge peach in the river; when they split it at home, a healthy boy leapt out. They named him Momotaro and raised him with care. In time, hearing of ogres ravaging the village, Momotaro resolved to go to Ogre Island. 'I'll give you Grandma's millet dumplings, so will you come with me?' Along the way, a dog, a monkey, and a pheasant became his companions. On Ogre Island, fearsome ogres were rampaging. Joining their strength, Momotaro and friends fought bravely and at last made the ogres surrender. The ogres returned the stolen treasure and promised never to do wrong again. Momotaro brought the treasure home and lived happily with everyone in the village.</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>なんて 〜だろう／〜ましょう／〜てきます</t>
+          <t>〜決心をする／〜くれないか／力を合わせて</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>昔話の会話＋擬音(どんぶらこ/パカッ)。</t>
+          <t>鬼退治まで一話完結。</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>有名な昔話を会話で。</t>
+          <t>仲間と力を合わせる。</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>多声TTS:ナレーター/おばあさん/おじいさん/桃太郎</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="135" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+          <t>多声TTS:ナレーター/桃太郎</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="315" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>L-T-002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -3292,63 +3311,66 @@
           <t>昔話</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n"/>
+      <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
           <t>浦島太郎</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>むかしむかし、浦島太郎（うらしまたろう）という 若者（わかもの）が いました。ある 日（ひ）、いじめられている 亀（かめ）を 助（たす）けて あげました。お礼（れい）に、亀（かめ）は 太郎（たろう）を 海（うみ）の 中（なか）の「竜宮城（りゅうぐうじょう）」へ つれて 行（い）きました。そこは 美（うつく）しい おとめ「乙姫（おとひめ）」が すむ、ゆめのような 場所（ばしょ）でした。楽（たの）しい 日々（ひび）を すごし、太郎（たろう）が 家（いえ）に 帰（かえ）ると——村（むら）は すっかり 変（か）わって いました。なんと、何百年（なんびゃくねん）もの 時（とき）が すぎて いたのです。</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>157</v>
+          <t>（ナレーション）むかし、浦島太郎（うらしまたろう）という心（こころ）やさしい漁師（りょうし）がいました。ある日（ひ）、浜辺（はまべ）で子（こ）どもたちにいじめられている亀（かめ）を見（み）つけ、お金（かね）をはらって助（たす）けてやりました。
+（ナレーション）数日後（すうじつご）、海（うみ）に出（で）た太郎（たろう）の前（まえ）に、あの亀（かめ）が現（あらわ）れました。「助（たす）けてくれたお礼（れい）に」と、太郎（たろう）を背中（せなか）に乗（の）せ、海（うみ）の底（そこ）の竜宮城（りゅうぐうじょう）へ連（つ）れて行（い）きました。そこでは美（うつく）しい乙姫（おとひめ）が、ごちそうと踊（おど）りで太郎（たろう）をもてなしました。
+乙姫：「おみやげの玉手箱（たまてばこ）です。でも、けっして開（あ）けてはいけませんよ」。
+（ナレーション）夢（ゆめ）のような日々（ひび）。けれど村（むら）が恋（こい）しくなった太郎（たろう）は、玉手箱（たまてばこ）を持（も）って帰（かえ）りました。ところが、村（むら）はすっかり変（か）わり、知（し）っている人（ひと）は一人（ひとり）もいません。竜宮城（りゅうぐうじょう）での数日（すうじつ）の間（あいだ）に、地上（ちじょう）では何百年（なんびゃくねん）も過（す）ぎていたのです。さびしさのあまり、太郎（たろう）が約束（やくそく）を忘（わす）れて箱（はこ）を開（あ）けると、白（しろ）い煙（けむり）がもくもくと出（で）て、太郎（たろう）はたちまち白髪（しらが）のおじいさんになってしまいました。</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>351</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Long ago, there was a young man named Urashima Taro. One day, he rescued a turtle that was being bullied. In return, the turtle took Taro to the 'Dragon Palace' beneath the sea. It was a dreamlike place where the beautiful maiden 'Otohime' lived. After spending happy days there, Taro returned home—but the village had completely changed. Astonishingly, hundreds of years had passed.</t>
+          <t>Long ago there was a kind-hearted fisherman named Urashima Taro. One day on the beach he found a turtle being bullied by children, and paid money to save it. A few days later, out at sea, that turtle appeared before him. 'To thank you for saving me,' it carried Taro on its back to the Dragon Palace at the bottom of the sea. There the beautiful Otohime hosted Taro with feasts and dancing. 'Here is a parting gift, the tamatebako. But you must never open it.' Dreamlike days passed. But missing his village, Taro went home with the box. Yet the village had completely changed, and not a single person he knew remained. During his few days in the palace, hundreds of years had passed on land. Out of loneliness, forgetting the promise, Taro opened the box; white smoke billowed out, and he instantly became a white-haired old man.</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>〜て あげる／〜のような／なんと</t>
+          <t>〜てやる／けっして〜てはいけない／〜のあまり</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>助けた恩と時の流れ。</t>
+          <t>玉手箱の結末まで完結。</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>玉手箱の結末は…?</t>
+          <t>約束を破った代償。</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>1話者・朗読</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="150" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+          <t>多声TTS:ナレーター/乙姫</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="300" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>L-T-003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -3358,63 +3380,66 @@
           <t>昔話</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n"/>
+      <c r="D4" s="3" t="inlineStr"/>
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>かぐや姫</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>むかし、竹（たけ）を とって 暮（く）らす おじいさんが いました。ある 日（ひ）、光（ひか）る 竹（たけ）の 中（なか）から、小（ちい）さな 女（おんな）の 子（こ）が 生（う）まれました。「かぐや姫（ひめ）」と 名（な）づけられた その 子（こ）は、月（つき）のように 美（うつく）しく 育（そだ）ちました。やがて、たくさんの 男（おとこ）たちが 結婚（けっこん）を もうし込（こ）みましたが、姫（ひめ）は 首（くび）を たてに ふりません。実（じつ）は、かぐや姫（ひめ）は 月（つき）の 世界（せかい）から 来（き）た 人（ひと）でした。満月（まんげつ）の 夜（よる）、姫（ひめ）は 月（つき）へ 帰（かえ）って いきました。</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>159</v>
+          <t>（ナレーション）むかし、竹（たけ）を取（と）って暮（く）らすおじいさんがいました。ある日（ひ）、根元（ねもと）が光（ひか）る竹（たけ）を見（み）つけ、切（き）ってみると、中（なか）に手（て）のひらほどの小（ちい）さな女（おんな）の子（こ）がいました。子（こ）どものいなかった夫婦（ふうふ）は大喜（おおよろこ）びで、その子（こ）をかぐや姫（ひめ）と名（な）づけ、大切（たいせつ）に育（そだ）てました。
+（ナレーション）かぐや姫（ひめ）は、月（つき）のように美（うつく）しい娘（むすめ）に育（そだ）ちました。うわさを聞（き）いた多（おお）くの男（おとこ）たちが結婚（けっこん）を申（もう）し込（こ）みましたが、姫（ひめ）は首（くび）を縦（たて）に振（ふ）りません。
+かぐや姫：「ごめんなさい。わたしは、近（ちか）いうちに月（つき）へ帰（かえ）らなければならないのです」。
+（ナレーション）実（じつ）は、かぐや姫（ひめ）は月（つき）の世界（せかい）から来（き）た人（ひと）でした。満月（まんげつ）の夜（よる）、空（そら）から大勢（おおぜい）の使（つか）いが、光（ひかり）とともに姫（ひめ）を迎（むか）えに来（き）ました。おじいさんとおばあさんは泣（な）いて引（ひ）き止（と）めましたが、別（わか）れの時（とき）は来（き）てしまいます。姫（ひめ）は二人（ふたり）に深（ふか）く感謝（かんしゃ）し、別（わか）れを惜（お）しみながら、静（しず）かに天（てん）へのぼっていきました。</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>329</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Long ago, there was an old man who made his living cutting bamboo. One day, a tiny girl was born from a glowing stalk of bamboo. Named 'Kaguya-hime,' she grew as beautiful as the moon. In time, many men proposed marriage, but the princess would not nod yes. In fact, Kaguya-hime was a person from the world of the moon. On the night of the full moon, she returned to the moon.</t>
+          <t>Long ago there was an old man who made his living cutting bamboo. One day he found a stalk glowing at its base; when he cut it, inside was a tiny girl the size of a palm. The childless couple were overjoyed, named her Kaguya-hime, and raised her with care. Kaguya-hime grew into a maiden as beautiful as the moon. Many men who heard the rumor proposed marriage, but the princess would not nod yes. 'I'm sorry. I must return to the moon before long.' In truth, Kaguya-hime was from the world of the moon. On the night of the full moon, a great host of envoys came from the sky with light to fetch her. The old couple wept and tried to hold her back, but the time of parting came. Deeply grateful to them, sad to part, the princess quietly ascended to the heavens.</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>〜の中から／〜のように／やがて</t>
+          <t>〜ません／〜なければならない／〜ながら</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>竹から生まれた姫。</t>
+          <t>月へ帰るまで完結。</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>日本最古の物語の一つ。</t>
+          <t>別れの切なさ。</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>1話者・朗読</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="150" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+          <t>多声TTS:ナレーター/かぐや姫</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="345" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>L-T-004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -3424,63 +3449,68 @@
           <t>昔話</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n"/>
+      <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr">
         <is>
           <t>鶴の恩返し</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>さむい 冬（ふゆ）の 日（ひ）、ある 男（おとこ）が、わなに かかった 鶴（つる）を 助（たす）けました。その 夜（よる）、美（うつく）しい 女（おんな）の 人（ひと）が 家（いえ）を たずねて きて、男（おとこ）の 妻（つま）に なりました。妻（つま）は『けっして 見（み）ないで ください』と 言（い）って、部屋（へや）で 布（ぬの）を おりました。その 布（ぬの）は とても 高（たか）く 売（う）れました。ある 日（ひ）、男（おとこ）が こっそり のぞくと——そこには、自分（じぶん）の 羽根（はね）を ぬいて 布（ぬの）を おる 鶴（つる）の 姿（すがた）が ありました。正体（しょうたい）を 知（し）られた 妻（つま）は、空（そら）へ 飛（と）んで 行（い）きました。</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>169</v>
+          <t>（ナレーション）さむい雪（ゆき）の日（ひ）、一人（ひとり）の男（おとこ）が、わなにかかって苦（くる）しんでいる鶴（つる）を見（み）つけ、そっと逃（に）がしてやりました。その夜（よる）、戸（と）をたたく音（おと）がして、美（うつく）しい女（おんな）の人（ひと）が「道（みち）に迷（まよ）った」とたずねて来（き）ました。やがて二人（ふたり）は夫婦（ふうふ）になりました。
+（ナレーション）まずしい暮（く）らしを助（たす）けようと、妻（つま）は機（はた）を織（お）りはじめました。
+妻：「布（ぬの）を織（お）っている間（あいだ）は、けっして部屋（へや）をのぞかないでください」。
+（ナレーション）でき上（あ）がった布（ぬの）は、おどろくほど美（うつく）しく、高（たか）い値段（ねだん）で売（う）れました。けれど男（おとこ）は、どうしても中（なか）が気（き）になります。ある日（ひ）、約束（やくそく）を破（やぶ）ってそっとのぞくと――そこにいたのは、やせ細（ほそ）った鶴（つる）が、自分（じぶん）の羽根（はね）を一本（いっぽん）ずつ抜（ぬ）いて、布（ぬの）に織（お）り込（こ）んでいる姿（すがた）でした。あの日（ひ）助（たす）けた鶴（つる）の、恩返（おんがえ）しだったのです。
+妻：「姿（すがた）を見（み）られたからには、もう、ここにはいられません」。
+（ナレーション）妻（つま）は一羽（いちわ）の鶴（つる）にもどり、何度（なんど）も振（ふ）り返（かえ）りながら、雪空（ゆきぞら）へ飛（と）び去（さ）っていきました。</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>354</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>On a cold winter day, a man rescued a crane caught in a trap. That night, a beautiful woman visited his house and became his wife. She said, 'Please never look,' and wove cloth in a room. The cloth sold for a very high price. One day, when the man secretly peeked—there was the crane, plucking its own feathers to weave the cloth. Once her true form was known, the wife flew away into the sky.</t>
+          <t>On a cold, snowy day, a man found a crane suffering in a trap and gently set it free. That night, there was a knock at the door, and a beautiful woman came saying she had lost her way. In time the two became husband and wife. To help their poor life, the wife began to weave at the loom. 'While I weave the cloth, never look into the room.' The finished cloth was astonishingly beautiful and sold for a high price. But the man couldn't stop wondering what was inside. One day, breaking the promise, he quietly peeked—and there was a gaunt crane, plucking its own feathers one by one and weaving them into the cloth. It was the crane he had saved, repaying his kindness. 'Now that you have seen my true form, I can no longer stay here.' The wife turned back into a crane and, looking back again and again, flew away into the snowy sky.</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>〜を 助ける／けっして〜ないで／〜と …が ある</t>
+          <t>〜てやる／けっして〜ないで／〜からには</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>約束と恩返し。</t>
+          <t>恩返しと別れまで完結。</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>見てはいけない約束の結末。</t>
+          <t>見るなの約束。</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>1話者・朗読</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="135" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+          <t>多声TTS:ナレーター/妻</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="345" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>L-T-005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -3490,53 +3520,57 @@
           <t>昔話</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n"/>
+      <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="inlineStr">
         <is>
           <t>笠地蔵</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>年（とし）の くれ、まずしい おじいさんが、町（まち）へ 笠（かさ）を 売（う）りに 行（い）きました。でも、一（ひと）つも 売（う）れません。帰（かえ）り道（みち）、雪（ゆき）の 中（なか）に 立（た）つ 六（む）つの お地蔵（じぞう）さまを 見（み）つけました。『さむそうだ』と、おじいさんは 売（う）り物（もの）の 笠（かさ）を お地蔵（じぞう）さまに かぶせて あげました。一（ひと）つ 足（た）りないので、自分（じぶん）の 手（て）ぬぐいを かけました。その 夜（よる）、ふしぎな ことが おきました。朝（あさ）、戸（と）を 開（あ）けると、米（こめ）や もちが 山（やま）のように 置（お）いて あったのです。</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>173</v>
+          <t>（ナレーション）年（とし）の暮（く）れ、まずしいけれど心（こころ）のやさしいおじいさんが、お正月（しょうがつ）のもちを買（か）うお金（かね）にしようと、手作（てづく）りの笠（かさ）を町（まち）へ売（う）りに行（い）きました。けれど、笠（かさ）は一（ひと）つも売（う）れず、雪（ゆき）まで降（ふ）り出（だ）してしまいました。
+（ナレーション）すごすごと帰（かえ）る道（みち）、おじいさんは、雪（ゆき）の中（なか）に並（なら）んで立（た）つ六体（ろくたい）のお地蔵（じぞう）さまを見（み）つけました。頭（あたま）に雪（ゆき）を積（つ）もらせて、寒（さむ）そうにしています。
+おじいさん：「お地蔵（じぞう）さま、さぞ寒（さむ）かろう。これをどうぞ」。
+（ナレーション）おじいさんは、売（う）り物（もの）の笠（かさ）を一（ひと）つずつかぶせてあげました。けれど笠（かさ）は五（いつ）つしかなく、一（ひと）つ足（た）りません。そこで、自分（じぶん）がかぶっていた手（て）ぬぐいを取（と）って、最後（さいご）のお地蔵（じぞう）さまの頭（あたま）にかけてあげました。
+（ナレーション）その夜（よる）、ふしぎなことが起（お）こりました。明（あ）け方（がた）、外（そと）で重（おも）い物（もの）を置（お）くような音（おと）がします。戸（と）を開（あ）けると、米（こめ）やもち、おせちのごちそうが、山（やま）のように積（つ）まれていたのです。雪（ゆき）の上（うえ）には、六体（ろくたい）のお地蔵（じぞう）さまの足跡（あしあと）が残（のこ）っていました。親切（しんせつ）への、お礼（れい）だったのです。</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>381</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>At year's end, a poor old man went to town to sell straw hats. But not one sold. On the way home, he found six Jizo statues standing in the snow. 'They look cold,' he said, and placed the hats he had been selling on the statues. One was short, so he used his own hand towel. That night, something mysterious happened. In the morning, when he opened the door, rice and mochi were piled up like a mountain.</t>
+          <t>At year's end, a poor but kind-hearted old man went to town to sell handmade straw hats, hoping to buy mochi for New Year. But not one hat sold, and it even began to snow. Trudging home, the old man found six Jizo statues standing in a row in the snow, snow piling on their heads, looking cold. 'O Jizo, you must be very cold. Please take these.' He placed his hats on them one by one. But he had only five hats—one short. So he took off the hand towel he was wearing and put it on the last Jizo's head. That night, something mysterious happened. Toward dawn, there was a sound outside like heavy things being set down. When he opened the door, rice, mochi, and New Year feasts were piled like a mountain. In the snow remained the footprints of six Jizo. It was their thanks for his kindness.</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>〜そうだ／〜て あげる／〜のように</t>
+          <t>〜かろう／〜てあげる／〜のように</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>親切が返ってくる話。</t>
+          <t>親切が報われ完結。</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>心温まる年越しの奇跡。</t>
+          <t>小さな親切の奇跡。</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>1話者・朗読</t>
+          <t>多声TTS:ナレーター/おじいさん</t>
         </is>
       </c>
     </row>

--- a/長文.xlsx
+++ b/長文.xlsx
@@ -61,7 +61,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -71,6 +71,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -532,12 +535,12 @@
       </c>
     </row>
     <row r="2" ht="210" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>L-K-001</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -557,12 +560,12 @@
           <t>空港に着いた</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
@@ -579,7 +582,7 @@
 （ナレーション）スタンプを もらって、カイは 大（おお）きく 息（いき）を ついた。「やっと 来た…。これから 新（あたら）しい 毎日（まいにち）が 始（はじ）まるんだ」。</t>
         </is>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="5" t="n">
         <v>205</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -609,12 +612,12 @@
       </c>
     </row>
     <row r="3" ht="225" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>L-K-002</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -634,12 +637,12 @@
           <t>ゴミ出しでこまった</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -656,7 +659,7 @@
 （ナレーション）カイは ほっとした。「田中（たなか）さん、親切（しんせつ）だなあ。心強（こころづよ）いな」。</t>
         </is>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="5" t="n">
         <v>231</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -686,12 +689,12 @@
       </c>
     </row>
     <row r="4" ht="180" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>L-K-003</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -711,12 +714,12 @@
           <t>はじめての友だち（ミナ）</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -733,7 +736,7 @@
 （ナレーション）この 日（ひ）から、ミナは カイの いちばんの 友（とも）だちに なった。</t>
         </is>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="5" t="n">
         <v>180</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -763,12 +766,12 @@
       </c>
     </row>
     <row r="5" ht="195" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>L-K-004</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -788,12 +791,12 @@
           <t>バイトを始める</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -809,7 +812,7 @@
 （ナレーション）ケンタの 明（あか）るさに、カイの きんちょうは すっと ほどけた。「日本人（にほんじん）の 友（とも）だち、第一号（だいいちごう）だ」。</t>
         </is>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="5" t="n">
         <v>222</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -839,12 +842,12 @@
       </c>
     </row>
     <row r="6" ht="195" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>L-K-005</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -864,12 +867,12 @@
           <t>日本語学校の初日</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -885,7 +888,7 @@
 （ナレーション）さくら先生（せんせい）の ていねいな 日本語（にほんご）と、ミナの 笑顔（えがお）。カイの 新（あたら）しい 毎日（まいにち）は、ここから 始（はじ）まった。</t>
         </is>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" s="5" t="n">
         <v>194</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -1017,12 +1020,12 @@
       </c>
     </row>
     <row r="2" ht="210" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>L-J-001</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1042,12 +1045,12 @@
           <t>京都へ行く</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -1066,7 +1069,7 @@
 （ナレーション）わすれられない 一日（いちにち）に なった。</t>
         </is>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="5" t="n">
         <v>181</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -1096,12 +1099,12 @@
       </c>
     </row>
     <row r="3" ht="180" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>L-J-002</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1121,12 +1124,12 @@
           <t>お祭りに行く</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -1144,7 +1147,7 @@
 （ナレーション）大（おお）きな 音（おと）と 光（ひかり）。カイの 胸（むね）は どきどきしていた。</t>
         </is>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="5" t="n">
         <v>165</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -1276,12 +1279,12 @@
       </c>
     </row>
     <row r="2" ht="225" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>L-L-001</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1301,12 +1304,12 @@
           <t>はじめての美容院</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -1325,7 +1328,7 @@
 （ナレーション）少（すこ）し 短すぎたけれど、カイは なんだか うれしかった。</t>
         </is>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="5" t="n">
         <v>210</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -1457,12 +1460,12 @@
       </c>
     </row>
     <row r="2" ht="165" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>L-B-001</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1482,12 +1485,12 @@
           <t>好きな食べ物の話</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -1501,7 +1504,7 @@
 カイ：みなさんの 好（す）きな 日本（にほん）の 食べ物は 何（なん）ですか？ また 教（おし）えてね。じゃあ、また！</t>
         </is>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="5" t="n">
         <v>177</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -1633,12 +1636,12 @@
       </c>
     </row>
     <row r="2" ht="120" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>L-R-001</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1658,12 +1661,12 @@
           <t>桜が満開（国内）</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>ニュース</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -1673,7 +1676,7 @@
           <t>おはようございます。今朝（けさ）の ニュースです。昨日（きのう）、東京（とうきょう）の 公園（こうえん）で 桜（さくら）が 満開（まんかい）に なりました。週末（しゅうまつ）は たくさんの 家族（かぞく）連（づ）れで にぎわいそうです。天気（てんき）も よく、お花見（はなみ）に ぴったりの 一日（いちにち）に なるでしょう。一方（いっぽう）、来週（らいしゅう）からは 少（すこ）し 寒（さむ）く なるという 予報（よほう）も 出（で）ています。体調（たいちょう）に 気（き）を つけて お過（す）ごしください。では、今日（きょう）も よい 一日を。</t>
         </is>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="5" t="n">
         <v>142</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -1703,12 +1706,12 @@
       </c>
     </row>
     <row r="3" ht="105" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>L-R-002</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1728,12 +1731,12 @@
           <t>全国の天気（天気）</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>天気予報</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -1743,7 +1746,7 @@
           <t>全国（ぜんこく）の 天気（てんき）です。今日（きょう）は 西日本（にしにほん）で 晴（は）れますが、東日本（ひがしにほん）は 午後（ごご）から 雲（くも）が 多（おお）く なるでしょう。夜（よる）には 雨（あめ）が 降（ふ）る 所（ところ）も あります。傘（かさ）を 持（も）って 出（で）かけると 安心（あんしん）です。気温（きおん）は 各地（かくち）で 20度（ど）前後（ぜんご）、過（す）ごしやすい 一日（いちにち）に なりそうです。</t>
         </is>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="5" t="n">
         <v>97</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -1773,12 +1776,12 @@
       </c>
     </row>
     <row r="4" ht="105" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>L-R-003</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1798,12 +1801,12 @@
           <t>海外のニュース（国際）</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>ニュース</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -1813,7 +1816,7 @@
           <t>こんにちは、国際（こくさい）ニュースです。アメリカで、新（あたら）しい 技術（ぎじゅつ）の 会議（かいぎ）が 開（ひら）かれました。世界中（せかいじゅう）から たくさんの 研究者（けんきゅうしゃ）が 集（あつ）まりました。日本（にほん）からも 多（おお）くの 企業（きぎょう）が 参加（さんか）し、注目（ちゅうもく）を 集（あつ）めています。来年（らいねん）は アジアでも 同（おな）じ 会議が 開かれる 予定（よてい）です。</t>
         </is>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="5" t="n">
         <v>105</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -1843,12 +1846,12 @@
       </c>
     </row>
     <row r="5" ht="90" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>L-R-004</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1868,12 +1871,12 @@
           <t>サッカーの試合（スポーツ）</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>ニュース</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -1883,7 +1886,7 @@
           <t>スポーツの ニュースです。昨日（きのう）、サッカーの 試合（しあい）が ありました。日本（にほん）チームは 2対（たい）1で 勝（か）ちました。最後（さいご）の ゴールは、とても すばらしかったです。スタジアムの ファンは 大（おお）きな 声（こえ）で 応援（おうえん）しました。次（つぎ）の 試合は 来週（らいしゅう）の 土曜日（どようび）です。楽（たの）しみですね。</t>
         </is>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="5" t="n">
         <v>109</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -1913,12 +1916,12 @@
       </c>
     </row>
     <row r="6" ht="120" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>L-R-005</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1938,12 +1941,12 @@
           <t>勉強が続かない</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>トーク</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -1953,7 +1956,7 @@
           <t>こんばんは、パーソナリティの ユウキです。今日（きょう）も 一日（いちにち）お疲（つか）れさまでした。さて、リスナーの みなさんから お便（たよ）りを いただきました。「最近（さいきん）、日本語（にほんご）の 勉強（べんきょう）が 続（つづ）かなくて 困（こま）っています」。わかります〜。でも、大丈夫（だいじょうぶ）。毎日（まいにち）5分（ふん）でも いいんです。好（す）きな ドラマや 歌（うた）で 楽（たの）しく 続（つづ）けましょう。それでは、今夜（こんや）の 一曲（いっきょく）です。</t>
         </is>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" s="5" t="n">
         <v>142</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -1983,12 +1986,12 @@
       </c>
     </row>
     <row r="7" ht="90" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>L-R-006</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2008,12 +2011,12 @@
           <t>漢字が覚えられない</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>トーク</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -2023,7 +2026,7 @@
           <t>今日（きょう）の お便（たよ）りです。「漢字（かんじ）が なかなか 覚（おぼ）えられません」。わかります。漢字は 数（かず）が 多（おお）いですからね。おすすめは、毎日（まいにち）少（すこ）しずつ、生活（せいかつ）の 中（なか）で 見（み）た 漢字を 覚（おぼ）えることです。看板（かんばん）や メニューも いい 教材（きょうざい）ですよ。あせらず 続（つづ）けましょう。</t>
         </is>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="I7" s="5" t="n">
         <v>103</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -2053,12 +2056,12 @@
       </c>
     </row>
     <row r="8" ht="120" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>L-R-007</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2078,12 +2081,12 @@
           <t>ゲストのカイさん</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>対話</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -2099,7 +2102,7 @@
 司会：いいですね！ がんばってください。</t>
         </is>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I8" s="5" t="n">
         <v>142</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -2129,12 +2132,12 @@
       </c>
     </row>
     <row r="9" ht="135" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>L-R-008</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2154,12 +2157,12 @@
           <t>週末どうだった？</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>対話</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -2174,7 +2177,7 @@
 カイ：へえ、いいね！</t>
         </is>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I9" s="5" t="n">
         <v>122</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -2306,12 +2309,12 @@
       </c>
     </row>
     <row r="2" ht="150" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>L-M-001</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2327,12 +2330,12 @@
           <t>消えた駅弁の謎 第1話：駅で事件発生</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -2341,18 +2344,18 @@
         <is>
           <t>（ナレーション）東京駅（とうきょうえき）の 有名（ゆうめい）な 駅弁屋（えきべんや）で 事件（じけん）が 起（お）きた。
 店長（てんちょう）：たいへんだ！ 一番（いちばん）人気（にんき）の「うみの幸（さち）弁当（べんとう）」が、10個（こ）も 消（き）えてる！
-駅員（えきいん）の田中（たなか）：鍵（かぎ）は かかっていたんですよね？
+駅員（えきいん）の明智（あけち）：鍵（かぎ）は かかっていたんですよね？
 店長：はい、朝（あさ）まで しっかり…。
-田中：おかしいな。鍵（かぎ）が かかっていたのに、どうやって…？
-（ナレーション）田中（たなか）さんは 考（かんが）えた。これは ただの どろぼうでは ないかもしれない。</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="n">
+明智：おかしいな。鍵（かぎ）が かかっていたのに、どうやって…？
+（ナレーション）明智（あけち）さんは 考（かんが）えた。これは ただの どろぼうでは ないかもしれない。</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="n">
         <v>143</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>(Narration) An incident occurred at a famous ekiben shop in Tokyo Station. / Manager: This is terrible! Ten of our most popular 'Sea Bounty Bento' have vanished! / Tanaka (staff): The door was locked, right? / Manager: Yes, firmly until morning... / Tanaka: Strange. The door was locked, so how...? / (Narration) Tanaka thought. This might not be an ordinary thief.</t>
+          <t>(Narration) An incident occurred at a famous ekiben shop in Tokyo Station. / Manager: This is terrible! Ten of our most popular 'Sea Bounty Bento' have vanished! / Akechi (staff): The door was locked, right? / Manager: Yes, firmly until morning... / Akechi: Strange. The door was locked, so how...? / (Narration) Akechi thought. This might not be an ordinary thief.</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -2377,12 +2380,12 @@
       </c>
     </row>
     <row r="3" ht="165" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>L-M-002</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2398,33 +2401,33 @@
           <t>消えた駅弁の謎 第2話：証言を聞く</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>対話</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>田中（たなか）：すみません、今朝（けさ）、何（なに）か 見（み）ませんでしたか。
+          <t>明智（あけち）：すみません、今朝（けさ）、何（なに）か 見（み）ませんでしたか。
 掃除（そうじ）の人：5時（じ）ごろ、白（しろ）い 服（ふく）の 人（ひと）を 見（み）ましたよ。
-田中：白い 服…。ありがとうございます。
+明智：白い 服…。ありがとうございます。
 コーヒー店（てん）の人：そういえば、変（へん）な 音（おと）が しましたね。バサバサっと。
-田中：バサバサ？
+明智：バサバサ？
 （ナレーション）でも、防犯（ぼうはん）カメラには だれも 映（うつ）っていない。
-田中：（首（くび）を かしげて）うーん、おかしいなあ…。</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="n">
+明智：（首（くび）を かしげて）うーん、おかしいなあ…。</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n">
         <v>144</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Tanaka: Excuse me, did you see anything this morning? / Cleaner: Around 5, I saw someone in white clothes. / Tanaka: White clothes... Thank you. / Coffee-shop worker: Come to think of it, there was a strange sound. A flapping sound. / Tanaka: Flapping? / (Narration) But the security camera showed no one. / Tanaka: (tilting his head) Hmm, that's strange...</t>
+          <t>Akechi: Excuse me, did you see anything this morning? / Cleaner: Around 5, I saw someone in white clothes. / Akechi: White clothes... Thank you. / Coffee-shop worker: Come to think of it, there was a strange sound. A flapping sound. / Akechi: Flapping? / (Narration) But the security camera showed no one. / Akechi: (tilting his head) Hmm, that's strange...</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -2449,12 +2452,12 @@
       </c>
     </row>
     <row r="4" ht="135" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>L-M-003</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2470,32 +2473,32 @@
           <t>消えた駅弁の謎 第3話：容疑者登場</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>対話</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>（ナレーション）次（つぎ）の 日（ひ）、田中（たなか）さんは 白（しろ）い 服（ふく）の 男（おとこ）を 見（み）つけた。駅（えき）の 清掃員（せいそういん）だ。
-田中：あの 朝（あさ）、何（なに）を していましたか。
+          <t>（ナレーション）次（つぎ）の 日（ひ）、明智（あけち）さんは 白（しろ）い 服（ふく）の 男（おとこ）を 見（み）つけた。駅（えき）の 清掃員（せいそういん）だ。
+明智：あの 朝（あさ）、何（なに）を していましたか。
 清掃員：私（わたし）は ただ、ゴミを 集（あつ）めていただけですよ。
 （ナレーション）そのとき、男（おとこ）の カバンから 弁当（べんとう）の 包（つつ）み紙（がみ）が ひらり、と 落（お）ちた。
-田中：（目（め）を 光（ひか）らせて）…これは？
+明智：（目（め）を 光（ひか）らせて）…これは？
 清掃員：えっ、いや、これは…！</t>
         </is>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="5" t="n">
         <v>124</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>(Narration) The next day, Tanaka found the man in white—a station cleaner. / Tanaka: What were you doing that morning? / Cleaner: I was just collecting trash. / (Narration) Just then, a bento wrapper fluttered out of the man's bag. / Tanaka: (eyes flashing) ...What's this? / Cleaner: Huh, no, this is...!</t>
+          <t>(Narration) The next day, Akechi found the man in white—a station cleaner. / Akechi: What were you doing that morning? / Cleaner: I was just collecting trash. / (Narration) Just then, a bento wrapper fluttered out of the man's bag. / Akechi: (eyes flashing) ...What's this? / Cleaner: Huh, no, this is...!</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -2520,12 +2523,12 @@
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>L-M-004</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2541,12 +2544,12 @@
           <t>消えた駅弁の謎 第4話：真犯人は？</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -2554,19 +2557,19 @@
       <c r="H5" s="3" t="inlineStr">
         <is>
           <t>清掃員：それは、私（わたし）が 拾（ひろ）った ゴミです。本当（ほんとう）です！
-（ナレーション）田中（たなか）さんは 防犯（ぼうはん）カメラを もう一度（いちど）見（み）た。すると、屋根（やね）の すきまから…
-田中：あっ！ 見（み）て ください。大（おお）きな カラスが、弁当（べんとう）を 運（はこ）んでる！
+（ナレーション）明智（あけち）さんは 防犯（ぼうはん）カメラを もう一度（いちど）見（み）た。すると、屋根（やね）の すきまから…
+明智：あっ！ 見（み）て ください。大（おお）きな カラスが、弁当（べんとう）を 運（はこ）んでる！
 店長：えーっ！ 犯人（はんにん）は カラス だったの！？
 （ナレーション）みんな 大笑（おおわら）い。鍵（かぎ）の 謎（なぞ）は、屋根（やね）の 小（ちい）さな 窓（まど）だったのだ。
-田中：はは、事件（じけん）は 無事（ぶじ）解決（かいけつ）、ですね。</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="n">
+明智：はは、事件（じけん）は 無事（ぶじ）解決（かいけつ）、ですね。</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n">
         <v>145</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Cleaner: That's trash I picked up. It's true! / (Narration) Tanaka watched the security camera again. Then, through a gap in the roof... / Tanaka: Ah! Look! A big crow is carrying the bento! / Manager: Whaaat! The culprit was a crow?! / (Narration) Everyone burst out laughing. The mystery of the lock was a small window in the roof. / Tanaka: Haha, case closed.</t>
+          <t>Cleaner: That's trash I picked up. It's true! / (Narration) Akechi watched the security camera again. Then, through a gap in the roof... / Akechi: Ah! Look! A big crow is carrying the bento! / Manager: Whaaat! The culprit was a crow?! / (Narration) Everyone burst out laughing. The mystery of the lock was a small window in the roof. / Akechi: Haha, case closed.</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -2591,12 +2594,12 @@
       </c>
     </row>
     <row r="6" ht="165" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>L-M-005</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2612,12 +2615,12 @@
           <t>消えた最終電車</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -2632,7 +2635,7 @@
 （つづく）</t>
         </is>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" s="5" t="n">
         <v>154</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -2764,12 +2767,12 @@
       </c>
     </row>
     <row r="2" ht="420" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>L-D-001</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2785,12 +2788,12 @@
           <t>カップラーメンの誕生</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -2807,7 +2810,7 @@
 （ナレーション）こうして一杯（いっぱい）のインスタントラーメンが生（う）まれた。さらに安藤（あんどう）は、世界（せかい）へ届（とど）けるため、器（うつわ）ごと食（た）べられる「カップ」を発明（はつめい）する。発売（はつばい）の日（ひ）、半信半疑（はんしんはんぎ）だった人々（ひとびと）は、湯（ゆ）を注（そそ）いで三分（さんぷん）、ふたを開（あ）けて笑顔（えがお）になった。一人（ひとり）の執念（しゅうねん）が、世界（せかい）の食卓（しょくたく）を永遠（えいえん）に変（か）えたのである。</t>
         </is>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="5" t="n">
         <v>537</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -2837,12 +2840,12 @@
       </c>
     </row>
     <row r="3" ht="420" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>L-D-002</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2858,12 +2861,12 @@
           <t>新幹線――夢の超特急</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -2879,7 +2882,7 @@
 （ナレーション）かつて長（なが）い時間（じかん）がかかった東京（とうきょう）と大阪（おおさか）の間（あいだ）が、ぐっと近（ちか）くなった。仕事（しごと）でも旅行（りょこう）でも、日帰（ひがえ）りができる。新幹線（しんかんせん）は、人（ひと）と人（ひと）、町（まち）と町（まち）の距離（きょり）を、大（おお）きく縮（ちぢ）めたのだ。今（いま）も世界中（せかいじゅう）の高速鉄道（こうそくてつどう）が、この一本（いっぽん）の線路（せんろ）を手本（てほん）にし続（つづ）けている。</t>
         </is>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="5" t="n">
         <v>491</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -2909,12 +2912,12 @@
       </c>
     </row>
     <row r="4" ht="420" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>L-D-003</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2930,12 +2933,12 @@
           <t>ライト兄弟、空へ</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -2951,7 +2954,7 @@
 （ナレーション）成功（せいこう）の裏（うら）には、何年（なんねん）もの地道（じみち）な努力（どりょく）があった。二人（ふたり）は、失敗（しっぱい）の記録（きろく）を一（ひと）つ残（のこ）らずノートに書（か）きとめ、つぎの工夫（くふう）に生（い）かしていったのだ。だれもが笑（わら）った夢（ゆめ）を、あきらめなかった二人（ふたり）。その小（ちい）さな12秒（びょう）から、世界中（せかいじゅう）の空（そら）の旅（たび）が始（はじ）まったのである。</t>
         </is>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="5" t="n">
         <v>473</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -2981,12 +2984,12 @@
       </c>
     </row>
     <row r="5" ht="420" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>L-D-004</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -3002,12 +3005,12 @@
           <t>エジソンと電球</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -3023,7 +3026,7 @@
 （ナレーション）「天才（てんさい）とは、1パーセントのひらめきと、99パーセントの努力（どりょく）である」。失敗（しっぱい）を恐（おそ）れず、努力（どりょく）を続（つづ）けたエジソンの言葉（ことば）は、今（いま）も世界中（せかいじゅう）の人（ひと）の胸（むね）に生（い）きている。</t>
         </is>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="5" t="n">
         <v>479</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -3053,12 +3056,12 @@
       </c>
     </row>
     <row r="6" ht="420" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>L-D-005</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -3074,12 +3077,12 @@
           <t>ヘレン・ケラーと先生</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -3095,7 +3098,7 @@
 （ナレーション）後（のち）にヘレンは、世界中（せかいじゅう）を旅（たび）して講演（こうえん）し、目（め）や耳（みみ）の不自由（ふじゆう）な人々（ひとびと）のために力（ちから）をつくした。「世界（せかい）は苦（くる）しみに満（み）ちているが、それを乗（の）りこえる力（ちから）にも満（み）ちている」。サリバン先生（せんせい）とヘレンの物語（ものがたり）は、同（おな）じ苦（くる）しみを持（も）つ世界中（せかいじゅう）の人々（ひとびと）に、今（いま）も希望（きぼう）を与（あた）え続（つづ）けている。</t>
         </is>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" s="5" t="n">
         <v>508</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -3227,12 +3230,12 @@
       </c>
     </row>
     <row r="2" ht="300" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>L-T-001</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -3248,12 +3251,12 @@
           <t>桃太郎</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -3266,7 +3269,7 @@
 （ナレーション）道（みち）の途中（とちゅう）で、犬（いぬ）、猿（さる）、きじが仲間（なかま）になりました。鬼（おに）ヶ島（しま）に着（つ）くと、おそろしい鬼（おに）たちが暴（あば）れています。桃太郎（ももたろう）たちは力（ちから）を合（あ）わせて勇敢（ゆうかん）に戦（たたか）い、ついに鬼（おに）を降参（こうさん）させました。鬼（おに）は奪（うば）った宝物（たからもの）を返（かえ）し、二度（にど）と悪（わる）いことをしないと約束（やくそく）しました。桃太郎（ももたろう）は宝物（たからもの）を持（も）ち帰（かえ）り、村（むら）のみんなと幸（しあわ）せに暮（く）らしました。</t>
         </is>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="5" t="n">
         <v>303</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -3296,12 +3299,12 @@
       </c>
     </row>
     <row r="3" ht="315" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>L-T-002</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -3317,12 +3320,12 @@
           <t>浦島太郎</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -3335,7 +3338,7 @@
 （ナレーション）夢（ゆめ）のような日々（ひび）。けれど村（むら）が恋（こい）しくなった太郎（たろう）は、玉手箱（たまてばこ）を持（も）って帰（かえ）りました。ところが、村（むら）はすっかり変（か）わり、知（し）っている人（ひと）は一人（ひとり）もいません。竜宮城（りゅうぐうじょう）での数日（すうじつ）の間（あいだ）に、地上（ちじょう）では何百年（なんびゃくねん）も過（す）ぎていたのです。さびしさのあまり、太郎（たろう）が約束（やくそく）を忘（わす）れて箱（はこ）を開（あ）けると、白（しろ）い煙（けむり）がもくもくと出（で）て、太郎（たろう）はたちまち白髪（しらが）のおじいさんになってしまいました。</t>
         </is>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="5" t="n">
         <v>351</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -3365,12 +3368,12 @@
       </c>
     </row>
     <row r="4" ht="300" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>L-T-003</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -3386,12 +3389,12 @@
           <t>かぐや姫</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -3404,7 +3407,7 @@
 （ナレーション）実（じつ）は、かぐや姫（ひめ）は月（つき）の世界（せかい）から来（き）た人（ひと）でした。満月（まんげつ）の夜（よる）、空（そら）から大勢（おおぜい）の使（つか）いが、光（ひかり）とともに姫（ひめ）を迎（むか）えに来（き）ました。おじいさんとおばあさんは泣（な）いて引（ひ）き止（と）めましたが、別（わか）れの時（とき）は来（き）てしまいます。姫（ひめ）は二人（ふたり）に深（ふか）く感謝（かんしゃ）し、別（わか）れを惜（お）しみながら、静（しず）かに天（てん）へのぼっていきました。</t>
         </is>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="5" t="n">
         <v>329</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -3434,12 +3437,12 @@
       </c>
     </row>
     <row r="5" ht="345" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>L-T-004</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -3455,12 +3458,12 @@
           <t>鶴の恩返し</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -3475,7 +3478,7 @@
 （ナレーション）妻（つま）は一羽（いちわ）の鶴（つる）にもどり、何度（なんど）も振（ふ）り返（かえ）りながら、雪空（ゆきぞら）へ飛（と）び去（さ）っていきました。</t>
         </is>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="5" t="n">
         <v>354</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -3505,12 +3508,12 @@
       </c>
     </row>
     <row r="6" ht="345" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>L-T-005</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -3526,12 +3529,12 @@
           <t>笠地蔵</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -3545,7 +3548,7 @@
 （ナレーション）その夜（よる）、ふしぎなことが起（お）こりました。明（あ）け方（がた）、外（そと）で重（おも）い物（もの）を置（お）くような音（おと）がします。戸（と）を開（あ）けると、米（こめ）やもち、おせちのごちそうが、山（やま）のように積（つ）まれていたのです。雪（ゆき）の上（うえ）には、六体（ろくたい）のお地蔵（じぞう）さまの足跡（あしあと）が残（のこ）っていました。親切（しんせつ）への、お礼（れい）だったのです。</t>
         </is>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" s="5" t="n">
         <v>381</v>
       </c>
       <c r="J6" s="3" t="inlineStr">

--- a/長文.xlsx
+++ b/長文.xlsx
@@ -61,7 +61,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -71,6 +71,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -535,12 +541,12 @@
       </c>
     </row>
     <row r="2" ht="210" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>L-K-001</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -560,12 +566,12 @@
           <t>空港に着いた</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
@@ -582,7 +588,7 @@
 （ナレーション）スタンプを もらって、カイは 大（おお）きく 息（いき）を ついた。「やっと 来た…。これから 新（あたら）しい 毎日（まいにち）が 始（はじ）まるんだ」。</t>
         </is>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="7" t="n">
         <v>205</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -612,12 +618,12 @@
       </c>
     </row>
     <row r="3" ht="225" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>L-K-002</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -637,12 +643,12 @@
           <t>ゴミ出しでこまった</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -659,7 +665,7 @@
 （ナレーション）カイは ほっとした。「田中（たなか）さん、親切（しんせつ）だなあ。心強（こころづよ）いな」。</t>
         </is>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I3" s="7" t="n">
         <v>231</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -689,12 +695,12 @@
       </c>
     </row>
     <row r="4" ht="180" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>L-K-003</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -714,12 +720,12 @@
           <t>はじめての友だち（ミナ）</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -736,7 +742,7 @@
 （ナレーション）この 日（ひ）から、ミナは カイの いちばんの 友（とも）だちに なった。</t>
         </is>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I4" s="7" t="n">
         <v>180</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -766,12 +772,12 @@
       </c>
     </row>
     <row r="5" ht="195" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>L-K-004</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -791,12 +797,12 @@
           <t>バイトを始める</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -812,7 +818,7 @@
 （ナレーション）ケンタの 明（あか）るさに、カイの きんちょうは すっと ほどけた。「日本人（にほんじん）の 友（とも）だち、第一号（だいいちごう）だ」。</t>
         </is>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="7" t="n">
         <v>222</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -842,12 +848,12 @@
       </c>
     </row>
     <row r="6" ht="195" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>L-K-005</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -867,12 +873,12 @@
           <t>日本語学校の初日</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -888,7 +894,7 @@
 （ナレーション）さくら先生（せんせい）の ていねいな 日本語（にほんご）と、ミナの 笑顔（えがお）。カイの 新（あたら）しい 毎日（まいにち）は、ここから 始（はじ）まった。</t>
         </is>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I6" s="7" t="n">
         <v>194</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -1020,12 +1026,12 @@
       </c>
     </row>
     <row r="2" ht="210" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>L-J-001</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1045,12 +1051,12 @@
           <t>京都へ行く</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -1069,7 +1075,7 @@
 （ナレーション）わすれられない 一日（いちにち）に なった。</t>
         </is>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="7" t="n">
         <v>181</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -1099,12 +1105,12 @@
       </c>
     </row>
     <row r="3" ht="180" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>L-J-002</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1124,12 +1130,12 @@
           <t>お祭りに行く</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -1147,7 +1153,7 @@
 （ナレーション）大（おお）きな 音（おと）と 光（ひかり）。カイの 胸（むね）は どきどきしていた。</t>
         </is>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I3" s="7" t="n">
         <v>165</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -1279,12 +1285,12 @@
       </c>
     </row>
     <row r="2" ht="225" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>L-L-001</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1304,12 +1310,12 @@
           <t>はじめての美容院</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -1328,7 +1334,7 @@
 （ナレーション）少（すこ）し 短すぎたけれど、カイは なんだか うれしかった。</t>
         </is>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="7" t="n">
         <v>210</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -1460,12 +1466,12 @@
       </c>
     </row>
     <row r="2" ht="165" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>L-B-001</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1485,12 +1491,12 @@
           <t>好きな食べ物の話</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -1504,7 +1510,7 @@
 カイ：みなさんの 好（す）きな 日本（にほん）の 食べ物は 何（なん）ですか？ また 教（おし）えてね。じゃあ、また！</t>
         </is>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="7" t="n">
         <v>177</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -1636,12 +1642,12 @@
       </c>
     </row>
     <row r="2" ht="120" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>L-R-001</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1661,12 +1667,12 @@
           <t>桜が満開（国内）</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>ニュース</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -1676,7 +1682,7 @@
           <t>おはようございます。今朝（けさ）の ニュースです。昨日（きのう）、東京（とうきょう）の 公園（こうえん）で 桜（さくら）が 満開（まんかい）に なりました。週末（しゅうまつ）は たくさんの 家族（かぞく）連（づ）れで にぎわいそうです。天気（てんき）も よく、お花見（はなみ）に ぴったりの 一日（いちにち）に なるでしょう。一方（いっぽう）、来週（らいしゅう）からは 少（すこ）し 寒（さむ）く なるという 予報（よほう）も 出（で）ています。体調（たいちょう）に 気（き）を つけて お過（す）ごしください。では、今日（きょう）も よい 一日を。</t>
         </is>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="7" t="n">
         <v>142</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -1706,12 +1712,12 @@
       </c>
     </row>
     <row r="3" ht="105" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>L-R-002</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1731,12 +1737,12 @@
           <t>全国の天気（天気）</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>天気予報</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -1746,7 +1752,7 @@
           <t>全国（ぜんこく）の 天気（てんき）です。今日（きょう）は 西日本（にしにほん）で 晴（は）れますが、東日本（ひがしにほん）は 午後（ごご）から 雲（くも）が 多（おお）く なるでしょう。夜（よる）には 雨（あめ）が 降（ふ）る 所（ところ）も あります。傘（かさ）を 持（も）って 出（で）かけると 安心（あんしん）です。気温（きおん）は 各地（かくち）で 20度（ど）前後（ぜんご）、過（す）ごしやすい 一日（いちにち）に なりそうです。</t>
         </is>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I3" s="7" t="n">
         <v>97</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -1776,12 +1782,12 @@
       </c>
     </row>
     <row r="4" ht="105" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>L-R-003</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1801,12 +1807,12 @@
           <t>海外のニュース（国際）</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>ニュース</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -1816,7 +1822,7 @@
           <t>こんにちは、国際（こくさい）ニュースです。アメリカで、新（あたら）しい 技術（ぎじゅつ）の 会議（かいぎ）が 開（ひら）かれました。世界中（せかいじゅう）から たくさんの 研究者（けんきゅうしゃ）が 集（あつ）まりました。日本（にほん）からも 多（おお）くの 企業（きぎょう）が 参加（さんか）し、注目（ちゅうもく）を 集（あつ）めています。来年（らいねん）は アジアでも 同（おな）じ 会議が 開かれる 予定（よてい）です。</t>
         </is>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I4" s="7" t="n">
         <v>105</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -1846,12 +1852,12 @@
       </c>
     </row>
     <row r="5" ht="90" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>L-R-004</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1871,12 +1877,12 @@
           <t>サッカーの試合（スポーツ）</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>ニュース</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -1886,7 +1892,7 @@
           <t>スポーツの ニュースです。昨日（きのう）、サッカーの 試合（しあい）が ありました。日本（にほん）チームは 2対（たい）1で 勝（か）ちました。最後（さいご）の ゴールは、とても すばらしかったです。スタジアムの ファンは 大（おお）きな 声（こえ）で 応援（おうえん）しました。次（つぎ）の 試合は 来週（らいしゅう）の 土曜日（どようび）です。楽（たの）しみですね。</t>
         </is>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="7" t="n">
         <v>109</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -1916,12 +1922,12 @@
       </c>
     </row>
     <row r="6" ht="120" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>L-R-005</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1941,12 +1947,12 @@
           <t>勉強が続かない</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>トーク</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -1956,7 +1962,7 @@
           <t>こんばんは、パーソナリティの ユウキです。今日（きょう）も 一日（いちにち）お疲（つか）れさまでした。さて、リスナーの みなさんから お便（たよ）りを いただきました。「最近（さいきん）、日本語（にほんご）の 勉強（べんきょう）が 続（つづ）かなくて 困（こま）っています」。わかります〜。でも、大丈夫（だいじょうぶ）。毎日（まいにち）5分（ふん）でも いいんです。好（す）きな ドラマや 歌（うた）で 楽（たの）しく 続（つづ）けましょう。それでは、今夜（こんや）の 一曲（いっきょく）です。</t>
         </is>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I6" s="7" t="n">
         <v>142</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -1986,12 +1992,12 @@
       </c>
     </row>
     <row r="7" ht="90" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>L-R-006</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2011,12 +2017,12 @@
           <t>漢字が覚えられない</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>トーク</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -2026,7 +2032,7 @@
           <t>今日（きょう）の お便（たよ）りです。「漢字（かんじ）が なかなか 覚（おぼ）えられません」。わかります。漢字は 数（かず）が 多（おお）いですからね。おすすめは、毎日（まいにち）少（すこ）しずつ、生活（せいかつ）の 中（なか）で 見（み）た 漢字を 覚（おぼ）えることです。看板（かんばん）や メニューも いい 教材（きょうざい）ですよ。あせらず 続（つづ）けましょう。</t>
         </is>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I7" s="7" t="n">
         <v>103</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -2056,12 +2062,12 @@
       </c>
     </row>
     <row r="8" ht="120" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>L-R-007</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2081,12 +2087,12 @@
           <t>ゲストのカイさん</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>対話</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -2102,7 +2108,7 @@
 司会：いいですね！ がんばってください。</t>
         </is>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="I8" s="7" t="n">
         <v>142</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -2132,12 +2138,12 @@
       </c>
     </row>
     <row r="9" ht="135" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>L-R-008</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2157,12 +2163,12 @@
           <t>週末どうだった？</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>対話</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -2177,7 +2183,7 @@
 カイ：へえ、いいね！</t>
         </is>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I9" s="7" t="n">
         <v>122</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -2309,12 +2315,12 @@
       </c>
     </row>
     <row r="2" ht="150" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>L-M-001</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2330,12 +2336,12 @@
           <t>消えた駅弁の謎 第1話：駅で事件発生</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -2350,7 +2356,7 @@
 （ナレーション）明智（あけち）さんは 考（かんが）えた。これは ただの どろぼうでは ないかもしれない。</t>
         </is>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="7" t="n">
         <v>143</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -2380,12 +2386,12 @@
       </c>
     </row>
     <row r="3" ht="165" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>L-M-002</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2401,12 +2407,12 @@
           <t>消えた駅弁の謎 第2話：証言を聞く</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>対話</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -2422,7 +2428,7 @@
 明智：（首（くび）を かしげて）うーん、おかしいなあ…。</t>
         </is>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I3" s="7" t="n">
         <v>144</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -2452,12 +2458,12 @@
       </c>
     </row>
     <row r="4" ht="135" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>L-M-003</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2473,12 +2479,12 @@
           <t>消えた駅弁の謎 第3話：容疑者登場</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>対話</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -2493,7 +2499,7 @@
 清掃員：えっ、いや、これは…！</t>
         </is>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I4" s="7" t="n">
         <v>124</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -2523,12 +2529,12 @@
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>L-M-004</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2544,12 +2550,12 @@
           <t>消えた駅弁の謎 第4話：真犯人は？</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -2564,7 +2570,7 @@
 明智：はは、事件（じけん）は 無事（ぶじ）解決（かいけつ）、ですね。</t>
         </is>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="7" t="n">
         <v>145</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -2594,12 +2600,12 @@
       </c>
     </row>
     <row r="6" ht="165" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>L-M-005</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2615,12 +2621,12 @@
           <t>消えた最終電車</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -2635,7 +2641,7 @@
 （つづく）</t>
         </is>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I6" s="7" t="n">
         <v>154</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -2767,12 +2773,12 @@
       </c>
     </row>
     <row r="2" ht="420" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>L-D-001</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2788,12 +2794,12 @@
           <t>カップラーメンの誕生</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -2810,7 +2816,7 @@
 （ナレーション）こうして一杯（いっぱい）のインスタントラーメンが生（う）まれた。さらに安藤（あんどう）は、世界（せかい）へ届（とど）けるため、器（うつわ）ごと食（た）べられる「カップ」を発明（はつめい）する。発売（はつばい）の日（ひ）、半信半疑（はんしんはんぎ）だった人々（ひとびと）は、湯（ゆ）を注（そそ）いで三分（さんぷん）、ふたを開（あ）けて笑顔（えがお）になった。一人（ひとり）の執念（しゅうねん）が、世界（せかい）の食卓（しょくたく）を永遠（えいえん）に変（か）えたのである。</t>
         </is>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="7" t="n">
         <v>537</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -2840,12 +2846,12 @@
       </c>
     </row>
     <row r="3" ht="420" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>L-D-002</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2861,12 +2867,12 @@
           <t>新幹線――夢の超特急</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -2882,7 +2888,7 @@
 （ナレーション）かつて長（なが）い時間（じかん）がかかった東京（とうきょう）と大阪（おおさか）の間（あいだ）が、ぐっと近（ちか）くなった。仕事（しごと）でも旅行（りょこう）でも、日帰（ひがえ）りができる。新幹線（しんかんせん）は、人（ひと）と人（ひと）、町（まち）と町（まち）の距離（きょり）を、大（おお）きく縮（ちぢ）めたのだ。今（いま）も世界中（せかいじゅう）の高速鉄道（こうそくてつどう）が、この一本（いっぽん）の線路（せんろ）を手本（てほん）にし続（つづ）けている。</t>
         </is>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I3" s="7" t="n">
         <v>491</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -2912,12 +2918,12 @@
       </c>
     </row>
     <row r="4" ht="420" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>L-D-003</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -2933,12 +2939,12 @@
           <t>ライト兄弟、空へ</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -2954,7 +2960,7 @@
 （ナレーション）成功（せいこう）の裏（うら）には、何年（なんねん）もの地道（じみち）な努力（どりょく）があった。二人（ふたり）は、失敗（しっぱい）の記録（きろく）を一（ひと）つ残（のこ）らずノートに書（か）きとめ、つぎの工夫（くふう）に生（い）かしていったのだ。だれもが笑（わら）った夢（ゆめ）を、あきらめなかった二人（ふたり）。その小（ちい）さな12秒（びょう）から、世界中（せかいじゅう）の空（そら）の旅（たび）が始（はじ）まったのである。</t>
         </is>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I4" s="7" t="n">
         <v>473</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -2984,12 +2990,12 @@
       </c>
     </row>
     <row r="5" ht="420" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>L-D-004</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -3005,12 +3011,12 @@
           <t>エジソンと電球</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -3026,7 +3032,7 @@
 （ナレーション）「天才（てんさい）とは、1パーセントのひらめきと、99パーセントの努力（どりょく）である」。失敗（しっぱい）を恐（おそ）れず、努力（どりょく）を続（つづ）けたエジソンの言葉（ことば）は、今（いま）も世界中（せかいじゅう）の人（ひと）の胸（むね）に生（い）きている。</t>
         </is>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="7" t="n">
         <v>479</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -3056,12 +3062,12 @@
       </c>
     </row>
     <row r="6" ht="420" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>L-D-005</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -3077,12 +3083,12 @@
           <t>ヘレン・ケラーと先生</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -3098,7 +3104,7 @@
 （ナレーション）後（のち）にヘレンは、世界中（せかいじゅう）を旅（たび）して講演（こうえん）し、目（め）や耳（みみ）の不自由（ふじゆう）な人々（ひとびと）のために力（ちから）をつくした。「世界（せかい）は苦（くる）しみに満（み）ちているが、それを乗（の）りこえる力（ちから）にも満（み）ちている」。サリバン先生（せんせい）とヘレンの物語（ものがたり）は、同（おな）じ苦（くる）しみを持（も）つ世界中（せかいじゅう）の人々（ひとびと）に、今（いま）も希望（きぼう）を与（あた）え続（つづ）けている。</t>
         </is>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I6" s="7" t="n">
         <v>508</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -3230,12 +3236,12 @@
       </c>
     </row>
     <row r="2" ht="300" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>L-T-001</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -3251,12 +3257,12 @@
           <t>桃太郎</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -3269,7 +3275,7 @@
 （ナレーション）道（みち）の途中（とちゅう）で、犬（いぬ）、猿（さる）、きじが仲間（なかま）になりました。鬼（おに）ヶ島（しま）に着（つ）くと、おそろしい鬼（おに）たちが暴（あば）れています。桃太郎（ももたろう）たちは力（ちから）を合（あ）わせて勇敢（ゆうかん）に戦（たたか）い、ついに鬼（おに）を降参（こうさん）させました。鬼（おに）は奪（うば）った宝物（たからもの）を返（かえ）し、二度（にど）と悪（わる）いことをしないと約束（やくそく）しました。桃太郎（ももたろう）は宝物（たからもの）を持（も）ち帰（かえ）り、村（むら）のみんなと幸（しあわ）せに暮（く）らしました。</t>
         </is>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="7" t="n">
         <v>303</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -3299,12 +3305,12 @@
       </c>
     </row>
     <row r="3" ht="315" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>L-T-002</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -3320,12 +3326,12 @@
           <t>浦島太郎</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -3338,7 +3344,7 @@
 （ナレーション）夢（ゆめ）のような日々（ひび）。けれど村（むら）が恋（こい）しくなった太郎（たろう）は、玉手箱（たまてばこ）を持（も）って帰（かえ）りました。ところが、村（むら）はすっかり変（か）わり、知（し）っている人（ひと）は一人（ひとり）もいません。竜宮城（りゅうぐうじょう）での数日（すうじつ）の間（あいだ）に、地上（ちじょう）では何百年（なんびゃくねん）も過（す）ぎていたのです。さびしさのあまり、太郎（たろう）が約束（やくそく）を忘（わす）れて箱（はこ）を開（あ）けると、白（しろ）い煙（けむり）がもくもくと出（で）て、太郎（たろう）はたちまち白髪（しらが）のおじいさんになってしまいました。</t>
         </is>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I3" s="7" t="n">
         <v>351</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -3368,12 +3374,12 @@
       </c>
     </row>
     <row r="4" ht="300" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>L-T-003</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -3389,12 +3395,12 @@
           <t>かぐや姫</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -3407,7 +3413,7 @@
 （ナレーション）実（じつ）は、かぐや姫（ひめ）は月（つき）の世界（せかい）から来（き）た人（ひと）でした。満月（まんげつ）の夜（よる）、空（そら）から大勢（おおぜい）の使（つか）いが、光（ひかり）とともに姫（ひめ）を迎（むか）えに来（き）ました。おじいさんとおばあさんは泣（な）いて引（ひ）き止（と）めましたが、別（わか）れの時（とき）は来（き）てしまいます。姫（ひめ）は二人（ふたり）に深（ふか）く感謝（かんしゃ）し、別（わか）れを惜（お）しみながら、静（しず）かに天（てん）へのぼっていきました。</t>
         </is>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I4" s="7" t="n">
         <v>329</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -3437,12 +3443,12 @@
       </c>
     </row>
     <row r="5" ht="345" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>L-T-004</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -3458,12 +3464,12 @@
           <t>鶴の恩返し</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -3478,7 +3484,7 @@
 （ナレーション）妻（つま）は一羽（いちわ）の鶴（つる）にもどり、何度（なんど）も振（ふ）り返（かえ）りながら、雪空（ゆきぞら）へ飛（と）び去（さ）っていきました。</t>
         </is>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="7" t="n">
         <v>354</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -3508,12 +3514,12 @@
       </c>
     </row>
     <row r="6" ht="345" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>L-T-005</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -3529,12 +3535,12 @@
           <t>笠地蔵</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -3548,7 +3554,7 @@
 （ナレーション）その夜（よる）、ふしぎなことが起（お）こりました。明（あ）け方（がた）、外（そと）で重（おも）い物（もの）を置（お）くような音（おと）がします。戸（と）を開（あ）けると、米（こめ）やもち、おせちのごちそうが、山（やま）のように積（つ）まれていたのです。雪（ゆき）の上（うえ）には、六体（ろくたい）のお地蔵（じぞう）さまの足跡（あしあと）が残（のこ）っていました。親切（しんせつ）への、お礼（れい）だったのです。</t>
         </is>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I6" s="7" t="n">
         <v>381</v>
       </c>
       <c r="J6" s="3" t="inlineStr">

--- a/長文.xlsx
+++ b/長文.xlsx
@@ -2,22 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="39300" yWindow="345" windowWidth="27960" windowHeight="14955" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日本生活スタート" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日本一人旅" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="カイの日常" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="カイの休憩室" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラジオトーク" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="まとめ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日本生活スタート" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日本一人旅" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="カイの日常" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="カイの休憩室" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ミステリー" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ドキュメンタリー" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="昔話" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ニュース" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="お便り相談室" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ゲストインタビュー" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2人のフリートーク" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -33,7 +36,10 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -45,16 +51,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
+        <fgColor rgb="FFFCE4EC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -72,21 +93,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -449,8 +470,911 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="19" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="12.109375" bestFit="1" customWidth="1" min="3" max="4"/>
+    <col width="14.44140625" bestFit="1" customWidth="1" min="5" max="6"/>
+    <col width="14.44140625" customWidth="1" min="7" max="9"/>
+    <col width="17.21875" bestFit="1" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>日本生活スタート</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>日本一人旅</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>カイの日常</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>カイの休憩室</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>ラジオトーク</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>ニュース</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>お便り相談室</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>ゲストインタビュー</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>ミステリー</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>ドキュメンタリー</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>昔話</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28.8" customHeight="1">
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>対話</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>対話</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>対話</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>対話</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>対話</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="n"/>
+      <c r="H2" s="6" t="n"/>
+      <c r="I2" s="6" t="n"/>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>ナレーター大
+＋台詞小</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <f>A4+1</f>
+        <v/>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <f>A5+1</f>
+        <v/>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <f>A6+1</f>
+        <v/>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <f>A7+1</f>
+        <v/>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <f>A8+1</f>
+        <v/>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <f>A9+1</f>
+        <v/>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <f>A10+1</f>
+        <v/>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <f>A11+1</f>
+        <v/>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <f>A12+1</f>
+        <v/>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <f>A13+1</f>
+        <v/>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <f>A14+1</f>
+        <v/>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <f>A15+1</f>
+        <v/>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <f>A16+1</f>
+        <v/>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>タブ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>カテゴリー</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>サブテーマ</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>形式</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>対象レベル(非表示)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>字数</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>英訳</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>キー表現</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ポイント</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>楽しさ・継続フック</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>備考(音声)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>L-R-005</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>お便り相談室</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>勉強が続かない</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>トーク</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>こんばんは、パーソナリティの ユウキです。今日（きょう）も 一日（いちにち）お疲（つか）れさまでした。さて、リスナーの みなさんから お便（たよ）りを いただきました。「最近（さいきん）、日本語（にほんご）の 勉強（べんきょう）が 続（つづ）かなくて 困（こま）っています」。わかります〜。でも、大丈夫（だいじょうぶ）。毎日（まいにち）5分（ふん）でも いいんです。好（す）きな ドラマや 歌（うた）で 楽（たの）しく 続（つづ）けましょう。それでは、今夜（こんや）の 一曲（いっきょく）です。</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>142</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Good evening, this is your host, Yuki. Thanks for your hard work today. Now, a message from a listener: 'Lately I can't keep up my Japanese study and I'm troubled.' I understand! But it's okay. Even 5 minutes a day is fine. Keep it up enjoyably with dramas or songs you like. Now, tonight's song.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>お疲れさまでした／お便り／〜ましょう</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>相談＋励ましの語り口。</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>共感＝続けたくなる。</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1話者・パーソナリティ調</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>L-R-006</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>お便り相談室</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>漢字が覚えられない</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>トーク</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>今日（きょう）の お便（たよ）りです。「漢字（かんじ）が なかなか 覚（おぼ）えられません」。わかります。漢字は 数（かず）が 多（おお）いですからね。おすすめは、毎日（まいにち）少（すこ）しずつ、生活（せいかつ）の 中（なか）で 見（み）た 漢字を 覚（おぼ）えることです。看板（かんばん）や メニューも いい 教材（きょうざい）ですよ。あせらず 続（つづ）けましょう。</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>103</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Today's listener message: 'I just can't memorize kanji.' I understand—there are so many. My tip: learn a little every day, from kanji you see in daily life. Signs and menus make good study material too. Don't rush—keep at it.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>なかなか 〜られません／少しずつ／あせらず 続けましょう</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>相談＋アドバイスの語り。</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>共感＆励ましで続く。</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1話者・パーソナリティ調</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>タブ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>カテゴリー</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>サブテーマ</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>形式</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>対象レベル(非表示)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>字数</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>英訳</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>キー表現</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ポイント</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>楽しさ・継続フック</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>備考(音声)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>L-R-007</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ゲストインタビュー</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ゲストのカイさん</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>対話</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>司会（しかい）：今日（きょう）の ゲストは、日本（にほん）で 勉強（べんきょう）している カイさんです。日本に 来て どのくらいですか。
+カイ：半年（はんとし）くらいです。
+司会：日本で 一番（いちばん）好（す）きな ものは？
+カイ：温泉（おんせん）です。とても 気持（きも）ちが いいです。
+司会：これから 何（なに）を したいですか。
+カイ：日本語（にほんご）を もっと 上手（じょうず）に なりたいです。
+司会：いいですね！ がんばってください。</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>142</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Host: Today's guest is Kai, who is studying in Japan. How long have you been in Japan? / Kai: About half a year. / Host: What's your favorite thing in Japan? / Kai: Hot springs. They feel so good. / Host: What do you want to do from now on? / Kai: I want to get better at Japanese. / Host: Nice! Keep it up.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>どのくらいですか／一番 好きな ものは？／がんばってください</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>インタビューの定番質問。</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>多様な人の声・人間味。</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>多声TTS:司会/ゲスト</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>タブ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>カテゴリー</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>サブテーマ</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>形式</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>対象レベル(非表示)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>字数</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>英訳</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>キー表現</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ポイント</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>楽しさ・継続フック</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>備考(音声)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>L-R-008</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2人のフリートーク</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>週末どうだった？</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>対話</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ケンタ：週末（しゅうまつ）、どうだった？
+カイ：友（とも）だちの ミナと 海（うみ）に 行（い）ったよ。すごく きれいだった！
+ケンタ：いいなあ。おれは 一日中（いちにちじゅう）、家（いえ）で ドラマを 見（み）てた。
+カイ：それも いいね。何（なに）の ドラマ？
+ケンタ：日本（にほん）の 恋愛（れんあい）ドラマ。じつは 日本語の 勉強（べんきょう）にも なるんだぜ。
+カイ：へえ、いいね！</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>122</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Kenta: How was your weekend? / Kai: I went to the beach with my friend Mina. It was so beautiful! / Kenta: Nice. I watched dramas at home all day. / Kai: That's good too. What drama? / Kenta: A Japanese romance drama. Actually it's good Japanese study too. / Kai: Oh, nice!</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>どうだった?／〜に 行ったよ／勉強にも なる</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>相棒ケンタとカイのゆるい雑談(再登場)。</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>くだけた会話＝多聴に最適。</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>多声TTS:ケンタ/カイ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -463,12 +1387,11 @@
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="12" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="43.2" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
@@ -541,12 +1464,12 @@
       </c>
     </row>
     <row r="2" ht="210" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>L-K-001</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -566,12 +1489,12 @@
           <t>空港に着いた</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
@@ -588,7 +1511,7 @@
 （ナレーション）スタンプを もらって、カイは 大（おお）きく 息（いき）を ついた。「やっと 来た…。これから 新（あたら）しい 毎日（まいにち）が 始（はじ）まるんだ」。</t>
         </is>
       </c>
-      <c r="I2" s="7" t="n">
+      <c r="I2" s="2" t="n">
         <v>205</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -618,12 +1541,12 @@
       </c>
     </row>
     <row r="3" ht="225" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>L-K-002</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -643,12 +1566,12 @@
           <t>ゴミ出しでこまった</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -665,7 +1588,7 @@
 （ナレーション）カイは ほっとした。「田中（たなか）さん、親切（しんせつ）だなあ。心強（こころづよ）いな」。</t>
         </is>
       </c>
-      <c r="I3" s="7" t="n">
+      <c r="I3" s="2" t="n">
         <v>231</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -695,12 +1618,12 @@
       </c>
     </row>
     <row r="4" ht="180" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>L-K-003</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -720,12 +1643,12 @@
           <t>はじめての友だち（ミナ）</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -742,7 +1665,7 @@
 （ナレーション）この 日（ひ）から、ミナは カイの いちばんの 友（とも）だちに なった。</t>
         </is>
       </c>
-      <c r="I4" s="7" t="n">
+      <c r="I4" s="2" t="n">
         <v>180</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -772,12 +1695,12 @@
       </c>
     </row>
     <row r="5" ht="195" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>L-K-004</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -797,12 +1720,12 @@
           <t>バイトを始める</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -818,7 +1741,7 @@
 （ナレーション）ケンタの 明（あか）るさに、カイの きんちょうは すっと ほどけた。「日本人（にほんじん）の 友（とも）だち、第一号（だいいちごう）だ」。</t>
         </is>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="I5" s="2" t="n">
         <v>222</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -848,12 +1771,12 @@
       </c>
     </row>
     <row r="6" ht="195" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>L-K-005</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -873,12 +1796,12 @@
           <t>日本語学校の初日</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -894,7 +1817,7 @@
 （ナレーション）さくら先生（せんせい）の ていねいな 日本語（にほんご）と、ミナの 笑顔（えがお）。カイの 新（あたら）しい 毎日（まいにち）は、ここから 始（はじ）まった。</t>
         </is>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="I6" s="2" t="n">
         <v>194</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -928,14 +1851,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -948,12 +1871,11 @@
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="12" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="43.2" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
@@ -1026,12 +1948,12 @@
       </c>
     </row>
     <row r="2" ht="210" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>L-J-001</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1051,12 +1973,12 @@
           <t>京都へ行く</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -1075,7 +1997,7 @@
 （ナレーション）わすれられない 一日（いちにち）に なった。</t>
         </is>
       </c>
-      <c r="I2" s="7" t="n">
+      <c r="I2" s="2" t="n">
         <v>181</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -1105,12 +2027,12 @@
       </c>
     </row>
     <row r="3" ht="180" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>L-J-002</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1130,12 +2052,12 @@
           <t>お祭りに行く</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -1153,7 +2075,7 @@
 （ナレーション）大（おお）きな 音（おと）と 光（ひかり）。カイの 胸（むね）は どきどきしていた。</t>
         </is>
       </c>
-      <c r="I3" s="7" t="n">
+      <c r="I3" s="2" t="n">
         <v>165</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -1187,14 +2109,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -1207,12 +2129,11 @@
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="12" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="43.2" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
@@ -1285,12 +2206,12 @@
       </c>
     </row>
     <row r="2" ht="225" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>L-L-001</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1310,12 +2231,12 @@
           <t>はじめての美容院</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -1334,7 +2255,7 @@
 （ナレーション）少（すこ）し 短すぎたけれど、カイは なんだか うれしかった。</t>
         </is>
       </c>
-      <c r="I2" s="7" t="n">
+      <c r="I2" s="2" t="n">
         <v>210</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -1368,14 +2289,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -1388,12 +2309,11 @@
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="12" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="43.2" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
@@ -1466,12 +2386,12 @@
       </c>
     </row>
     <row r="2" ht="165" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>L-B-001</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -1491,12 +2411,12 @@
           <t>好きな食べ物の話</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -1510,7 +2430,7 @@
 カイ：みなさんの 好（す）きな 日本（にほん）の 食べ物は 何（なん）ですか？ また 教（おし）えてね。じゃあ、また！</t>
         </is>
       </c>
-      <c r="I2" s="7" t="n">
+      <c r="I2" s="2" t="n">
         <v>177</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -1544,14 +2464,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -1564,12 +2484,11 @@
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="12" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="43.2" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
@@ -1641,574 +2560,359 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="120" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>L-R-001</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
+    <row r="2" ht="150" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>L-M-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>ラジオトーク</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>ニュース</t>
-        </is>
-      </c>
+          <t>ミステリー</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>桜が満開（国内）</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>ニュース</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
+          <t>消えた駅弁の謎 第1話：駅で事件発生</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>（ナレーション）東京駅（とうきょうえき）の 有名（ゆうめい）な 駅弁屋（えきべんや）で 事件（じけん）が 起（お）きた。
+店長（てんちょう）：たいへんだ！ 一番（いちばん）人気（にんき）の「うみの幸（さち）弁当（べんとう）」が、10個（こ）も 消（き）えてる！
+駅員（えきいん）の明智（あけち）：鍵（かぎ）は かかっていたんですよね？
+店長：はい、朝（あさ）まで しっかり…。
+明智：おかしいな。鍵（かぎ）が かかっていたのに、どうやって…？
+（ナレーション）明智（あけち）さんは 考（かんが）えた。これは ただの どろぼうでは ないかもしれない。</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>(Narration) An incident occurred at a famous ekiben shop in Tokyo Station. / Manager: This is terrible! Ten of our most popular 'Sea Bounty Bento' have vanished! / Akechi (staff): The door was locked, right? / Manager: Yes, firmly until morning... / Akechi: Strange. The door was locked, so how...? / (Narration) Akechi thought. This might not be an ordinary thief.</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>たいへんだ／〜んですよね／どうやって…?</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>事件の発端を会話で（密室の謎）。</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>続きが気になる第1話。</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>多声TTS:ナレーター/店長/田中</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="165" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>L-M-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>ミステリー</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>消えた駅弁の謎 第2話：証言を聞く</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>対話</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>明智（あけち）：すみません、今朝（けさ）、何（なに）か 見（み）ませんでしたか。
+掃除（そうじ）の人：5時（じ）ごろ、白（しろ）い 服（ふく）の 人（ひと）を 見（み）ましたよ。
+明智：白い 服…。ありがとうございます。
+コーヒー店（てん）の人：そういえば、変（へん）な 音（おと）が しましたね。バサバサっと。
+明智：バサバサ？
+（ナレーション）でも、防犯（ぼうはん）カメラには だれも 映（うつ）っていない。
+明智：（首（くび）を かしげて）うーん、おかしいなあ…。</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Akechi: Excuse me, did you see anything this morning? / Cleaner: Around 5, I saw someone in white clothes. / Akechi: White clothes... Thank you. / Coffee-shop worker: Come to think of it, there was a strange sound. A flapping sound. / Akechi: Flapping? / (Narration) But the security camera showed no one. / Akechi: (tilting his head) Hmm, that's strange...</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>見ませんでしたか／そういえば／うーん</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>証言の会話と矛盾。会話表現「そういえば/うーん」。</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>謎が深まる。</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>多声TTS:田中/証人たち/ナレーター</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="135" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>L-M-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>ミステリー</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>消えた駅弁の謎 第3話：容疑者登場</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>対話</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>おはようございます。今朝（けさ）の ニュースです。昨日（きのう）、東京（とうきょう）の 公園（こうえん）で 桜（さくら）が 満開（まんかい）に なりました。週末（しゅうまつ）は たくさんの 家族（かぞく）連（づ）れで にぎわいそうです。天気（てんき）も よく、お花見（はなみ）に ぴったりの 一日（いちにち）に なるでしょう。一方（いっぽう）、来週（らいしゅう）からは 少（すこ）し 寒（さむ）く なるという 予報（よほう）も 出（で）ています。体調（たいちょう）に 気（き）を つけて お過（す）ごしください。では、今日（きょう）も よい 一日を。</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="n">
-        <v>142</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>Good morning. Here's this morning's news. Yesterday, the cherry blossoms reached full bloom in a Tokyo park. This weekend it should be crowded with families. The weather is good too—a perfect day for hanami. On the other hand, it's forecast to get a bit colder from next week. Please take care of your health. Have a good day.</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>今朝の ニュース／満開／〜そうです／一方</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>ニュースの流れと話題転換「一方」。</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>季節感で“朝の習慣”に。</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>1話者・アナウンサー調</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="105" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>L-R-002</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>（ナレーション）次（つぎ）の 日（ひ）、明智（あけち）さんは 白（しろ）い 服（ふく）の 男（おとこ）を 見（み）つけた。駅（えき）の 清掃員（せいそういん）だ。
+明智：あの 朝（あさ）、何（なに）を していましたか。
+清掃員：私（わたし）は ただ、ゴミを 集（あつ）めていただけですよ。
+（ナレーション）そのとき、男（おとこ）の カバンから 弁当（べんとう）の 包（つつ）み紙（がみ）が ひらり、と 落（お）ちた。
+明智：（目（め）を 光（ひか）らせて）…これは？
+清掃員：えっ、いや、これは…！</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>(Narration) The next day, Akechi found the man in white—a station cleaner. / Akechi: What were you doing that morning? / Cleaner: I was just collecting trash. / (Narration) Just then, a bento wrapper fluttered out of the man's bag. / Akechi: (eyes flashing) ...What's this? / Cleaner: Huh, no, this is...!</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>〜だけですよ／これは？／えっ、いや</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>容疑者への会話と証拠。会話表現「〜だけですよ/えっ、いや」。</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>犯人か?の緊張。</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>多声TTS:ナレーター/田中/清掃員</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="150" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>L-M-004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>ラジオトーク</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>ニュース</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>全国の天気（天気）</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>天気予報</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>全国（ぜんこく）の 天気（てんき）です。今日（きょう）は 西日本（にしにほん）で 晴（は）れますが、東日本（ひがしにほん）は 午後（ごご）から 雲（くも）が 多（おお）く なるでしょう。夜（よる）には 雨（あめ）が 降（ふ）る 所（ところ）も あります。傘（かさ）を 持（も）って 出（で）かけると 安心（あんしん）です。気温（きおん）は 各地（かくち）で 20度（ど）前後（ぜんご）、過（す）ごしやすい 一日（いちにち）に なりそうです。</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="n">
-        <v>97</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Here's the nationwide weather. Today it's sunny in western Japan, but in eastern Japan clouds will increase from the afternoon. Some areas may see rain at night. It's safer to take an umbrella. Temperatures will be around 20 degrees—a comfortable day.</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>晴れます／雲が 多く なる／傘を 持って</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>全国天気の聞き取り（地域差）。</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>「傘いる?」毎朝役立つ。</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>1話者・予報士調</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="105" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>L-R-003</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>ミステリー</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>消えた駅弁の謎 第4話：真犯人は？</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>清掃員：それは、私（わたし）が 拾（ひろ）った ゴミです。本当（ほんとう）です！
+（ナレーション）明智（あけち）さんは 防犯（ぼうはん）カメラを もう一度（いちど）見（み）た。すると、屋根（やね）の すきまから…
+明智：あっ！ 見（み）て ください。大（おお）きな カラスが、弁当（べんとう）を 運（はこ）んでる！
+店長：えーっ！ 犯人（はんにん）は カラス だったの！？
+（ナレーション）みんな 大笑（おおわら）い。鍵（かぎ）の 謎（なぞ）は、屋根（やね）の 小（ちい）さな 窓（まど）だったのだ。
+明智：はは、事件（じけん）は 無事（ぶじ）解決（かいけつ）、ですね。</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Cleaner: That's trash I picked up. It's true! / (Narration) Akechi watched the security camera again. Then, through a gap in the roof... / Akechi: Ah! Look! A big crow is carrying the bento! / Manager: Whaaat! The culprit was a crow?! / (Narration) Everyone burst out laughing. The mystery of the lock was a small window in the roof. / Akechi: Haha, case closed.</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>見て ください／〜だったの!?／無事 解決</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>真相を会話で。会話表現「あっ/えーっ/はは」。</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>犯人はカラス＝意外な落ち。</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>多声TTS:ナレーター/田中/清掃員/店長</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="165" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>L-M-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>ラジオトーク</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>ニュース</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>海外のニュース（国際）</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>ニュース</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>ミステリー</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>消えた最終電車</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>物語</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>こんにちは、国際（こくさい）ニュースです。アメリカで、新（あたら）しい 技術（ぎじゅつ）の 会議（かいぎ）が 開（ひら）かれました。世界中（せかいじゅう）から たくさんの 研究者（けんきゅうしゃ）が 集（あつ）まりました。日本（にほん）からも 多（おお）くの 企業（きぎょう）が 参加（さんか）し、注目（ちゅうもく）を 集（あつ）めています。来年（らいねん）は アジアでも 同（おな）じ 会議が 開かれる 予定（よてい）です。</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>105</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Hello, international news. In the U.S., a conference on new technology was held. Many researchers gathered from around the world. Many companies from Japan also took part and are drawing attention. Next year, the same conference is scheduled to be held in Asia too.</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>国際ニュース／〜が 開かれました／注目を 集めています</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>国際ニュースの定型表現。</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>世界とつながる話題。</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>1話者・アナウンサー調</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="90" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>L-R-004</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>長文</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>ラジオトーク</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>ニュース</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>サッカーの試合（スポーツ）</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>ニュース</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>スポーツの ニュースです。昨日（きのう）、サッカーの 試合（しあい）が ありました。日本（にほん）チームは 2対（たい）1で 勝（か）ちました。最後（さいご）の ゴールは、とても すばらしかったです。スタジアムの ファンは 大（おお）きな 声（こえ）で 応援（おうえん）しました。次（つぎ）の 試合は 来週（らいしゅう）の 土曜日（どようび）です。楽（たの）しみですね。</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>109</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>Sports news. Yesterday there was a soccer match. The Japan team won 2 to 1. The final goal was wonderful. Fans in the stadium cheered loudly. The next match is next Saturday. Something to look forward to.</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>2対1で 勝ちました／応援しました／楽しみですね</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>スポーツ結果(点数/勝敗)の聞き取り。</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>勝利の興奮。</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>1話者・アナウンサー調</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="120" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>L-R-005</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>長文</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>ラジオトーク</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>お便り相談室</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>勉強が続かない</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>トーク</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>こんばんは、パーソナリティの ユウキです。今日（きょう）も 一日（いちにち）お疲（つか）れさまでした。さて、リスナーの みなさんから お便（たよ）りを いただきました。「最近（さいきん）、日本語（にほんご）の 勉強（べんきょう）が 続（つづ）かなくて 困（こま）っています」。わかります〜。でも、大丈夫（だいじょうぶ）。毎日（まいにち）5分（ふん）でも いいんです。好（す）きな ドラマや 歌（うた）で 楽（たの）しく 続（つづ）けましょう。それでは、今夜（こんや）の 一曲（いっきょく）です。</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>142</v>
+          <t>夜（よる）11時（じ）50分（ぷん）、駅員（えきいん）の 木村（きむら）さんは おかしな ことに 気（き）づいた。
+木村：あれ？ さっきまで ホームに いた 女（おんな）の 人（ひと）、どこへ 行（い）ったんだ…。
+終電（しゅうでん）は まだ 来（き）ていない。改札（かいさつ）も 通（とお）っていない。なのに、ホームには 誰（だれ）も いない。
+木村：かばんだけが、ベンチに 残（のこ）っている…。
+次（つぎ）の 朝（あさ）、かばんの 中（なか）から 一枚（いちまい）の 古（ふる）い 切符（きっぷ）が 見（み）つかった。日付（ひづけ）は——30年（ねん）前（まえ）だった。
+（つづく）</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>154</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Good evening, this is your host, Yuki. Thanks for your hard work today. Now, a message from a listener: 'Lately I can't keep up my Japanese study and I'm troubled.' I understand! But it's okay. Even 5 minutes a day is fine. Keep it up enjoyably with dramas or songs you like. Now, tonight's song.</t>
+          <t>11:50 p.m. Station attendant Kimura noticed something strange. Kimura: Huh? The woman who was on the platform just now—where did she go...? The last train hasn't come yet. She didn't pass the gate. And yet, no one is on the platform. Kimura: Only a bag is left on the bench... The next morning, an old ticket was found inside the bag. The date was—30 years ago. (To be continued)</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>お疲れさまでした／お便り／〜ましょう</t>
+          <t>〜に 気づいた／なのに／〜だった</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>相談＋励ましの語り口。</t>
+          <t>続きが気になる導入。</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>共感＝続けたくなる。</t>
+          <t>30年前の切符の謎。</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>1話者・パーソナリティ調</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="90" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>L-R-006</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>長文</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>ラジオトーク</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>お便り相談室</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>漢字が覚えられない</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>トーク</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>今日（きょう）の お便（たよ）りです。「漢字（かんじ）が なかなか 覚（おぼ）えられません」。わかります。漢字は 数（かず）が 多（おお）いですからね。おすすめは、毎日（まいにち）少（すこ）しずつ、生活（せいかつ）の 中（なか）で 見（み）た 漢字を 覚（おぼ）えることです。看板（かんばん）や メニューも いい 教材（きょうざい）ですよ。あせらず 続（つづ）けましょう。</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="n">
-        <v>103</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>Today's listener message: 'I just can't memorize kanji.' I understand—there are so many. My tip: learn a little every day, from kanji you see in daily life. Signs and menus make good study material too. Don't rush—keep at it.</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>なかなか 〜られません／少しずつ／あせらず 続けましょう</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>相談＋アドバイスの語り。</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>共感＆励ましで続く。</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>1話者・パーソナリティ調</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="120" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>L-R-007</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>長文</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>ラジオトーク</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>ゲストインタビュー</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>ゲストのカイさん</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>対話</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>司会（しかい）：今日（きょう）の ゲストは、日本（にほん）で 勉強（べんきょう）している カイさんです。日本に 来て どのくらいですか。
-カイ：半年（はんとし）くらいです。
-司会：日本で 一番（いちばん）好（す）きな ものは？
-カイ：温泉（おんせん）です。とても 気持（きも）ちが いいです。
-司会：これから 何（なに）を したいですか。
-カイ：日本語（にほんご）を もっと 上手（じょうず）に なりたいです。
-司会：いいですね！ がんばってください。</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>142</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>Host: Today's guest is Kai, who is studying in Japan. How long have you been in Japan? / Kai: About half a year. / Host: What's your favorite thing in Japan? / Kai: Hot springs. They feel so good. / Host: What do you want to do from now on? / Kai: I want to get better at Japanese. / Host: Nice! Keep it up.</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>どのくらいですか／一番 好きな ものは？／がんばってください</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>インタビューの定番質問。</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>多様な人の声・人間味。</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>多声TTS:司会/ゲスト</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="135" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>L-R-008</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>長文</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>ラジオトーク</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>2人のフリートーク</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>週末どうだった？</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>対話</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>N4</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>ケンタ：週末（しゅうまつ）、どうだった？
-カイ：友（とも）だちの ミナと 海（うみ）に 行（い）ったよ。すごく きれいだった！
-ケンタ：いいなあ。おれは 一日中（いちにちじゅう）、家（いえ）で ドラマを 見（み）てた。
-カイ：それも いいね。何（なに）の ドラマ？
-ケンタ：日本（にほん）の 恋愛（れんあい）ドラマ。じつは 日本語の 勉強（べんきょう）にも なるんだぜ。
-カイ：へえ、いいね！</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>122</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>Kenta: How was your weekend? / Kai: I went to the beach with my friend Mina. It was so beautiful! / Kenta: Nice. I watched dramas at home all day. / Kai: That's good too. What drama? / Kenta: A Japanese romance drama. Actually it's good Japanese study too. / Kai: Oh, nice!</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>どうだった?／〜に 行ったよ／勉強にも なる</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>相棒ケンタとカイのゆるい雑談(再登場)。</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>くだけた会話＝多聴に最適。</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>多声TTS:ケンタ/カイ</t>
+          <t>多声TTS:ナレーション/駅員</t>
         </is>
       </c>
     </row>
@@ -2217,14 +2921,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -2237,12 +2941,11 @@
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="12" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="43.2" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
@@ -2314,359 +3017,364 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="150" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>L-M-001</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
+    <row r="2" ht="409.6" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>L-D-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>ミステリー</t>
+          <t>ドキュメンタリー</t>
         </is>
       </c>
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>消えた駅弁の謎 第1話：駅で事件発生</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>物語</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>N4</t>
+          <t>カップラーメンの誕生</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>ドキュメンタリー</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>N3</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>（ナレーション）東京駅（とうきょうえき）の 有名（ゆうめい）な 駅弁屋（えきべんや）で 事件（じけん）が 起（お）きた。
-店長（てんちょう）：たいへんだ！ 一番（いちばん）人気（にんき）の「うみの幸（さち）弁当（べんとう）」が、10個（こ）も 消（き）えてる！
-駅員（えきいん）の明智（あけち）：鍵（かぎ）は かかっていたんですよね？
-店長：はい、朝（あさ）まで しっかり…。
-明智：おかしいな。鍵（かぎ）が かかっていたのに、どうやって…？
-（ナレーション）明智（あけち）さんは 考（かんが）えた。これは ただの どろぼうでは ないかもしれない。</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="n">
-        <v>143</v>
+          <t>（ナレーション）戦後（せんご）の日本（にほん）。焼（や）け野原（のはら）が広（ひろ）がる寒（さむ）い夜（よる）、一軒（いっけん）の屋台（やたい）に長（なが）い行列（ぎょうれつ）ができていた。人々（ひとびと）は、温（あたた）かいラーメン一杯（いっぱい）を、ふるえながら待（ま）っていた。その光景（こうけい）を、安藤（あんどう）はじっと見（み）つめていた。
+安藤：「これほど多（おお）くの人（ひと）が、一杯（いっぱい）のラーメンを求（もと）めている。家（いえ）で、すぐに、手軽（てがる）に食（た）べられるラーメンを作（つく）れないだろうか」。
+（ナレーション）安藤（あんどう）は、自宅（じたく）の裏（うら）に小（ちい）さな小屋（こや）を建（た）て、たった一人（ひとり）で研究（けんきゅう）を始（はじ）めた。来（く）る日（ひ）も来（く）る日（ひ）も、麺（めん）づくりに明（あ）け暮（く）れる。だが、ゆでた麺（めん）はすぐにのびて、味（あじ）も落（お）ちてしまう。失敗（しっぱい）は何百回（なんびゃっかい）も続（つづ）いた。
+安藤：「どうすれば、長（なが）く保存（ほぞん）でき、湯（ゆ）をかけるだけで元（もと）に戻（もど）るんだ…」。
+（ナレーション）眠（ねむ）る時間（じかん）も惜（お）しんだ。見（み）かねた妻（つま）が、夜（よる）おそく台所（だいどころ）から声（こえ）をかけた。
+妻：「あなた、少（すこ）し休（やす）んだら？ 今日（きょう）は天（てん）ぷらを揚（あ）げましたよ」。
+（ナレーション）その時（とき）だった。安藤（あんどう）の目（め）が、油（あぶら）の中（なか）の天（てん）ぷらに釘付（くぎづ）けになった。衣（ころも）から、無数（むすう）の泡（あわ）が立（た）ちのぼっている。水分（すいぶん）が一気（いっき）に飛（と）んでいく――。「これだ！ 油（あぶら）で揚（あ）げれば麺（めん）は乾（かわ）き、無数（むすう）の穴（あな）に湯（ゆ）がしみ込（こ）めば、麺（めん）は元（もと）に戻（もど）る！」。
+（ナレーション）こうして一杯（いっぱい）のインスタントラーメンが生（う）まれた。さらに安藤（あんどう）は、世界（せかい）へ届（とど）けるため、器（うつわ）ごと食（た）べられる「カップ」を発明（はつめい）する。発売（はつばい）の日（ひ）、半信半疑（はんしんはんぎ）だった人々（ひとびと）は、湯（ゆ）を注（そそ）いで三分（さんぷん）、ふたを開（あ）けて笑顔（えがお）になった。一人（ひとり）の執念（しゅうねん）が、世界（せかい）の食卓（しょくたく）を永遠（えいえん）に変（か）えたのである。</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>537</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>(Narration) An incident occurred at a famous ekiben shop in Tokyo Station. / Manager: This is terrible! Ten of our most popular 'Sea Bounty Bento' have vanished! / Akechi (staff): The door was locked, right? / Manager: Yes, firmly until morning... / Akechi: Strange. The door was locked, so how...? / (Narration) Akechi thought. This might not be an ordinary thief.</t>
+          <t>Postwar Japan. On a cold night amid the burnt ruins, a long line formed at a single food stall. People waited, shivering, for one warm bowl of ramen. Ando watched intently. 'So many people long for a single bowl. Could I make ramen you can eat at home, quickly and easily?' He built a small shed behind his house and began researching alone. Day after day he toiled over noodles, but boiled noodles soon went soft and lost flavor. He failed hundreds of times. 'How can I make it keep, and return to normal with just hot water?' He begrudged even sleep. His worried wife called out late at night: 'Dear, why not rest? I fried tempura today.' That was the moment. Ando's eyes fixed on the tempura in the oil—countless bubbles rising from the batter, the moisture flying off. 'That's it! Fry the noodles and they dry; pour hot water into the tiny holes and they return.' Thus instant ramen was born. To reach the world, he also invented the edible 'cup.' On launch day, doubtful people poured hot water, waited three minutes, lifted the lid, and smiled. One man's tenacity changed dinner tables worldwide forever.</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>たいへんだ／〜んですよね／どうやって…?</t>
+          <t>〜ないだろうか／〜だけで／〜ば 元に戻る</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>事件の発端を会話で（密室の謎）。</t>
+          <t>執念が世界を変えた発明。</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>続きが気になる第1話。</t>
+          <t>失敗の先のひらめき。</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>多声TTS:ナレーター/店長/田中</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="165" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>L-M-002</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
+          <t>多声TTS:ナレーター/安藤/妻</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="409.6" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>L-D-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>ミステリー</t>
+          <t>ドキュメンタリー</t>
         </is>
       </c>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>消えた駅弁の謎 第2話：証言を聞く</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>対話</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>N4</t>
+          <t>新幹線――夢の超特急</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>ドキュメンタリー</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>N3</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>明智（あけち）：すみません、今朝（けさ）、何（なに）か 見（み）ませんでしたか。
-掃除（そうじ）の人：5時（じ）ごろ、白（しろ）い 服（ふく）の 人（ひと）を 見（み）ましたよ。
-明智：白い 服…。ありがとうございます。
-コーヒー店（てん）の人：そういえば、変（へん）な 音（おと）が しましたね。バサバサっと。
-明智：バサバサ？
-（ナレーション）でも、防犯（ぼうはん）カメラには だれも 映（うつ）っていない。
-明智：（首（くび）を かしげて）うーん、おかしいなあ…。</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="n">
-        <v>144</v>
+          <t>（ナレーション）1964年（ねん）、東京（とうきょう）と大阪（おおさか）を結（むす）ぶ新幹線（しんかんせん）が走（はし）り始（はじ）めた。当時（とうじ）、時速（じそく）200キロを超（こ）える電車（でんしゃ）は、世界（せかい）のどこにも存在（そんざい）しなかった。
+技術者（ぎじゅつしゃ）：「そんなスピードは危険（きけん）だ。脱線（だっせん）したら、大事故（だいじこ）になる」。
+（ナレーション）多（おお）くの人（ひと）が、無理（むり）だと反対（はんたい）した。けれど、技術者（ぎじゅつしゃ）たちはあきらめなかった。彼（かれ）らは、空気（くうき）の力（ちから）、線路（せんろ）のカーブ、車輪（しゃりん）の揺（ゆ）れを、何度（なんど）も何度（なんど）も計算（けいさん）し直（なお）した。安全（あんぜん）のためなら、どんな小（ちい）さな問題（もんだい）も見逃（みのが）さなかった。
+技術者：「ここで妥協（だきょう）すれば、必（かなら）ず後（あと）で事故（じこ）が起（お）きる。とことんやろう」。
+（ナレーション）試験（しけん）と改良（かいりょう）の日々（ひび）。眠（ねむ）れない長（なが）い夜（よる）が続（つづ）いた。仲間（なかま）と知恵（ちえ）を出（だ）し合（あ）い、一（ひと）つずつ壁（かべ）を越（こ）えていく。そして迎（むか）えた開業（かいぎょう）の日（ひ）。白（しろ）と青（あお）の車両（しゃりょう）が、静（しず）かに、しかし力強（ちからづよ）くホームをすべり出（で）た。
+（ナレーション）新幹線（しんかんせん）は、一度（いちど）の事故（じこ）もなく、東京（とうきょう）から大阪（おおさか）まで走（はし）りきった。「夢（ゆめ）の超特急（ちょうとっきゅう）」は、日本（にほん）の誇（ほこ）りとなった。それは単（たん）なる速（はや）い電車（でんしゃ）ではない。不可能（ふかのう）を可能（かのう）に変（か）えた、技術者（ぎじゅつしゃ）たちの執念（しゅうねん）の結晶（けっしょう）だった。
+（ナレーション）かつて長（なが）い時間（じかん）がかかった東京（とうきょう）と大阪（おおさか）の間（あいだ）が、ぐっと近（ちか）くなった。仕事（しごと）でも旅行（りょこう）でも、日帰（ひがえ）りができる。新幹線（しんかんせん）は、人（ひと）と人（ひと）、町（まち）と町（まち）の距離（きょり）を、大（おお）きく縮（ちぢ）めたのだ。今（いま）も世界中（せかいじゅう）の高速鉄道（こうそくてつどう）が、この一本（いっぽん）の線路（せんろ）を手本（てほん）にし続（つづ）けている。</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>491</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Akechi: Excuse me, did you see anything this morning? / Cleaner: Around 5, I saw someone in white clothes. / Akechi: White clothes... Thank you. / Coffee-shop worker: Come to think of it, there was a strange sound. A flapping sound. / Akechi: Flapping? / (Narration) But the security camera showed no one. / Akechi: (tilting his head) Hmm, that's strange...</t>
+          <t>In 1964, the Shinkansen linking Tokyo and Osaka began to run. At the time, no train anywhere in the world exceeded 200 km/h. 'Such speed is dangerous. If it derails, there will be a terrible accident.' Many opposed it as impossible. But the engineers did not give up. They recalculated air resistance, track curves, and wheel vibration again and again. For safety, they overlooked no problem, however small. 'If we compromise here, an accident will surely come later. Let's see it through.' Days of testing and improvement; long sleepless nights. Sharing wisdom with colleagues, they cleared the walls one by one. Then came opening day. The white-and-blue cars slid quietly but powerfully from the platform. The Shinkansen ran the whole way from Tokyo to Osaka without a single accident. The 'dream super-express' became Japan's pride—not merely a fast train, but the crystallization of engineers' tenacity that turned the impossible into the possible. Even now, high-speed railways around the world look to this one line as their model.</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>見ませんでしたか／そういえば／うーん</t>
+          <t>〜を超える／〜のためなら／〜きった</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>証言の会話と矛盾。会話表現「そういえば/うーん」。</t>
+          <t>不可能を可能にした執念。</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>謎が深まる。</t>
+          <t>反対を覆した技術の結晶。</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>多声TTS:田中/証人たち/ナレーター</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="135" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>L-M-003</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
+          <t>多声TTS:ナレーター/技術者</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="409.6" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>L-D-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>ミステリー</t>
+          <t>ドキュメンタリー</t>
         </is>
       </c>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>消えた駅弁の謎 第3話：容疑者登場</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>対話</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
+          <t>ライト兄弟、空へ</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>ドキュメンタリー</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>（ナレーション）次（つぎ）の 日（ひ）、明智（あけち）さんは 白（しろ）い 服（ふく）の 男（おとこ）を 見（み）つけた。駅（えき）の 清掃員（せいそういん）だ。
-明智：あの 朝（あさ）、何（なに）を していましたか。
-清掃員：私（わたし）は ただ、ゴミを 集（あつ）めていただけですよ。
-（ナレーション）そのとき、男（おとこ）の カバンから 弁当（べんとう）の 包（つつ）み紙（がみ）が ひらり、と 落（お）ちた。
-明智：（目（め）を 光（ひか）らせて）…これは？
-清掃員：えっ、いや、これは…！</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>124</v>
+          <t>（ナレーション）100年（ねん）以上（いじょう）前（まえ）、アメリカの小（ちい）さな町（まち）に、自転車屋（じてんしゃや）を営（いとな）む二人（ふたり）の兄弟（きょうだい）がいた。ライト兄弟（きょうだい）である。当時（とうじ）、「人間（にんげん）が空（そら）を飛（と）ぶ」など、だれもが笑（わら）う夢物語（ゆめものがたり）だった。
+兄（あに）：「鳥（とり）は、どうやって風（かぜ）を受（う）け、体（からだ）を傾（かたむ）けて曲（ま）がっているんだろう」。
+（ナレーション）二人（ふたり）は来（く）る日（ひ）も来（く）る日（ひ）も、空（そら）をとぶ鳥（とり）を観察（かんさつ）した。翼（つばさ）の形（かたち）を作（つく）っては試（ため）し、こわれては、また作（つく）り直（なお）す。風（かぜ）の強（つよ）い丘（おか）で、何度（なんど）も地面（じめん）に たたきつけられた。それでも、二人（ふたり）の目（め）は、いつも空（そら）を見（み）ていた。
+弟（おとうと）：「兄（あに）さん、今度（こんど）こそ、風（かぜ）に乗（の）れる気（き）がする」。
+（ナレーション）1903年（ねん）の冷（つめ）たい冬（ふゆ）の朝（あさ）。強（つよ）い風（かぜ）の中（なか）、手作（てづく）りの飛行機（ひこうき）がエンジンの音（おと）を響（ひび）かせた。プロペラが回（まわ）り、機体（きたい）がゆっくりと動（うご）き出（だ）す。そして――ふわりと、車輪（しゃりん）が地面（じめん）を離（はな）れた。
+（ナレーション）飛（と）んだ時間（じかん）は、わずか12秒（びょう）。距離（きょり）は、たった36メートル。けれどそれは、人類（じんるい）が自分（じぶん）の力（ちから）で初（はじ）めて空（そら）を飛（と）んだ、歴史（れきし）が変（か）わった瞬間（しゅんかん）だった。
+（ナレーション）成功（せいこう）の裏（うら）には、何年（なんねん）もの地道（じみち）な努力（どりょく）があった。二人（ふたり）は、失敗（しっぱい）の記録（きろく）を一（ひと）つ残（のこ）らずノートに書（か）きとめ、つぎの工夫（くふう）に生（い）かしていったのだ。だれもが笑（わら）った夢（ゆめ）を、あきらめなかった二人（ふたり）。その小（ちい）さな12秒（びょう）から、世界中（せかいじゅう）の空（そら）の旅（たび）が始（はじ）まったのである。</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>473</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>(Narration) The next day, Akechi found the man in white—a station cleaner. / Akechi: What were you doing that morning? / Cleaner: I was just collecting trash. / (Narration) Just then, a bento wrapper fluttered out of the man's bag. / Akechi: (eyes flashing) ...What's this? / Cleaner: Huh, no, this is...!</t>
+          <t>More than a century ago, in a small American town, two brothers ran a bicycle shop: the Wright brothers. Back then, 'humans flying' was a fairy tale everyone laughed at. 'How do birds catch the wind and tilt their bodies to turn?' Day after day they watched birds in flight. They built wing shapes and tested them; when they broke, they rebuilt. On a windy hill they were dashed to the ground again and again. Yet their eyes were always on the sky. 'Brother, this time I feel we can ride the wind.' On a cold winter morning in 1903, in a strong wind, their handmade airplane roared. The propeller turned, the craft slowly moved—and then, gently, the wheels left the ground. The flight lasted just 12 seconds, only 36 meters. But it was the moment humanity first flew by its own power, and history changed. Two brothers who never gave up on a dream everyone mocked. From that tiny 12 seconds, the world's journeys through the sky began.</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>〜だけですよ／これは？／えっ、いや</t>
+          <t>〜だろう／〜ては 〜直す／それでも</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>容疑者への会話と証拠。会話表現「〜だけですよ/えっ、いや」。</t>
+          <t>笑われた夢への挑戦。</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>犯人か?の緊張。</t>
+          <t>12秒が歴史を変えた。</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>多声TTS:ナレーター/田中/清掃員</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="150" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>L-M-004</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
+          <t>多声TTS:ナレーター/兄/弟</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="409.6" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>L-D-004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>ミステリー</t>
+          <t>ドキュメンタリー</t>
         </is>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>消えた駅弁の謎 第4話：真犯人は？</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>物語</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
+          <t>エジソンと電球</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>ドキュメンタリー</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>清掃員：それは、私（わたし）が 拾（ひろ）った ゴミです。本当（ほんとう）です！
-（ナレーション）明智（あけち）さんは 防犯（ぼうはん）カメラを もう一度（いちど）見（み）た。すると、屋根（やね）の すきまから…
-明智：あっ！ 見（み）て ください。大（おお）きな カラスが、弁当（べんとう）を 運（はこ）んでる！
-店長：えーっ！ 犯人（はんにん）は カラス だったの！？
-（ナレーション）みんな 大笑（おおわら）い。鍵（かぎ）の 謎（なぞ）は、屋根（やね）の 小（ちい）さな 窓（まど）だったのだ。
-明智：はは、事件（じけん）は 無事（ぶじ）解決（かいけつ）、ですね。</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>145</v>
+          <t>（ナレーション）まだ電気（でんき）のない時代（じだい）。夜（よる）の暗（くら）やみを照（て）らすのは、ろうそくやランプの、小（ちい）さくゆれる炎（ほのお）だけだった。アメリカの発明家（はつめいか）エジソンは、決心（けっしん）した。「だれもが使（つか）える、長（なが）く明（あか）るい電球（でんきゅう）を作（つく）る」と。
+（ナレーション）光（ひか）る糸（いと）の材料（ざいりょう）を探（さが）して、エジソンは実験（じっけん）をくり返（かえ）した。木綿（もめん）、紙（かみ）、髪（かみ）の毛（け）――ありとあらゆるものを試（ため）したが、糸（いと）はすぐに燃（も）えつきてしまう。失敗（しっぱい）の数（かず）は、千回（せんかい）をこえた。
+助手（じょしゅ）：「先生（せんせい）、また失敗（しっぱい）です。もう、あきらめませんか」。
+エジソン：「いや。これは失敗（しっぱい）じゃない。『うまくいかない方法（ほうほう）』を、また一（ひと）つ見（み）つけただけさ」。
+（ナレーション）エジソンは、最後（さいご）まで信（しん）じることをやめなかった。やがて、日本（にほん）の竹（たけ）から作（つく）った細（ほそ）い糸（いと）が、なんと40時間（じかん）以上（いじょう）も光（ひか）り続（つづ）けた。研究室（けんきゅうしつ）に、あたたかな明（あ）かりがともった。
+（ナレーション）その夜（よる）、世界（せかい）の暗（くら）やみは、少（すこ）しずつ明（あか）るく照（て）らされていった。電球（でんきゅう）だけではない。エジソンは生涯（しょうがい）に千以上（せんいじょう）もの発明（はつめい）を世（よ）に残（のこ）した。その原動力（げんどうりょく）は、子（こ）どものころから変（か）わらない「なぜ？」という強（つよ）い好奇心（こうきしん）だった。
+（ナレーション）「天才（てんさい）とは、1パーセントのひらめきと、99パーセントの努力（どりょく）である」。失敗（しっぱい）を恐（おそ）れず、努力（どりょく）を続（つづ）けたエジソンの言葉（ことば）は、今（いま）も世界中（せかいじゅう）の人（ひと）の胸（むね）に生（い）きている。</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>479</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Cleaner: That's trash I picked up. It's true! / (Narration) Akechi watched the security camera again. Then, through a gap in the roof... / Akechi: Ah! Look! A big crow is carrying the bento! / Manager: Whaaat! The culprit was a crow?! / (Narration) Everyone burst out laughing. The mystery of the lock was a small window in the roof. / Akechi: Haha, case closed.</t>
+          <t>In an age without electricity, the only thing lighting the darkness of night was the small, flickering flame of candles and lamps. The American inventor Edison resolved: 'I will make a long-lasting, bright bulb that anyone can use.' Searching for a glowing filament, Edison repeated experiments—cotton, paper, hair—he tried everything, but the thread burned out at once. His failures passed a thousand. 'Sir, another failure. Shouldn't we give up?' 'No. This isn't failure. I've just found one more way that doesn't work.' Edison never stopped believing. Eventually, a thin filament made from Japanese bamboo glowed for over 40 hours. A warm light came on in the lab. That night, the world's darkness was lit, little by little. 'Genius is 1% inspiration and 99% perspiration.' The words of Edison, who feared no failure and kept on striving, still live in people's hearts around the world.</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>見て ください／〜だったの!?／無事 解決</t>
+          <t>〜と決心した／くり返した／〜じゃない</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>真相を会話で。会話表現「あっ/えーっ/はは」。</t>
+          <t>失敗を恐れぬ努力。</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>犯人はカラス＝意外な落ち。</t>
+          <t>世界の夜を明るくした。</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>多声TTS:ナレーター/田中/清掃員/店長</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="165" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>L-M-005</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
+          <t>多声TTS:ナレーター/エジソン/助手</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="409.6" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>L-D-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>ミステリー</t>
+          <t>ドキュメンタリー</t>
         </is>
       </c>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>消えた最終電車</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>物語</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
+          <t>ヘレン・ケラーと先生</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>ドキュメンタリー</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>夜（よる）11時（じ）50分（ぷん）、駅員（えきいん）の 木村（きむら）さんは おかしな ことに 気（き）づいた。
-木村：あれ？ さっきまで ホームに いた 女（おんな）の 人（ひと）、どこへ 行（い）ったんだ…。
-終電（しゅうでん）は まだ 来（き）ていない。改札（かいさつ）も 通（とお）っていない。なのに、ホームには 誰（だれ）も いない。
-木村：かばんだけが、ベンチに 残（のこ）っている…。
-次（つぎ）の 朝（あさ）、かばんの 中（なか）から 一枚（いちまい）の 古（ふる）い 切符（きっぷ）が 見（み）つかった。日付（ひづけ）は——30年（ねん）前（まえ）だった。
-（つづく）</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>154</v>
+          <t>（ナレーション）目（め）が見（み）えず、耳（みみ）も聞（き）こえない少女（しょうじょ）がいた。ヘレン・ケラー。言葉（ことば）を知（し）らない彼女（かのじょ）の心（こころ）は、出口（でぐち）のない暗（くら）い闇（やみ）の中（なか）にあった。思（おも）い通（どお）りにならず、ヘレンは毎日（まいにち）あばれ、家族（かぞく）も困（こま）りはてていた。
+（ナレーション）そんなある日（ひ）、一人（ひとり）の家庭教師（かていきょうし）がやって来（き）た。サリバン先生（せんせい）である。
+サリバン：「あきらめません。わたしが、あなたに世界（せかい）の名前（なまえ）を教（おし）えます」。
+（ナレーション）先生（せんせい）は、ヘレンの手（て）のひらに、指（ゆび）で何度（なんど）も文字（もじ）を書（か）いた。コップ、人形（にんぎょう）、いす……。けれどヘレンには、それが「名前（なまえ）」だとわからない。根気（こんき）のいる日々（ひび）が続（つづ）いた。
+（ナレーション）ある朝（あさ）、二人（ふたり）は井戸（いど）のそばにいた。先生（せんせい）がヘレンの手（て）に、冷（つめ）たい水（みず）を流（なが）しながら、もう一方（いっぽう）の手（て）に「W-A-T-E-R」と書（か）いた。その瞬間（しゅんかん）、ヘレンの体（からだ）に電気（でんき）が走（はし）ったように、はっと動（うご）きが止（と）まった。「そうか……これが『水（みず）』なんだ！」。
+（ナレーション）世界（せかい）のすべてに名前（なまえ）があると知（し）った、その日（ひ）。ヘレンの暗（くら）い世界（せかい）に、光（ひかり）がさした。やがて彼女（かのじょ）は懸命（けんめい）に学（まな）び、大学（だいがく）を卒業（そつぎょう）した。
+（ナレーション）後（のち）にヘレンは、世界中（せかいじゅう）を旅（たび）して講演（こうえん）し、目（め）や耳（みみ）の不自由（ふじゆう）な人々（ひとびと）のために力（ちから）をつくした。「世界（せかい）は苦（くる）しみに満（み）ちているが、それを乗（の）りこえる力（ちから）にも満（み）ちている」。サリバン先生（せんせい）とヘレンの物語（ものがたり）は、同（おな）じ苦（くる）しみを持（も）つ世界中（せかいじゅう）の人々（ひとびと）に、今（いま）も希望（きぼう）を与（あた）え続（つづ）けている。</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>508</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>11:50 p.m. Station attendant Kimura noticed something strange. Kimura: Huh? The woman who was on the platform just now—where did she go...? The last train hasn't come yet. She didn't pass the gate. And yet, no one is on the platform. Kimura: Only a bag is left on the bench... The next morning, an old ticket was found inside the bag. The date was—30 years ago. (To be continued)</t>
+          <t>There was a girl who could neither see nor hear: Helen Keller. Knowing no words, her heart was in a dark gloom with no exit. Unable to make herself understood, Helen raged every day, and her family was at a loss. Then one day a tutor came—Miss Sullivan. 'I won't give up. I will teach you the names of the world.' The teacher wrote letters with her finger on Helen's palm, again and again—cup, doll, chair. But Helen couldn't grasp that these were 'names.' Patient days continued. One morning, the two were by a well. As the teacher let cold water flow over one of Helen's hands, she spelled 'W-A-T-E-R' on the other. In that instant, as if electricity ran through her, Helen froze. 'I see... this is water!' The day she learned that everything in the world has a name, light shone into her dark world. In time she studied hard, graduated from university, and became someone who gave hope to people worldwide who shared her struggle.</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>〜に 気づいた／なのに／〜だった</t>
+          <t>〜ません／〜ながら／〜と知った</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>続きが気になる導入。</t>
+          <t>闇に光がさした瞬間。</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>30年前の切符の謎。</t>
+          <t>学ぶ喜びと希望。</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>多声TTS:ナレーション/駅員</t>
+          <t>多声TTS:ナレーター/サリバン</t>
         </is>
       </c>
     </row>
@@ -2675,14 +3383,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -2695,12 +3403,11 @@
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="12" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="43.2" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
@@ -2772,497 +3479,34 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="420" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>L-D-001</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
+    <row r="2" ht="300" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>L-T-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>ドキュメンタリー</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr"/>
+          <t>昔話</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>カップラーメンの誕生</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>ドキュメンタリー</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>（ナレーション）戦後（せんご）の日本（にほん）。焼（や）け野原（のはら）が広（ひろ）がる寒（さむ）い夜（よる）、一軒（いっけん）の屋台（やたい）に長（なが）い行列（ぎょうれつ）ができていた。人々（ひとびと）は、温（あたた）かいラーメン一杯（いっぱい）を、ふるえながら待（ま）っていた。その光景（こうけい）を、安藤（あんどう）はじっと見（み）つめていた。
-安藤：「これほど多（おお）くの人（ひと）が、一杯（いっぱい）のラーメンを求（もと）めている。家（いえ）で、すぐに、手軽（てがる）に食（た）べられるラーメンを作（つく）れないだろうか」。
-（ナレーション）安藤（あんどう）は、自宅（じたく）の裏（うら）に小（ちい）さな小屋（こや）を建（た）て、たった一人（ひとり）で研究（けんきゅう）を始（はじ）めた。来（く）る日（ひ）も来（く）る日（ひ）も、麺（めん）づくりに明（あ）け暮（く）れる。だが、ゆでた麺（めん）はすぐにのびて、味（あじ）も落（お）ちてしまう。失敗（しっぱい）は何百回（なんびゃっかい）も続（つづ）いた。
-安藤：「どうすれば、長（なが）く保存（ほぞん）でき、湯（ゆ）をかけるだけで元（もと）に戻（もど）るんだ…」。
-（ナレーション）眠（ねむ）る時間（じかん）も惜（お）しんだ。見（み）かねた妻（つま）が、夜（よる）おそく台所（だいどころ）から声（こえ）をかけた。
-妻：「あなた、少（すこ）し休（やす）んだら？ 今日（きょう）は天（てん）ぷらを揚（あ）げましたよ」。
-（ナレーション）その時（とき）だった。安藤（あんどう）の目（め）が、油（あぶら）の中（なか）の天（てん）ぷらに釘付（くぎづ）けになった。衣（ころも）から、無数（むすう）の泡（あわ）が立（た）ちのぼっている。水分（すいぶん）が一気（いっき）に飛（と）んでいく――。「これだ！ 油（あぶら）で揚（あ）げれば麺（めん）は乾（かわ）き、無数（むすう）の穴（あな）に湯（ゆ）がしみ込（こ）めば、麺（めん）は元（もと）に戻（もど）る！」。
-（ナレーション）こうして一杯（いっぱい）のインスタントラーメンが生（う）まれた。さらに安藤（あんどう）は、世界（せかい）へ届（とど）けるため、器（うつわ）ごと食（た）べられる「カップ」を発明（はつめい）する。発売（はつばい）の日（ひ）、半信半疑（はんしんはんぎ）だった人々（ひとびと）は、湯（ゆ）を注（そそ）いで三分（さんぷん）、ふたを開（あ）けて笑顔（えがお）になった。一人（ひとり）の執念（しゅうねん）が、世界（せかい）の食卓（しょくたく）を永遠（えいえん）に変（か）えたのである。</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="n">
-        <v>537</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>Postwar Japan. On a cold night amid the burnt ruins, a long line formed at a single food stall. People waited, shivering, for one warm bowl of ramen. Ando watched intently. 'So many people long for a single bowl. Could I make ramen you can eat at home, quickly and easily?' He built a small shed behind his house and began researching alone. Day after day he toiled over noodles, but boiled noodles soon went soft and lost flavor. He failed hundreds of times. 'How can I make it keep, and return to normal with just hot water?' He begrudged even sleep. His worried wife called out late at night: 'Dear, why not rest? I fried tempura today.' That was the moment. Ando's eyes fixed on the tempura in the oil—countless bubbles rising from the batter, the moisture flying off. 'That's it! Fry the noodles and they dry; pour hot water into the tiny holes and they return.' Thus instant ramen was born. To reach the world, he also invented the edible 'cup.' On launch day, doubtful people poured hot water, waited three minutes, lifted the lid, and smiled. One man's tenacity changed dinner tables worldwide forever.</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>〜ないだろうか／〜だけで／〜ば 元に戻る</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>執念が世界を変えた発明。</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>失敗の先のひらめき。</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>多声TTS:ナレーター/安藤/妻</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="420" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>L-D-002</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>長文</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>ドキュメンタリー</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>新幹線――夢の超特急</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>ドキュメンタリー</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>（ナレーション）1964年（ねん）、東京（とうきょう）と大阪（おおさか）を結（むす）ぶ新幹線（しんかんせん）が走（はし）り始（はじ）めた。当時（とうじ）、時速（じそく）200キロを超（こ）える電車（でんしゃ）は、世界（せかい）のどこにも存在（そんざい）しなかった。
-技術者（ぎじゅつしゃ）：「そんなスピードは危険（きけん）だ。脱線（だっせん）したら、大事故（だいじこ）になる」。
-（ナレーション）多（おお）くの人（ひと）が、無理（むり）だと反対（はんたい）した。けれど、技術者（ぎじゅつしゃ）たちはあきらめなかった。彼（かれ）らは、空気（くうき）の力（ちから）、線路（せんろ）のカーブ、車輪（しゃりん）の揺（ゆ）れを、何度（なんど）も何度（なんど）も計算（けいさん）し直（なお）した。安全（あんぜん）のためなら、どんな小（ちい）さな問題（もんだい）も見逃（みのが）さなかった。
-技術者：「ここで妥協（だきょう）すれば、必（かなら）ず後（あと）で事故（じこ）が起（お）きる。とことんやろう」。
-（ナレーション）試験（しけん）と改良（かいりょう）の日々（ひび）。眠（ねむ）れない長（なが）い夜（よる）が続（つづ）いた。仲間（なかま）と知恵（ちえ）を出（だ）し合（あ）い、一（ひと）つずつ壁（かべ）を越（こ）えていく。そして迎（むか）えた開業（かいぎょう）の日（ひ）。白（しろ）と青（あお）の車両（しゃりょう）が、静（しず）かに、しかし力強（ちからづよ）くホームをすべり出（で）た。
-（ナレーション）新幹線（しんかんせん）は、一度（いちど）の事故（じこ）もなく、東京（とうきょう）から大阪（おおさか）まで走（はし）りきった。「夢（ゆめ）の超特急（ちょうとっきゅう）」は、日本（にほん）の誇（ほこ）りとなった。それは単（たん）なる速（はや）い電車（でんしゃ）ではない。不可能（ふかのう）を可能（かのう）に変（か）えた、技術者（ぎじゅつしゃ）たちの執念（しゅうねん）の結晶（けっしょう）だった。
-（ナレーション）かつて長（なが）い時間（じかん）がかかった東京（とうきょう）と大阪（おおさか）の間（あいだ）が、ぐっと近（ちか）くなった。仕事（しごと）でも旅行（りょこう）でも、日帰（ひがえ）りができる。新幹線（しんかんせん）は、人（ひと）と人（ひと）、町（まち）と町（まち）の距離（きょり）を、大（おお）きく縮（ちぢ）めたのだ。今（いま）も世界中（せかいじゅう）の高速鉄道（こうそくてつどう）が、この一本（いっぽん）の線路（せんろ）を手本（てほん）にし続（つづ）けている。</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="n">
-        <v>491</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>In 1964, the Shinkansen linking Tokyo and Osaka began to run. At the time, no train anywhere in the world exceeded 200 km/h. 'Such speed is dangerous. If it derails, there will be a terrible accident.' Many opposed it as impossible. But the engineers did not give up. They recalculated air resistance, track curves, and wheel vibration again and again. For safety, they overlooked no problem, however small. 'If we compromise here, an accident will surely come later. Let's see it through.' Days of testing and improvement; long sleepless nights. Sharing wisdom with colleagues, they cleared the walls one by one. Then came opening day. The white-and-blue cars slid quietly but powerfully from the platform. The Shinkansen ran the whole way from Tokyo to Osaka without a single accident. The 'dream super-express' became Japan's pride—not merely a fast train, but the crystallization of engineers' tenacity that turned the impossible into the possible. Even now, high-speed railways around the world look to this one line as their model.</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>〜を超える／〜のためなら／〜きった</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>不可能を可能にした執念。</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>反対を覆した技術の結晶。</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>多声TTS:ナレーター/技術者</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="420" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>L-D-003</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>長文</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>ドキュメンタリー</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>ライト兄弟、空へ</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>ドキュメンタリー</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>（ナレーション）100年（ねん）以上（いじょう）前（まえ）、アメリカの小（ちい）さな町（まち）に、自転車屋（じてんしゃや）を営（いとな）む二人（ふたり）の兄弟（きょうだい）がいた。ライト兄弟（きょうだい）である。当時（とうじ）、「人間（にんげん）が空（そら）を飛（と）ぶ」など、だれもが笑（わら）う夢物語（ゆめものがたり）だった。
-兄（あに）：「鳥（とり）は、どうやって風（かぜ）を受（う）け、体（からだ）を傾（かたむ）けて曲（ま）がっているんだろう」。
-（ナレーション）二人（ふたり）は来（く）る日（ひ）も来（く）る日（ひ）も、空（そら）をとぶ鳥（とり）を観察（かんさつ）した。翼（つばさ）の形（かたち）を作（つく）っては試（ため）し、こわれては、また作（つく）り直（なお）す。風（かぜ）の強（つよ）い丘（おか）で、何度（なんど）も地面（じめん）に たたきつけられた。それでも、二人（ふたり）の目（め）は、いつも空（そら）を見（み）ていた。
-弟（おとうと）：「兄（あに）さん、今度（こんど）こそ、風（かぜ）に乗（の）れる気（き）がする」。
-（ナレーション）1903年（ねん）の冷（つめ）たい冬（ふゆ）の朝（あさ）。強（つよ）い風（かぜ）の中（なか）、手作（てづく）りの飛行機（ひこうき）がエンジンの音（おと）を響（ひび）かせた。プロペラが回（まわ）り、機体（きたい）がゆっくりと動（うご）き出（だ）す。そして――ふわりと、車輪（しゃりん）が地面（じめん）を離（はな）れた。
-（ナレーション）飛（と）んだ時間（じかん）は、わずか12秒（びょう）。距離（きょり）は、たった36メートル。けれどそれは、人類（じんるい）が自分（じぶん）の力（ちから）で初（はじ）めて空（そら）を飛（と）んだ、歴史（れきし）が変（か）わった瞬間（しゅんかん）だった。
-（ナレーション）成功（せいこう）の裏（うら）には、何年（なんねん）もの地道（じみち）な努力（どりょく）があった。二人（ふたり）は、失敗（しっぱい）の記録（きろく）を一（ひと）つ残（のこ）らずノートに書（か）きとめ、つぎの工夫（くふう）に生（い）かしていったのだ。だれもが笑（わら）った夢（ゆめ）を、あきらめなかった二人（ふたり）。その小（ちい）さな12秒（びょう）から、世界中（せかいじゅう）の空（そら）の旅（たび）が始（はじ）まったのである。</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>473</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>More than a century ago, in a small American town, two brothers ran a bicycle shop: the Wright brothers. Back then, 'humans flying' was a fairy tale everyone laughed at. 'How do birds catch the wind and tilt their bodies to turn?' Day after day they watched birds in flight. They built wing shapes and tested them; when they broke, they rebuilt. On a windy hill they were dashed to the ground again and again. Yet their eyes were always on the sky. 'Brother, this time I feel we can ride the wind.' On a cold winter morning in 1903, in a strong wind, their handmade airplane roared. The propeller turned, the craft slowly moved—and then, gently, the wheels left the ground. The flight lasted just 12 seconds, only 36 meters. But it was the moment humanity first flew by its own power, and history changed. Two brothers who never gave up on a dream everyone mocked. From that tiny 12 seconds, the world's journeys through the sky began.</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>〜だろう／〜ては 〜直す／それでも</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>笑われた夢への挑戦。</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>12秒が歴史を変えた。</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>多声TTS:ナレーター/兄/弟</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="420" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>L-D-004</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>長文</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>ドキュメンタリー</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>エジソンと電球</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>ドキュメンタリー</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>（ナレーション）まだ電気（でんき）のない時代（じだい）。夜（よる）の暗（くら）やみを照（て）らすのは、ろうそくやランプの、小（ちい）さくゆれる炎（ほのお）だけだった。アメリカの発明家（はつめいか）エジソンは、決心（けっしん）した。「だれもが使（つか）える、長（なが）く明（あか）るい電球（でんきゅう）を作（つく）る」と。
-（ナレーション）光（ひか）る糸（いと）の材料（ざいりょう）を探（さが）して、エジソンは実験（じっけん）をくり返（かえ）した。木綿（もめん）、紙（かみ）、髪（かみ）の毛（け）――ありとあらゆるものを試（ため）したが、糸（いと）はすぐに燃（も）えつきてしまう。失敗（しっぱい）の数（かず）は、千回（せんかい）をこえた。
-助手（じょしゅ）：「先生（せんせい）、また失敗（しっぱい）です。もう、あきらめませんか」。
-エジソン：「いや。これは失敗（しっぱい）じゃない。『うまくいかない方法（ほうほう）』を、また一（ひと）つ見（み）つけただけさ」。
-（ナレーション）エジソンは、最後（さいご）まで信（しん）じることをやめなかった。やがて、日本（にほん）の竹（たけ）から作（つく）った細（ほそ）い糸（いと）が、なんと40時間（じかん）以上（いじょう）も光（ひか）り続（つづ）けた。研究室（けんきゅうしつ）に、あたたかな明（あ）かりがともった。
-（ナレーション）その夜（よる）、世界（せかい）の暗（くら）やみは、少（すこ）しずつ明（あか）るく照（て）らされていった。電球（でんきゅう）だけではない。エジソンは生涯（しょうがい）に千以上（せんいじょう）もの発明（はつめい）を世（よ）に残（のこ）した。その原動力（げんどうりょく）は、子（こ）どものころから変（か）わらない「なぜ？」という強（つよ）い好奇心（こうきしん）だった。
-（ナレーション）「天才（てんさい）とは、1パーセントのひらめきと、99パーセントの努力（どりょく）である」。失敗（しっぱい）を恐（おそ）れず、努力（どりょく）を続（つづ）けたエジソンの言葉（ことば）は、今（いま）も世界中（せかいじゅう）の人（ひと）の胸（むね）に生（い）きている。</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>479</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>In an age without electricity, the only thing lighting the darkness of night was the small, flickering flame of candles and lamps. The American inventor Edison resolved: 'I will make a long-lasting, bright bulb that anyone can use.' Searching for a glowing filament, Edison repeated experiments—cotton, paper, hair—he tried everything, but the thread burned out at once. His failures passed a thousand. 'Sir, another failure. Shouldn't we give up?' 'No. This isn't failure. I've just found one more way that doesn't work.' Edison never stopped believing. Eventually, a thin filament made from Japanese bamboo glowed for over 40 hours. A warm light came on in the lab. That night, the world's darkness was lit, little by little. 'Genius is 1% inspiration and 99% perspiration.' The words of Edison, who feared no failure and kept on striving, still live in people's hearts around the world.</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>〜と決心した／くり返した／〜じゃない</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>失敗を恐れぬ努力。</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>世界の夜を明るくした。</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>多声TTS:ナレーター/エジソン/助手</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="420" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>L-D-005</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>長文</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>ドキュメンタリー</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>ヘレン・ケラーと先生</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>ドキュメンタリー</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>（ナレーション）目（め）が見（み）えず、耳（みみ）も聞（き）こえない少女（しょうじょ）がいた。ヘレン・ケラー。言葉（ことば）を知（し）らない彼女（かのじょ）の心（こころ）は、出口（でぐち）のない暗（くら）い闇（やみ）の中（なか）にあった。思（おも）い通（どお）りにならず、ヘレンは毎日（まいにち）あばれ、家族（かぞく）も困（こま）りはてていた。
-（ナレーション）そんなある日（ひ）、一人（ひとり）の家庭教師（かていきょうし）がやって来（き）た。サリバン先生（せんせい）である。
-サリバン：「あきらめません。わたしが、あなたに世界（せかい）の名前（なまえ）を教（おし）えます」。
-（ナレーション）先生（せんせい）は、ヘレンの手（て）のひらに、指（ゆび）で何度（なんど）も文字（もじ）を書（か）いた。コップ、人形（にんぎょう）、いす……。けれどヘレンには、それが「名前（なまえ）」だとわからない。根気（こんき）のいる日々（ひび）が続（つづ）いた。
-（ナレーション）ある朝（あさ）、二人（ふたり）は井戸（いど）のそばにいた。先生（せんせい）がヘレンの手（て）に、冷（つめ）たい水（みず）を流（なが）しながら、もう一方（いっぽう）の手（て）に「W-A-T-E-R」と書（か）いた。その瞬間（しゅんかん）、ヘレンの体（からだ）に電気（でんき）が走（はし）ったように、はっと動（うご）きが止（と）まった。「そうか……これが『水（みず）』なんだ！」。
-（ナレーション）世界（せかい）のすべてに名前（なまえ）があると知（し）った、その日（ひ）。ヘレンの暗（くら）い世界（せかい）に、光（ひかり）がさした。やがて彼女（かのじょ）は懸命（けんめい）に学（まな）び、大学（だいがく）を卒業（そつぎょう）した。
-（ナレーション）後（のち）にヘレンは、世界中（せかいじゅう）を旅（たび）して講演（こうえん）し、目（め）や耳（みみ）の不自由（ふじゆう）な人々（ひとびと）のために力（ちから）をつくした。「世界（せかい）は苦（くる）しみに満（み）ちているが、それを乗（の）りこえる力（ちから）にも満（み）ちている」。サリバン先生（せんせい）とヘレンの物語（ものがたり）は、同（おな）じ苦（くる）しみを持（も）つ世界中（せかいじゅう）の人々（ひとびと）に、今（いま）も希望（きぼう）を与（あた）え続（つづ）けている。</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>508</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>There was a girl who could neither see nor hear: Helen Keller. Knowing no words, her heart was in a dark gloom with no exit. Unable to make herself understood, Helen raged every day, and her family was at a loss. Then one day a tutor came—Miss Sullivan. 'I won't give up. I will teach you the names of the world.' The teacher wrote letters with her finger on Helen's palm, again and again—cup, doll, chair. But Helen couldn't grasp that these were 'names.' Patient days continued. One morning, the two were by a well. As the teacher let cold water flow over one of Helen's hands, she spelled 'W-A-T-E-R' on the other. In that instant, as if electricity ran through her, Helen froze. 'I see... this is water!' The day she learned that everything in the world has a name, light shone into her dark world. In time she studied hard, graduated from university, and became someone who gave hope to people worldwide who shared her struggle.</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>〜ません／〜ながら／〜と知った</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>闇に光がさした瞬間。</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>学ぶ喜びと希望。</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>多声TTS:ナレーター/サリバン</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>タブ</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>カテゴリー</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>サブテーマ</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>形式</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>対象レベル(非表示)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>字数</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>英訳</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>キー表現</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ポイント</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>楽しさ・継続フック</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>備考(音声)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="300" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>L-T-001</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>長文</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>昔話</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
           <t>桃太郎</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -3275,7 +3519,7 @@
 （ナレーション）道（みち）の途中（とちゅう）で、犬（いぬ）、猿（さる）、きじが仲間（なかま）になりました。鬼（おに）ヶ島（しま）に着（つ）くと、おそろしい鬼（おに）たちが暴（あば）れています。桃太郎（ももたろう）たちは力（ちから）を合（あ）わせて勇敢（ゆうかん）に戦（たたか）い、ついに鬼（おに）を降参（こうさん）させました。鬼（おに）は奪（うば）った宝物（たからもの）を返（かえ）し、二度（にど）と悪（わる）いことをしないと約束（やくそく）しました。桃太郎（ももたろう）は宝物（たからもの）を持（も）ち帰（かえ）り、村（むら）のみんなと幸（しあわ）せに暮（く）らしました。</t>
         </is>
       </c>
-      <c r="I2" s="7" t="n">
+      <c r="I2" s="2" t="n">
         <v>303</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -3305,12 +3549,12 @@
       </c>
     </row>
     <row r="3" ht="315" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>L-T-002</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -3320,18 +3564,18 @@
           <t>昔話</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
           <t>浦島太郎</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -3344,7 +3588,7 @@
 （ナレーション）夢（ゆめ）のような日々（ひび）。けれど村（むら）が恋（こい）しくなった太郎（たろう）は、玉手箱（たまてばこ）を持（も）って帰（かえ）りました。ところが、村（むら）はすっかり変（か）わり、知（し）っている人（ひと）は一人（ひとり）もいません。竜宮城（りゅうぐうじょう）での数日（すうじつ）の間（あいだ）に、地上（ちじょう）では何百年（なんびゃくねん）も過（す）ぎていたのです。さびしさのあまり、太郎（たろう）が約束（やくそく）を忘（わす）れて箱（はこ）を開（あ）けると、白（しろ）い煙（けむり）がもくもくと出（で）て、太郎（たろう）はたちまち白髪（しらが）のおじいさんになってしまいました。</t>
         </is>
       </c>
-      <c r="I3" s="7" t="n">
+      <c r="I3" s="2" t="n">
         <v>351</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -3374,12 +3618,12 @@
       </c>
     </row>
     <row r="4" ht="300" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>L-T-003</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -3389,18 +3633,18 @@
           <t>昔話</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>かぐや姫</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -3413,7 +3657,7 @@
 （ナレーション）実（じつ）は、かぐや姫（ひめ）は月（つき）の世界（せかい）から来（き）た人（ひと）でした。満月（まんげつ）の夜（よる）、空（そら）から大勢（おおぜい）の使（つか）いが、光（ひかり）とともに姫（ひめ）を迎（むか）えに来（き）ました。おじいさんとおばあさんは泣（な）いて引（ひ）き止（と）めましたが、別（わか）れの時（とき）は来（き）てしまいます。姫（ひめ）は二人（ふたり）に深（ふか）く感謝（かんしゃ）し、別（わか）れを惜（お）しみながら、静（しず）かに天（てん）へのぼっていきました。</t>
         </is>
       </c>
-      <c r="I4" s="7" t="n">
+      <c r="I4" s="2" t="n">
         <v>329</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -3443,12 +3687,12 @@
       </c>
     </row>
     <row r="5" ht="345" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>L-T-004</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -3458,18 +3702,18 @@
           <t>昔話</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="inlineStr">
         <is>
           <t>鶴の恩返し</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
@@ -3484,7 +3728,7 @@
 （ナレーション）妻（つま）は一羽（いちわ）の鶴（つる）にもどり、何度（なんど）も振（ふ）り返（かえ）りながら、雪空（ゆきぞら）へ飛（と）び去（さ）っていきました。</t>
         </is>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="I5" s="2" t="n">
         <v>354</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -3514,12 +3758,12 @@
       </c>
     </row>
     <row r="6" ht="345" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>L-T-005</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
@@ -3529,18 +3773,18 @@
           <t>昔話</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="inlineStr">
         <is>
           <t>笠地蔵</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
@@ -3554,7 +3798,7 @@
 （ナレーション）その夜（よる）、ふしぎなことが起（お）こりました。明（あ）け方（がた）、外（そと）で重（おも）い物（もの）を置（お）くような音（おと）がします。戸（と）を開（あ）けると、米（こめ）やもち、おせちのごちそうが、山（やま）のように積（つ）まれていたのです。雪（ゆき）の上（うえ）には、六体（ろくたい）のお地蔵（じぞう）さまの足跡（あしあと）が残（のこ）っていました。親切（しんせつ）への、お礼（れい）だったのです。</t>
         </is>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="I6" s="2" t="n">
         <v>381</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -3580,6 +3824,352 @@
       <c r="N6" s="3" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/おじいさん</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>タブ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>カテゴリー</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>サブテーマ</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>形式</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>対象レベル(非表示)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>字数</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>英訳</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>キー表現</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ポイント</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>楽しさ・継続フック</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>備考(音声)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>L-R-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ニュース</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>桜が満開（国内）</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ニュース</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>おはようございます。今朝（けさ）の ニュースです。昨日（きのう）、東京（とうきょう）の 公園（こうえん）で 桜（さくら）が 満開（まんかい）に なりました。週末（しゅうまつ）は たくさんの 家族（かぞく）連（づ）れで にぎわいそうです。天気（てんき）も よく、お花見（はなみ）に ぴったりの 一日（いちにち）に なるでしょう。一方（いっぽう）、来週（らいしゅう）からは 少（すこ）し 寒（さむ）く なるという 予報（よほう）も 出（で）ています。体調（たいちょう）に 気（き）を つけて お過（す）ごしください。では、今日（きょう）も よい 一日を。</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>142</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Good morning. Here's this morning's news. Yesterday, the cherry blossoms reached full bloom in a Tokyo park. This weekend it should be crowded with families. The weather is good too—a perfect day for hanami. On the other hand, it's forecast to get a bit colder from next week. Please take care of your health. Have a good day.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>今朝の ニュース／満開／〜そうです／一方</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>ニュースの流れと話題転換「一方」。</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>季節感で“朝の習慣”に。</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1話者・アナウンサー調</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>L-R-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ニュース</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>全国の天気（天気）</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>天気予報</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>全国（ぜんこく）の 天気（てんき）です。今日（きょう）は 西日本（にしにほん）で 晴（は）れますが、東日本（ひがしにほん）は 午後（ごご）から 雲（くも）が 多（おお）く なるでしょう。夜（よる）には 雨（あめ）が 降（ふ）る 所（ところ）も あります。傘（かさ）を 持（も）って 出（で）かけると 安心（あんしん）です。気温（きおん）は 各地（かくち）で 20度（ど）前後（ぜんご）、過（す）ごしやすい 一日（いちにち）に なりそうです。</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>97</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Here's the nationwide weather. Today it's sunny in western Japan, but in eastern Japan clouds will increase from the afternoon. Some areas may see rain at night. It's safer to take an umbrella. Temperatures will be around 20 degrees—a comfortable day.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>晴れます／雲が 多く なる／傘を 持って</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>全国天気の聞き取り（地域差）。</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>「傘いる?」毎朝役立つ。</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1話者・予報士調</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>L-R-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ニュース</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>海外のニュース（国際）</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ニュース</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>こんにちは、国際（こくさい）ニュースです。アメリカで、新（あたら）しい 技術（ぎじゅつ）の 会議（かいぎ）が 開（ひら）かれました。世界中（せかいじゅう）から たくさんの 研究者（けんきゅうしゃ）が 集（あつ）まりました。日本（にほん）からも 多（おお）くの 企業（きぎょう）が 参加（さんか）し、注目（ちゅうもく）を 集（あつ）めています。来年（らいねん）は アジアでも 同（おな）じ 会議が 開かれる 予定（よてい）です。</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>105</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Hello, international news. In the U.S., a conference on new technology was held. Many researchers gathered from around the world. Many companies from Japan also took part and are drawing attention. Next year, the same conference is scheduled to be held in Asia too.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>国際ニュース／〜が 開かれました／注目を 集めています</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>国際ニュースの定型表現。</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>世界とつながる話題。</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1話者・アナウンサー調</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>L-R-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ニュース</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>サッカーの試合（スポーツ）</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ニュース</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>スポーツの ニュースです。昨日（きのう）、サッカーの 試合（しあい）が ありました。日本（にほん）チームは 2対（たい）1で 勝（か）ちました。最後（さいご）の ゴールは、とても すばらしかったです。スタジアムの ファンは 大（おお）きな 声（こえ）で 応援（おうえん）しました。次（つぎ）の 試合は 来週（らいしゅう）の 土曜日（どようび）です。楽（たの）しみですね。</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>109</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Sports news. Yesterday there was a soccer match. The Japan team won 2 to 1. The final goal was wonderful. Fans in the stadium cheered loudly. The next match is next Saturday. Something to look forward to.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2対1で 勝ちました／応援しました／楽しみですね</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>スポーツ結果(点数/勝敗)の聞き取り。</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>勝利の興奮。</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1話者・アナウンサー調</t>
         </is>
       </c>
     </row>

--- a/長文.xlsx
+++ b/長文.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="39300" yWindow="345" windowWidth="27960" windowHeight="14955" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="29865" yWindow="210" windowWidth="37410" windowHeight="14955" tabRatio="600" firstSheet="0" activeTab="7" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="まとめ" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,14 +20,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="昔話" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,9 +40,6 @@
       <family val="2"/>
       <b val="1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -58,7 +55,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -66,61 +63,22 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -495,309 +453,299 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="2" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+    <row r="1" ht="34.05" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>テーマ</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>日本生活スタート</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>日本一人旅</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>カイの日常</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>カイの休憩室</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>ニュース</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>お便り相談室</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>ゲストインタビュー</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>2人のフリートーク</t>
         </is>
       </c>
-      <c r="J1" s="12" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>ミステリー</t>
         </is>
       </c>
-      <c r="K1" s="12" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="L1" s="12" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>昔話</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+    <row r="2" ht="19.95" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>形式</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>独話</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>独話</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>独話</t>
         </is>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>独話</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>独話</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>独話</t>
         </is>
       </c>
-      <c r="H2" s="12" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>対話</t>
         </is>
       </c>
-      <c r="I2" s="12" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>対話</t>
         </is>
       </c>
-      <c r="J2" s="12" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>対話/独話</t>
         </is>
       </c>
-      <c r="K2" s="12" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>独話</t>
         </is>
       </c>
-      <c r="L2" s="12" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>独話</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+    <row r="3" ht="19.95" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>タイトル数</t>
         </is>
       </c>
-      <c r="B3" s="12" t="n">
+      <c r="B3" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C3" s="12" t="n">
+      <c r="C3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="12" t="n">
+      <c r="D3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="12" t="n">
+      <c r="E3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="12" t="n">
+      <c r="F3" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G3" s="12" t="n">
+      <c r="G3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="12" t="n">
+      <c r="H3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="12" t="n">
+      <c r="I3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="12" t="n">
+      <c r="J3" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="K3" s="12" t="n">
+      <c r="K3" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="L3" s="12" t="n">
+      <c r="L3" s="4" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="12" t="n">
+    <row r="4" ht="19.95" customHeight="1">
+      <c r="A4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>◯</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr"/>
-      <c r="D4" s="13" t="inlineStr"/>
-      <c r="E4" s="13" t="inlineStr"/>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>◯</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>◯</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr"/>
-      <c r="I4" s="13" t="inlineStr"/>
-      <c r="J4" s="13" t="inlineStr"/>
-      <c r="K4" s="13" t="inlineStr"/>
-      <c r="L4" s="13" t="inlineStr"/>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="12" t="n">
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="19.95" customHeight="1">
+      <c r="A5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>◯</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>◯</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>◯</t>
         </is>
       </c>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="inlineStr"/>
-      <c r="K5" s="13" t="inlineStr"/>
-      <c r="L5" s="13" t="inlineStr"/>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="n">
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="19.95" customHeight="1">
+      <c r="A6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>◯</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>◯</t>
         </is>
       </c>
-      <c r="G6" s="13" t="n"/>
-      <c r="H6" s="13" t="n"/>
-      <c r="I6" s="13" t="n"/>
-      <c r="J6" s="13" t="inlineStr"/>
-      <c r="K6" s="13" t="inlineStr"/>
-      <c r="L6" s="13" t="inlineStr"/>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="12" t="n">
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="19.95" customHeight="1">
+      <c r="A7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>◯</t>
         </is>
       </c>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="13" t="n"/>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>◯</t>
         </is>
       </c>
-      <c r="G7" s="13" t="n"/>
-      <c r="H7" s="13" t="n"/>
-      <c r="I7" s="13" t="n"/>
-      <c r="J7" s="13" t="inlineStr"/>
-      <c r="K7" s="13" t="inlineStr"/>
-      <c r="L7" s="13" t="inlineStr"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="12" t="n">
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="19.95" customHeight="1">
+      <c r="A8" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>◯</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="13" t="n"/>
-      <c r="H8" s="13" t="n"/>
-      <c r="I8" s="13" t="n"/>
-      <c r="J8" s="13" t="inlineStr"/>
-      <c r="K8" s="13" t="inlineStr"/>
-      <c r="L8" s="13" t="inlineStr"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -823,435 +771,433 @@
     <col width="64" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="52" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="13"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="11" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>タブ</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>カテゴリー</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>サブテーマ</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>形式</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>対象レベル(非表示)</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>字数</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>英訳</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>キー表現</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>ポイント</t>
         </is>
       </c>
-      <c r="M1" s="11" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>楽しさ・継続フック</t>
         </is>
       </c>
-      <c r="N1" s="11" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>備考(音声)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="184" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="184.05" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>L-M-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>ミステリー</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>消えた駅弁の謎 第1話：駅で事件発生</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>（ナレーション）東京駅（とうきょうえき）の 有名（ゆうめい）な 駅弁屋（えきべんや）で 事件（じけん）が 起（お）きた。
-店長（てんちょう）：たいへんだ！ 一番（いちばん）人気（にんき）の「うみの幸（さち）弁当（べんとう）」が、10個（こ）も 消（き）えてる！
+女（店長）：たいへんだ！ 一番（いちばん）人気（にんき）の「うみの幸（さち）弁当（べんとう）」が、10個（こ）も 消（き）えてる！
 駅員（えきいん）の明智（あけち）：鍵（かぎ）は かかっていたんですよね？
-店長：はい、朝（あさ）まで しっかり…。
-明智：おかしいな。鍵（かぎ）が かかっていたのに、どうやって…？
+女（店長）：はい、朝（あさ）まで しっかり…。
+男（明智）：おかしいな。鍵（かぎ）が かかっていたのに、どうやって…？
 （ナレーション）明智（あけち）さんは 考（かんが）えた。これは ただの どろぼうでは ないかもしれない。</t>
         </is>
       </c>
-      <c r="I2" s="3" t="n">
-        <v>134</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="I2" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>(Narration) An incident occurred at a famous ekiben shop in Tokyo Station. / Manager: This is terrible! Ten of our most popular 'Sea Bounty Bento' have vanished! / Akechi (staff): The door was locked, right? / Manager: Yes, firmly until morning... / Akechi: Strange. The door was locked, so how...? / (Narration) Akechi thought. This might not be an ordinary thief.</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>たいへんだ／〜んですよね／どうやって…?</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>事件の発端を会話で（密室の謎）。</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>続きが気になる第1話。</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/店長/田中</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="169" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="184.05" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>L-M-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>ミステリー</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>消えた駅弁の謎 第2話：証言を聞く</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>対話</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>明智（あけち）：すみません、今朝（けさ）、何（なに）か 見（み）ませんでしたか。
-掃除（そうじ）の人：5時（じ）ごろ、白（しろ）い 服（ふく）の 人（ひと）を 見（み）ましたよ。
-明智：白い 服…。ありがとうございます。
-コーヒー店（てん）の人：そういえば、変（へん）な 音（おと）が しましたね。バサバサっと。
-明智：バサバサ？
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>男（明智）：すみません、今朝（けさ）、何（なに）か 見（み）ませんでしたか。
+女（掃除の人）：5時（じ）ごろ、白（しろ）い 服（ふく）の 人（ひと）を 見（み）ましたよ。
+男（明智）：白い 服…。ありがとうございます。
+女（コーヒー店の人）：そういえば、変（へん）な 音（おと）が しましたね。バサバサっと。
+男（明智）：バサバサ？
 （ナレーション）でも、防犯（ぼうはん）カメラには だれも 映（うつ）っていない。
-明智：（首（くび）を かしげて）うーん、おかしいなあ…。</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>121</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+男（明智）：（首（くび）を かしげて）うーん、おかしいなあ…。</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>129</v>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>Akechi: Excuse me, did you see anything this morning? / Cleaner: Around 5, I saw someone in white clothes. / Akechi: White clothes... Thank you. / Coffee-shop worker: Come to think of it, there was a strange sound. A flapping sound. / Akechi: Flapping? / (Narration) But the security camera showed no one. / Akechi: (tilting his head) Hmm, that's strange...</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>見ませんでしたか／そういえば／うーん</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>証言の会話と矛盾。会話表現「そういえば/うーん」。</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="6" t="inlineStr">
         <is>
           <t>謎が深まる。</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="6" t="inlineStr">
         <is>
           <t>多声TTS:田中/証人たち/ナレーター</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="154" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="154.05" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>L-M-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>ミステリー</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>消えた駅弁の謎 第3話：容疑者登場</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>対話</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>（ナレーション）次（つぎ）の 日（ひ）、明智（あけち）さんは 白（しろ）い 服（ふく）の 男（おとこ）を 見（み）つけた。駅（えき）の 清掃員（せいそういん）だ。
-明智：あの 朝（あさ）、何（なに）を していましたか。
-清掃員：私（わたし）は ただ、ゴミを 集（あつ）めていただけですよ。
+男（明智）：あの 朝（あさ）、何（なに）を していましたか。
+女（清掃員）：私（わたし）は ただ、ゴミを 集（あつ）めていただけですよ。
 （ナレーション）そのとき、男（おとこ）の カバンから 弁当（べんとう）の 包（つつ）み紙（がみ）が ひらり、と 落（お）ちた。
-明智：（目（め）を 光（ひか）らせて）…これは？
-清掃員：えっ、いや、これは…！</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>112</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+男（明智）：（目（め）を 光（ひか）らせて）…これは？
+女（清掃員）：えっ、いや、これは…！</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>128</v>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>(Narration) The next day, Akechi found the man in white—a station cleaner. / Akechi: What were you doing that morning? / Cleaner: I was just collecting trash. / (Narration) Just then, a bento wrapper fluttered out of the man's bag. / Akechi: (eyes flashing) ...What's this? / Cleaner: Huh, no, this is...!</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>〜だけですよ／これは？／えっ、いや</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>容疑者への会話と証拠。会話表現「〜だけですよ/えっ、いや」。</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>犯人か?の緊張。</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/田中/清掃員</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="199" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5" ht="199.05" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>L-M-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>ミステリー</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>消えた駅弁の謎 第4話：真犯人は？</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>清掃員：それは、私（わたし）が 拾（ひろ）った ゴミです。本当（ほんとう）です！
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>女（清掃員）：それは、私（わたし）が 拾（ひろ）った ゴミです。本当（ほんとう）です！
 （ナレーション）明智（あけち）さんは 防犯（ぼうはん）カメラを もう一度（いちど）見（み）た。すると、屋根（やね）の すきまから…
-明智：あっ！ 見（み）て ください。大（おお）きな カラスが、弁当（べんとう）を 運（はこ）んでる！
-店長：えーっ！ 犯人（はんにん）は カラス だったの！？
+男（明智）：あっ！ 見（み）て ください。大（おお）きな カラスが、弁当（べんとう）を 運（はこ）んでる！
+女（店長）：えーっ！ 犯人（はんにん）は カラス だったの！？
 （ナレーション）みんな 大笑（おおわら）い。鍵（かぎ）の 謎（なぞ）は、屋根（やね）の 小（ちい）さな 窓（まど）だったのだ。
-明智：はは、事件（じけん）は 無事（ぶじ）解決（かいけつ）、ですね。</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>132</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
+男（明智）：はは、事件（じけん）は 無事（ぶじ）解決（かいけつ）、ですね。</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>148</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>Cleaner: That's trash I picked up. It's true! / (Narration) Akechi watched the security camera again. Then, through a gap in the roof... / Akechi: Ah! Look! A big crow is carrying the bento! / Manager: Whaaat! The culprit was a crow?! / (Narration) Everyone burst out laughing. The mystery of the lock was a small window in the roof. / Akechi: Haha, case closed.</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>見て ください／〜だったの!?／無事 解決</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr">
         <is>
           <t>真相を会話で。会話表現「あっ/えーっ/はは」。</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" s="6" t="inlineStr">
         <is>
           <t>犯人はカラス＝意外な落ち。</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="6" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/田中/清掃員/店長</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="184" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="6" ht="184.05" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>L-M-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>ミステリー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>消えた最終電車</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>夜（よる）11時（じ）50分（ぷん）、駅員（えきいん）の 木村（きむら）さんは おかしな ことに 気（き）づいた。
-木村：あれ？ さっきまで ホームに いた 女（おんな）の 人（ひと）、どこへ 行（い）ったんだ…。
+男（木村）：あれ？ さっきまで ホームに いた 女（おんな）の 人（ひと）、どこへ 行（い）ったんだ…。
 終電（しゅうでん）は まだ 来（き）ていない。改札（かいさつ）も 通（とお）っていない。なのに、ホームには 誰（だれ）も いない。
-木村：かばんだけが、ベンチに 残（のこ）っている…。
+男（木村）：かばんだけが、ベンチに 残（のこ）っている…。
 次（つぎ）の 朝（あさ）、かばんの 中（なか）から 一枚（いちまい）の 古（ふる）い 切符（きっぷ）が 見（み）つかった。日付（ひづけ）は——30年（ねん）前（まえ）だった。
 （つづく）</t>
         </is>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" s="6" t="n">
         <v>148</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>11:50 p.m. Station attendant Kimura noticed something strange. Kimura: Huh? The woman who was on the platform just now—where did she go...? The last train hasn't come yet. She didn't pass the gate. And yet, no one is on the platform. Kimura: Only a bag is left on the bench... The next morning, an old ticket was found inside the bag. The date was—30 years ago. (To be continued)</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>〜に 気づいた／なのに／〜だった</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
         <is>
           <t>続きが気になる導入。</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="M6" s="6" t="inlineStr">
         <is>
           <t>30年前の切符の謎。</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>多声TTS:ナレーション/駅員</t>
         </is>
@@ -1281,440 +1227,438 @@
     <col width="64" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="52" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="13"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="11" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>タブ</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>カテゴリー</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>サブテーマ</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>形式</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>対象レベル(非表示)</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>字数</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>英訳</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>キー表現</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>ポイント</t>
         </is>
       </c>
-      <c r="M1" s="11" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>楽しさ・継続フック</t>
         </is>
       </c>
-      <c r="N1" s="11" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>備考(音声)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="409" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="409.05" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>L-D-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>カップラーメンの誕生</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>（ナレーション）戦後（せんご）の日本（にほん）。焼（や）け野原（のはら）が広（ひろ）がる寒（さむ）い夜（よる）、一軒（いっけん）の屋台（やたい）に長（なが）い行列（ぎょうれつ）ができていた。人々（ひとびと）は、温（あたた）かいラーメン一杯（いっぱい）を、ふるえながら待（ま）っていた。その光景（こうけい）を、安藤（あんどう）はじっと見（み）つめていた。
-安藤：「これほど多（おお）くの人（ひと）が、一杯（いっぱい）のラーメンを求（もと）めている。家（いえ）で、すぐに、手軽（てがる）に食（た）べられるラーメンを作（つく）れないだろうか」。
+男（安藤）：「これほど多（おお）くの人（ひと）が、一杯（いっぱい）のラーメンを求（もと）めている。家（いえ）で、すぐに、手軽（てがる）に食（た）べられるラーメンを作（つく）れないだろうか」。
 （ナレーション）安藤（あんどう）は、自宅（じたく）の裏（うら）に小（ちい）さな小屋（こや）を建（た）て、たった一人（ひとり）で研究（けんきゅう）を始（はじ）めた。来（く）る日（ひ）も来（く）る日（ひ）も、麺（めん）づくりに明（あ）け暮（く）れる。だが、ゆでた麺（めん）はすぐにのびて、味（あじ）も落（お）ちてしまう。失敗（しっぱい）は何百回（なんびゃっかい）も続（つづ）いた。
-安藤：「どうすれば、長（なが）く保存（ほぞん）でき、湯（ゆ）をかけるだけで元（もと）に戻（もど）るんだ…」。
+男（安藤）：「どうすれば、長（なが）く保存（ほぞん）でき、湯（ゆ）をかけるだけで元（もと）に戻（もど）るんだ…」。
 （ナレーション）眠（ねむ）る時間（じかん）も惜（お）しんだ。見（み）かねた妻（つま）が、夜（よる）おそく台所（だいどころ）から声（こえ）をかけた。
-妻：「あなた、少（すこ）し休（やす）んだら？ 今日（きょう）は天（てん）ぷらを揚（あ）げましたよ」。
+女（妻）：「あなた、少（すこ）し休（やす）んだら？ 今日（きょう）は天（てん）ぷらを揚（あ）げましたよ」。
 （ナレーション）その時（とき）だった。安藤（あんどう）の目（め）が、油（あぶら）の中（なか）の天（てん）ぷらに釘付（くぎづ）けになった。衣（ころも）から、無数（むすう）の泡（あわ）が立（た）ちのぼっている。水分（すいぶん）が一気（いっき）に飛（と）んでいく――。「これだ！ 油（あぶら）で揚（あ）げれば麺（めん）は乾（かわ）き、無数（むすう）の穴（あな）に湯（ゆ）がしみ込（こ）めば、麺（めん）は元（もと）に戻（もど）る！」。
 （ナレーション）こうして一杯（いっぱい）のインスタントラーメンが生（う）まれた。さらに安藤（あんどう）は、世界（せかい）へ届（とど）けるため、器（うつわ）ごと食（た）べられる「カップ」を発明（はつめい）する。発売（はつばい）の日（ひ）、半信半疑（はんしんはんぎ）だった人々（ひとびと）は、湯（ゆ）を注（そそ）いで三分（さんぷん）、ふたを開（あ）けて笑顔（えがお）になった。一人（ひとり）の執念（しゅうねん）が、世界（せかい）の食卓（しょくたく）を永遠（えいえん）に変（か）えたのである。</t>
         </is>
       </c>
-      <c r="I2" s="3" t="n">
-        <v>529</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="I2" s="6" t="n">
+        <v>569</v>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>Postwar Japan. On a cold night amid the burnt ruins, a long line formed at a single food stall. People waited, shivering, for one warm bowl of ramen. Ando watched intently. 'So many people long for a single bowl. Could I make ramen you can eat at home, quickly and easily?' He built a small shed behind his house and began researching alone. Day after day he toiled over noodles, but boiled noodles soon went soft and lost flavor. He failed hundreds of times. 'How can I make it keep, and return to normal with just hot water?' He begrudged even sleep. His worried wife called out late at night: 'Dear, why not rest? I fried tempura today.' That was the moment. Ando's eyes fixed on the tempura in the oil—countless bubbles rising from the batter, the moisture flying off. 'That's it! Fry the noodles and they dry; pour hot water into the tiny holes and they return.' Thus instant ramen was born. To reach the world, he also invented the edible 'cup.' On launch day, doubtful people poured hot water, waited three minutes, lifted the lid, and smiled. One man's tenacity changed dinner tables worldwide forever.</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>〜ないだろうか／〜だけで／〜ば 元に戻る</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>執念が世界を変えた発明。</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>失敗の先のひらめき。</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/安藤/妻</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="409" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="409.05" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>L-D-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>新幹線――夢の超特急</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>（ナレーション）1964年（ねん）、東京（とうきょう）と大阪（おおさか）を結（むす）ぶ新幹線（しんかんせん）が走（はし）り始（はじ）めた。当時（とうじ）、時速（じそく）200キロを超（こ）える電車（でんしゃ）は、世界（せかい）のどこにも存在（そんざい）しなかった。
-技術者（ぎじゅつしゃ）：「そんなスピードは危険（きけん）だ。脱線（だっせん）したら、大事故（だいじこ）になる」。
+女（技術者）：「そんなスピードは危険（きけん）だ。脱線（だっせん）したら、大事故（だいじこ）になる」。
 （ナレーション）多（おお）くの人（ひと）が、無理（むり）だと反対（はんたい）した。けれど、技術者（ぎじゅつしゃ）たちはあきらめなかった。彼（かれ）らは、空気（くうき）の力（ちから）、線路（せんろ）のカーブ、車輪（しゃりん）の揺（ゆ）れを、何度（なんど）も何度（なんど）も計算（けいさん）し直（なお）した。安全（あんぜん）のためなら、どんな小（ちい）さな問題（もんだい）も見逃（みのが）さなかった。
-技術者：「ここで妥協（だきょう）すれば、必（かなら）ず後（あと）で事故（じこ）が起（お）きる。とことんやろう」。
+女（技術者）：「ここで妥協（だきょう）すれば、必（かなら）ず後（あと）で事故（じこ）が起（お）きる。とことんやろう」。
 （ナレーション）試験（しけん）と改良（かいりょう）の日々（ひび）。眠（ねむ）れない長（なが）い夜（よる）が続（つづ）いた。仲間（なかま）と知恵（ちえ）を出（だ）し合（あ）い、一（ひと）つずつ壁（かべ）を越（こ）えていく。そして迎（むか）えた開業（かいぎょう）の日（ひ）。白（しろ）と青（あお）の車両（しゃりょう）が、静（しず）かに、しかし力強（ちからづよ）くホームをすべり出（で）た。
 （ナレーション）新幹線（しんかんせん）は、一度（いちど）の事故（じこ）もなく、東京（とうきょう）から大阪（おおさか）まで走（はし）りきった。「夢（ゆめ）の超特急（ちょうとっきゅう）」は、日本（にほん）の誇（ほこ）りとなった。それは単（たん）なる速（はや）い電車（でんしゃ）ではない。不可能（ふかのう）を可能（かのう）に変（か）えた、技術者（ぎじゅつしゃ）たちの執念（しゅうねん）の結晶（けっしょう）だった。
 （ナレーション）かつて長（なが）い時間（じかん）がかかった東京（とうきょう）と大阪（おおさか）の間（あいだ）が、ぐっと近（ちか）くなった。仕事（しごと）でも旅行（りょこう）でも、日帰（ひがえ）りができる。新幹線（しんかんせん）は、人（ひと）と人（ひと）、町（まち）と町（まち）の距離（きょり）を、大（おお）きく縮（ちぢ）めたのだ。今（いま）も世界中（せかいじゅう）の高速鉄道（こうそくてつどう）が、この一本（いっぽん）の線路（せんろ）を手本（てほん）にし続（つづ）けている。</t>
         </is>
       </c>
-      <c r="I3" s="3" t="n">
-        <v>483</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="I3" s="6" t="n">
+        <v>523</v>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>In 1964, the Shinkansen linking Tokyo and Osaka began to run. At the time, no train anywhere in the world exceeded 200 km/h. 'Such speed is dangerous. If it derails, there will be a terrible accident.' Many opposed it as impossible. But the engineers did not give up. They recalculated air resistance, track curves, and wheel vibration again and again. For safety, they overlooked no problem, however small. 'If we compromise here, an accident will surely come later. Let's see it through.' Days of testing and improvement; long sleepless nights. Sharing wisdom with colleagues, they cleared the walls one by one. Then came opening day. The white-and-blue cars slid quietly but powerfully from the platform. The Shinkansen ran the whole way from Tokyo to Osaka without a single accident. The 'dream super-express' became Japan's pride—not merely a fast train, but the crystallization of engineers' tenacity that turned the impossible into the possible. Even now, high-speed railways around the world look to this one line as their model.</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>〜を超える／〜のためなら／〜きった</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>不可能を可能にした執念。</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="6" t="inlineStr">
         <is>
           <t>反対を覆した技術の結晶。</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="6" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/技術者</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="409" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="409.05" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>L-D-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>ライト兄弟、空へ</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>（ナレーション）100年（ねん）以上（いじょう）前（まえ）、アメリカの小（ちい）さな町（まち）に、自転車屋（じてんしゃや）を営（いとな）む二人（ふたり）の兄弟（きょうだい）がいた。ライト兄弟（きょうだい）である。当時（とうじ）、「人間（にんげん）が空（そら）を飛（と）ぶ」など、だれもが笑（わら）う夢物語（ゆめものがたり）だった。
-兄（あに）：「鳥（とり）は、どうやって風（かぜ）を受（う）け、体（からだ）を傾（かたむ）けて曲（ま）がっているんだろう」。
+男（兄）：「鳥（とり）は、どうやって風（かぜ）を受（う）け、体（からだ）を傾（かたむ）けて曲（ま）がっているんだろう」。
 （ナレーション）二人（ふたり）は来（く）る日（ひ）も来（く）る日（ひ）も、空（そら）をとぶ鳥（とり）を観察（かんさつ）した。翼（つばさ）の形（かたち）を作（つく）っては試（ため）し、こわれては、また作（つく）り直（なお）す。風（かぜ）の強（つよ）い丘（おか）で、何度（なんど）も地面（じめん）に たたきつけられた。それでも、二人（ふたり）の目（め）は、いつも空（そら）を見（み）ていた。
-弟（おとうと）：「兄（あに）さん、今度（こんど）こそ、風（かぜ）に乗（の）れる気（き）がする」。
+男（弟）：「兄（あに）さん、今度（こんど）こそ、風（かぜ）に乗（の）れる気（き）がする」。
 （ナレーション）1903年（ねん）の冷（つめ）たい冬（ふゆ）の朝（あさ）。強（つよ）い風（かぜ）の中（なか）、手作（てづく）りの飛行機（ひこうき）がエンジンの音（おと）を響（ひび）かせた。プロペラが回（まわ）り、機体（きたい）がゆっくりと動（うご）き出（だ）す。そして――ふわりと、車輪（しゃりん）が地面（じめん）を離（はな）れた。
 （ナレーション）飛（と）んだ時間（じかん）は、わずか12秒（びょう）。距離（きょり）は、たった36メートル。けれどそれは、人類（じんるい）が自分（じぶん）の力（ちから）で初（はじ）めて空（そら）を飛（と）んだ、歴史（れきし）が変（か）わった瞬間（しゅんかん）だった。
 （ナレーション）成功（せいこう）の裏（うら）には、何年（なんねん）もの地道（じみち）な努力（どりょく）があった。二人（ふたり）は、失敗（しっぱい）の記録（きろく）を一（ひと）つ残（のこ）らずノートに書（か）きとめ、つぎの工夫（くふう）に生（い）かしていったのだ。だれもが笑（わら）った夢（ゆめ）を、あきらめなかった二人（ふたり）。その小（ちい）さな12秒（びょう）から、世界中（せかいじゅう）の空（そら）の旅（たび）が始（はじ）まったのである。</t>
         </is>
       </c>
-      <c r="I4" s="3" t="n">
-        <v>469</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="I4" s="6" t="n">
+        <v>509</v>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>More than a century ago, in a small American town, two brothers ran a bicycle shop: the Wright brothers. Back then, 'humans flying' was a fairy tale everyone laughed at. 'How do birds catch the wind and tilt their bodies to turn?' Day after day they watched birds in flight. They built wing shapes and tested them; when they broke, they rebuilt. On a windy hill they were dashed to the ground again and again. Yet their eyes were always on the sky. 'Brother, this time I feel we can ride the wind.' On a cold winter morning in 1903, in a strong wind, their handmade airplane roared. The propeller turned, the craft slowly moved—and then, gently, the wheels left the ground. The flight lasted just 12 seconds, only 36 meters. But it was the moment humanity first flew by its own power, and history changed. Two brothers who never gave up on a dream everyone mocked. From that tiny 12 seconds, the world's journeys through the sky began.</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>〜だろう／〜ては 〜直す／それでも</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>笑われた夢への挑戦。</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>12秒が歴史を変えた。</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/兄/弟</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="409" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5" ht="409.05" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>L-D-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>エジソンと電球</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>（ナレーション）まだ電気（でんき）のない時代（じだい）。夜（よる）の暗（くら）やみを照（て）らすのは、ろうそくやランプの、小（ちい）さくゆれる炎（ほのお）だけだった。アメリカの発明家（はつめいか）エジソンは、決心（けっしん）した。「だれもが使（つか）える、長（なが）く明（あか）るい電球（でんきゅう）を作（つく）る」と。
 （ナレーション）光（ひか）る糸（いと）の材料（ざいりょう）を探（さが）して、エジソンは実験（じっけん）をくり返（かえ）した。木綿（もめん）、紙（かみ）、髪（かみ）の毛（け）――ありとあらゆるものを試（ため）したが、糸（いと）はすぐに燃（も）えつきてしまう。失敗（しっぱい）の数（かず）は、千回（せんかい）をこえた。
-助手（じょしゅ）：「先生（せんせい）、また失敗（しっぱい）です。もう、あきらめませんか」。
-エジソン：「いや。これは失敗（しっぱい）じゃない。『うまくいかない方法（ほうほう）』を、また一（ひと）つ見（み）つけただけさ」。
+女（助手）：「先生（せんせい）、また失敗（しっぱい）です。もう、あきらめませんか」。
+男（エジソン）：「いや。これは失敗（しっぱい）じゃない。『うまくいかない方法（ほうほう）』を、また一（ひと）つ見（み）つけただけさ」。
 （ナレーション）エジソンは、最後（さいご）まで信（しん）じることをやめなかった。やがて、日本（にほん）の竹（たけ）から作（つく）った細（ほそ）い糸（いと）が、なんと40時間（じかん）以上（いじょう）も光（ひか）り続（つづ）けた。研究室（けんきゅうしつ）に、あたたかな明（あ）かりがともった。
 （ナレーション）その夜（よる）、世界（せかい）の暗（くら）やみは、少（すこ）しずつ明（あか）るく照（て）らされていった。電球（でんきゅう）だけではない。エジソンは生涯（しょうがい）に千以上（せんいじょう）もの発明（はつめい）を世（よ）に残（のこ）した。その原動力（げんどうりょく）は、子（こ）どものころから変（か）わらない「なぜ？」という強（つよ）い好奇心（こうきしん）だった。
 （ナレーション）「天才（てんさい）とは、1パーセントのひらめきと、99パーセントの努力（どりょく）である」。失敗（しっぱい）を恐（おそ）れず、努力（どりょく）を続（つづ）けたエジソンの言葉（ことば）は、今（いま）も世界中（せかいじゅう）の人（ひと）の胸（むね）に生（い）きている。</t>
         </is>
       </c>
-      <c r="I5" s="3" t="n">
-        <v>471</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="I5" s="6" t="n">
+        <v>511</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>In an age without electricity, the only thing lighting the darkness of night was the small, flickering flame of candles and lamps. The American inventor Edison resolved: 'I will make a long-lasting, bright bulb that anyone can use.' Searching for a glowing filament, Edison repeated experiments—cotton, paper, hair—he tried everything, but the thread burned out at once. His failures passed a thousand. 'Sir, another failure. Shouldn't we give up?' 'No. This isn't failure. I've just found one more way that doesn't work.' Edison never stopped believing. Eventually, a thin filament made from Japanese bamboo glowed for over 40 hours. A warm light came on in the lab. That night, the world's darkness was lit, little by little. 'Genius is 1% inspiration and 99% perspiration.' The words of Edison, who feared no failure and kept on striving, still live in people's hearts around the world.</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>〜と決心した／くり返した／〜じゃない</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr">
         <is>
           <t>失敗を恐れぬ努力。</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" s="6" t="inlineStr">
         <is>
           <t>世界の夜を明るくした。</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="6" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/エジソン/助手</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="409" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="6" ht="409.05" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>L-D-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>ヘレン・ケラーと先生</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>ドキュメンタリー</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>（ナレーション）目（め）が見（み）えず、耳（みみ）も聞（き）こえない少女（しょうじょ）がいた。ヘレン・ケラー。言葉（ことば）を知（し）らない彼女（かのじょ）の心（こころ）は、出口（でぐち）のない暗（くら）い闇（やみ）の中（なか）にあった。思（おも）い通（どお）りにならず、ヘレンは毎日（まいにち）あばれ、家族（かぞく）も困（こま）りはてていた。
 （ナレーション）そんなある日（ひ）、一人（ひとり）の家庭教師（かていきょうし）がやって来（き）た。サリバン先生（せんせい）である。
-サリバン：「あきらめません。わたしが、あなたに世界（せかい）の名前（なまえ）を教（おし）えます」。
+女（サリバン）：「あきらめません。わたしが、あなたに世界（せかい）の名前（なまえ）を教（おし）えます」。
 （ナレーション）先生（せんせい）は、ヘレンの手（て）のひらに、指（ゆび）で何度（なんど）も文字（もじ）を書（か）いた。コップ、人形（にんぎょう）、いす……。けれどヘレンには、それが「名前（なまえ）」だとわからない。根気（こんき）のいる日々（ひび）が続（つづ）いた。
 （ナレーション）ある朝（あさ）、二人（ふたり）は井戸（いど）のそばにいた。先生（せんせい）がヘレンの手（て）に、冷（つめ）たい水（みず）を流（なが）しながら、もう一方（いっぽう）の手（て）に「W-A-T-E-R」と書（か）いた。その瞬間（しゅんかん）、ヘレンの体（からだ）に電気（でんき）が走（はし）ったように、はっと動（うご）きが止（と）まった。「そうか……これが『水（みず）』なんだ！」。
 （ナレーション）世界（せかい）のすべてに名前（なまえ）があると知（し）った、その日（ひ）。ヘレンの暗（くら）い世界（せかい）に、光（ひかり）がさした。やがて彼女（かのじょ）は懸命（けんめい）に学（まな）び、大学（だいがく）を卒業（そつぎょう）した。
 （ナレーション）後（のち）にヘレンは、世界中（せかいじゅう）を旅（たび）して講演（こうえん）し、目（め）や耳（みみ）の不自由（ふじゆう）な人々（ひとびと）のために力（ちから）をつくした。「世界（せかい）は苦（くる）しみに満（み）ちているが、それを乗（の）りこえる力（ちから）にも満（み）ちている」。サリバン先生（せんせい）とヘレンの物語（ものがたり）は、同（おな）じ苦（くる）しみを持（も）つ世界中（せかいじゅう）の人々（ひとびと）に、今（いま）も希望（きぼう）を与（あた）え続（つづ）けている。</t>
         </is>
       </c>
-      <c r="I6" s="3" t="n">
-        <v>503</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="I6" s="6" t="n">
+        <v>551</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>There was a girl who could neither see nor hear: Helen Keller. Knowing no words, her heart was in a dark gloom with no exit. Unable to make herself understood, Helen raged every day, and her family was at a loss. Then one day a tutor came—Miss Sullivan. 'I won't give up. I will teach you the names of the world.' The teacher wrote letters with her finger on Helen's palm, again and again—cup, doll, chair. But Helen couldn't grasp that these were 'names.' Patient days continued. One morning, the two were by a well. As the teacher let cold water flow over one of Helen's hands, she spelled 'W-A-T-E-R' on the other. In that instant, as if electricity ran through her, Helen froze. 'I see... this is water!' The day she learned that everything in the world has a name, light shone into her dark world. In time she studied hard, graduated from university, and became someone who gave hope to people worldwide who shared her struggle.</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>〜ません／〜ながら／〜と知った</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
         <is>
           <t>闇に光がさした瞬間。</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="M6" s="6" t="inlineStr">
         <is>
           <t>学ぶ喜びと希望。</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/サリバン</t>
         </is>
@@ -1744,427 +1688,425 @@
     <col width="64" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="52" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="13"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="11" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>タブ</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>カテゴリー</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>サブテーマ</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>形式</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>対象レベル(非表示)</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>字数</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>英訳</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>キー表現</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>ポイント</t>
         </is>
       </c>
-      <c r="M1" s="11" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>楽しさ・継続フック</t>
         </is>
       </c>
-      <c r="N1" s="11" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>備考(音声)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="334" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="334.05" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>L-T-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>昔話</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>桃太郎</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>（ナレーション）むかしむかし、あるところに、おじいさんとおばあさんが住（す）んでいました。ある日（ひ）、川（かわ）で大（おお）きな桃（もも）を拾（ひろ）い、家（いえ）で割（わ）ると、中（なか）から元気（げんき）な男（おとこ）の子（こ）が飛（と）び出（だ）しました。二人（ふたり）はその子（こ）を桃太郎（ももたろう）と名（な）づけ、大切（たいせつ）に育（そだ）てました。
 （ナレーション）やがて、村（むら）を荒（あ）らす鬼（おに）の話（はなし）を聞（き）いた桃太郎（ももたろう）は、鬼（おに）ヶ島（しま）へ向（む）かう決心（けっしん）をします。
-桃太郎：「おばあさんのきびだんごをあげるから、いっしょに来（き）てくれないか」。
+男（桃太郎）：「おばあさんのきびだんごをあげるから、いっしょに来（き）てくれないか」。
 （ナレーション）道（みち）の途中（とちゅう）で、犬（いぬ）、猿（さる）、きじが仲間（なかま）になりました。鬼（おに）ヶ島（しま）に着（つ）くと、おそろしい鬼（おに）たちが暴（あば）れています。桃太郎（ももたろう）たちは力（ちから）を合（あ）わせて勇敢（ゆうかん）に戦（たたか）い、ついに鬼（おに）を降参（こうさん）させました。鬼（おに）は奪（うば）った宝物（たからもの）を返（かえ）し、二度（にど）と悪（わる）いことをしないと約束（やくそく）しました。桃太郎（ももたろう）は宝物（たからもの）を持（も）ち帰（かえ）り、村（むら）のみんなと幸（しあわ）せに暮（く）らしました。</t>
         </is>
       </c>
-      <c r="I2" s="3" t="n">
-        <v>299</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="I2" s="6" t="n">
+        <v>323</v>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>Long ago, an old man and woman lived in a certain place. One day they found a huge peach in the river; when they split it at home, a healthy boy leapt out. They named him Momotaro and raised him with care. In time, hearing of ogres ravaging the village, Momotaro resolved to go to Ogre Island. 'I'll give you Grandma's millet dumplings, so will you come with me?' Along the way, a dog, a monkey, and a pheasant became his companions. On Ogre Island, fearsome ogres were rampaging. Joining their strength, Momotaro and friends fought bravely and at last made the ogres surrender. The ogres returned the stolen treasure and promised never to do wrong again. Momotaro brought the treasure home and lived happily with everyone in the village.</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>〜決心をする／〜くれないか／力を合わせて</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>鬼退治まで一話完結。</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>仲間と力を合わせる。</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/桃太郎</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="349" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="349.05" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>L-T-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>昔話</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>浦島太郎</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>（ナレーション）むかし、浦島太郎（うらしまたろう）という心（こころ）やさしい漁師（りょうし）がいました。ある日（ひ）、浜辺（はまべ）で子（こ）どもたちにいじめられている亀（かめ）を見（み）つけ、お金（かね）をはらって助（たす）けてやりました。
 （ナレーション）数日後（すうじつご）、海（うみ）に出（で）た太郎（たろう）の前（まえ）に、あの亀（かめ）が現（あらわ）れました。「助（たす）けてくれたお礼（れい）に」と、太郎（たろう）を背中（せなか）に乗（の）せ、海（うみ）の底（そこ）の竜宮城（りゅうぐうじょう）へ連（つ）れて行（い）きました。そこでは美（うつく）しい乙姫（おとひめ）が、ごちそうと踊（おど）りで太郎（たろう）をもてなしました。
-乙姫：「おみやげの玉手箱（たまてばこ）です。でも、けっして開（あ）けてはいけませんよ」。
+女（乙姫）：「おみやげの玉手箱（たまてばこ）です。でも、けっして開（あ）けてはいけませんよ」。
 （ナレーション）夢（ゆめ）のような日々（ひび）。けれど村（むら）が恋（こい）しくなった太郎（たろう）は、玉手箱（たまてばこ）を持（も）って帰（かえ）りました。ところが、村（むら）はすっかり変（か）わり、知（し）っている人（ひと）は一人（ひとり）もいません。竜宮城（りゅうぐうじょう）での数日（すうじつ）の間（あいだ）に、地上（ちじょう）では何百年（なんびゃくねん）も過（す）ぎていたのです。さびしさのあまり、太郎（たろう）が約束（やくそく）を忘（わす）れて箱（はこ）を開（あ）けると、白（しろ）い煙（けむり）がもくもくと出（で）て、太郎（たろう）はたちまち白髪（しらが）のおじいさんになってしまいました。</t>
         </is>
       </c>
-      <c r="I3" s="3" t="n">
-        <v>348</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="I3" s="6" t="n">
+        <v>372</v>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>Long ago there was a kind-hearted fisherman named Urashima Taro. One day on the beach he found a turtle being bullied by children, and paid money to save it. A few days later, out at sea, that turtle appeared before him. 'To thank you for saving me,' it carried Taro on its back to the Dragon Palace at the bottom of the sea. There the beautiful Otohime hosted Taro with feasts and dancing. 'Here is a parting gift, the tamatebako. But you must never open it.' Dreamlike days passed. But missing his village, Taro went home with the box. Yet the village had completely changed, and not a single person he knew remained. During his few days in the palace, hundreds of years had passed on land. Out of loneliness, forgetting the promise, Taro opened the box; white smoke billowed out, and he instantly became a white-haired old man.</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>〜てやる／けっして〜てはいけない／〜のあまり</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>玉手箱の結末まで完結。</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="6" t="inlineStr">
         <is>
           <t>約束を破った代償。</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="6" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/乙姫</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="349" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="349.05" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>L-T-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>昔話</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>かぐや姫</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>（ナレーション）むかし、竹（たけ）を取（と）って暮（く）らすおじいさんがいました。ある日（ひ）、根元（ねもと）が光（ひか）る竹（たけ）を見（み）つけ、切（き）ってみると、中（なか）に手（て）のひらほどの小（ちい）さな女（おんな）の子（こ）がいました。子（こ）どものいなかった夫婦（ふうふ）は大喜（おおよろこ）びで、その子（こ）をかぐや姫（ひめ）と名（な）づけ、大切（たいせつ）に育（そだ）てました。
 （ナレーション）かぐや姫（ひめ）は、月（つき）のように美（うつく）しい娘（むすめ）に育（そだ）ちました。うわさを聞（き）いた多（おお）くの男（おとこ）たちが結婚（けっこん）を申（もう）し込（こ）みましたが、姫（ひめ）は首（くび）を縦（たて）に振（ふ）りません。
-かぐや姫：「ごめんなさい。わたしは、近（ちか）いうちに月（つき）へ帰（かえ）らなければならないのです」。
+女（かぐや姫）：「ごめんなさい。わたしは、近（ちか）いうちに月（つき）へ帰（かえ）らなければならないのです」。
 （ナレーション）実（じつ）は、かぐや姫（ひめ）は月（つき）の世界（せかい）から来（き）た人（ひと）でした。満月（まんげつ）の夜（よる）、空（そら）から大勢（おおぜい）の使（つか）いが、光（ひかり）とともに姫（ひめ）を迎（むか）えに来（き）ました。おじいさんとおばあさんは泣（な）いて引（ひ）き止（と）めましたが、別（わか）れの時（とき）は来（き）てしまいます。姫（ひめ）は二人（ふたり）に深（ふか）く感謝（かんしゃ）し、別（わか）れを惜（お）しみながら、静（しず）かに天（てん）へのぼっていきました。</t>
         </is>
       </c>
-      <c r="I4" s="3" t="n">
-        <v>324</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="I4" s="6" t="n">
+        <v>348</v>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>Long ago there was an old man who made his living cutting bamboo. One day he found a stalk glowing at its base; when he cut it, inside was a tiny girl the size of a palm. The childless couple were overjoyed, named her Kaguya-hime, and raised her with care. Kaguya-hime grew into a maiden as beautiful as the moon. Many men who heard the rumor proposed marriage, but the princess would not nod yes. 'I'm sorry. I must return to the moon before long.' In truth, Kaguya-hime was from the world of the moon. On the night of the full moon, a great host of envoys came from the sky with light to fetch her. The old couple wept and tried to hold her back, but the time of parting came. Deeply grateful to them, sad to part, the princess quietly ascended to the heavens.</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>〜ません／〜なければならない／〜ながら</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>月へ帰るまで完結。</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>別れの切なさ。</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/かぐや姫</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="379" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5" ht="379.05" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>L-T-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>昔話</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>鶴の恩返し</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>（ナレーション）さむい雪（ゆき）の日（ひ）、一人（ひとり）の男（おとこ）が、わなにかかって苦（くる）しんでいる鶴（つる）を見（み）つけ、そっと逃（に）がしてやりました。その夜（よる）、戸（と）をたたく音（おと）がして、美（うつく）しい女（おんな）の人（ひと）が「道（みち）に迷（まよ）った」とたずねて来（き）ました。やがて二人（ふたり）は夫婦（ふうふ）になりました。
 （ナレーション）まずしい暮（く）らしを助（たす）けようと、妻（つま）は機（はた）を織（お）りはじめました。
-妻：「布（ぬの）を織（お）っている間（あいだ）は、けっして部屋（へや）をのぞかないでください」。
+女（妻）：「布（ぬの）を織（お）っている間（あいだ）は、けっして部屋（へや）をのぞかないでください」。
 （ナレーション）でき上（あ）がった布（ぬの）は、おどろくほど美（うつく）しく、高（たか）い値段（ねだん）で売（う）れました。けれど男（おとこ）は、どうしても中（なか）が気（き）になります。ある日（ひ）、約束（やくそく）を破（やぶ）ってそっとのぞくと――そこにいたのは、やせ細（ほそ）った鶴（つる）が、自分（じぶん）の羽根（はね）を一本（いっぽん）ずつ抜（ぬ）いて、布（ぬの）に織（お）り込（こ）んでいる姿（すがた）でした。あの日（ひ）助（たす）けた鶴（つる）の、恩返（おんがえ）しだったのです。
-妻：「姿（すがた）を見（み）られたからには、もう、ここにはいられません」。
+女（妻）：「姿（すがた）を見（み）られたからには、もう、ここにはいられません」。
 （ナレーション）妻（つま）は一羽（いちわ）の鶴（つる）にもどり、何度（なんど）も振（ふ）り返（かえ）りながら、雪空（ゆきぞら）へ飛（と）び去（さ）っていきました。</t>
         </is>
       </c>
-      <c r="I5" s="3" t="n">
-        <v>350</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="I5" s="6" t="n">
+        <v>382</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>On a cold, snowy day, a man found a crane suffering in a trap and gently set it free. That night, there was a knock at the door, and a beautiful woman came saying she had lost her way. In time the two became husband and wife. To help their poor life, the wife began to weave at the loom. 'While I weave the cloth, never look into the room.' The finished cloth was astonishingly beautiful and sold for a high price. But the man couldn't stop wondering what was inside. One day, breaking the promise, he quietly peeked—and there was a gaunt crane, plucking its own feathers one by one and weaving them into the cloth. It was the crane he had saved, repaying his kindness. 'Now that you have seen my true form, I can no longer stay here.' The wife turned back into a crane and, looking back again and again, flew away into the snowy sky.</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>〜てやる／けっして〜ないで／〜からには</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr">
         <is>
           <t>恩返しと別れまで完結。</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" s="6" t="inlineStr">
         <is>
           <t>見るなの約束。</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="6" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/妻</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="409" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="6" ht="409.05" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>L-T-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>昔話</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>笠地蔵</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>（ナレーション）年（とし）の暮（く）れ、まずしいけれど心（こころ）のやさしいおじいさんが、お正月（しょうがつ）のもちを買（か）うお金（かね）にしようと、手作（てづく）りの笠（かさ）を町（まち）へ売（う）りに行（い）きました。けれど、笠（かさ）は一（ひと）つも売（う）れず、雪（ゆき）まで降（ふ）り出（だ）してしまいました。
 （ナレーション）すごすごと帰（かえ）る道（みち）、おじいさんは、雪（ゆき）の中（なか）に並（なら）んで立（た）つ六体（ろくたい）のお地蔵（じぞう）さまを見（み）つけました。頭（あたま）に雪（ゆき）を積（つ）もらせて、寒（さむ）そうにしています。
-おじいさん：「お地蔵（じぞう）さま、さぞ寒（さむ）かろう。これをどうぞ」。
+男（おじいさん）：「お地蔵（じぞう）さま、さぞ寒（さむ）かろう。これをどうぞ」。
 （ナレーション）おじいさんは、売（う）り物（もの）の笠（かさ）を一（ひと）つずつかぶせてあげました。けれど笠（かさ）は五（いつ）つしかなく、一（ひと）つ足（た）りません。そこで、自分（じぶん）がかぶっていた手（て）ぬぐいを取（と）って、最後（さいご）のお地蔵（じぞう）さまの頭（あたま）にかけてあげました。
 （ナレーション）その夜（よる）、ふしぎなことが起（お）こりました。明（あ）け方（がた）、外（そと）で重（おも）い物（もの）を置（お）くような音（おと）がします。戸（と）を開（あ）けると、米（こめ）やもち、おせちのごちそうが、山（やま）のように積（つ）まれていたのです。雪（ゆき）の上（うえ）には、六体（ろくたい）のお地蔵（じぞう）さまの足跡（あしあと）が残（のこ）っていました。親切（しんせつ）への、お礼（れい）だったのです。</t>
         </is>
       </c>
-      <c r="I6" s="3" t="n">
-        <v>375</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="I6" s="6" t="n">
+        <v>407</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>At year's end, a poor but kind-hearted old man went to town to sell handmade straw hats, hoping to buy mochi for New Year. But not one hat sold, and it even began to snow. Trudging home, the old man found six Jizo statues standing in a row in the snow, snow piling on their heads, looking cold. 'O Jizo, you must be very cold. Please take these.' He placed his hats on them one by one. But he had only five hats—one short. So he took off the hand towel he was wearing and put it on the last Jizo's head. That night, something mysterious happened. Toward dawn, there was a sound outside like heavy things being set down. When he opened the door, rice, mochi, and New Year feasts were piled like a mountain. In the snow remained the footprints of six Jizo. It was their thanks for his kindness.</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>〜かろう／〜てあげる／〜のように</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
         <is>
           <t>親切が報われ完結。</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="M6" s="6" t="inlineStr">
         <is>
           <t>小さな親切の奇跡。</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/おじいさん</t>
         </is>
@@ -2194,121 +2136,119 @@
     <col width="64" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="52" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="13"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="11" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>タブ</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>カテゴリー</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>サブテーマ</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>形式</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>対象レベル(非表示)</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>字数</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>英訳</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>キー表現</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>ポイント</t>
         </is>
       </c>
-      <c r="M1" s="11" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>楽しさ・継続フック</t>
         </is>
       </c>
-      <c r="N1" s="11" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>備考(音声)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="409" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
+    <row r="2" ht="409.05" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>L-K-001</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>カイの物語</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>日本生活スタート</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>約束の写真</t>
         </is>
       </c>
-      <c r="F2" s="14" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="H2" s="14" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>「必ず、日本へ行く。」
 三年前の、あの日。カイは、そう約束した。
@@ -2375,60 +2315,60 @@
 なぜ、彼女は、写真を見て、止まったのか。</t>
         </is>
       </c>
-      <c r="I2" s="14" t="n">
+      <c r="I2" s="6" t="n">
         <v>1517</v>
       </c>
-      <c r="J2" s="14" t="n"/>
-      <c r="K2" s="14" t="n"/>
-      <c r="L2" s="14" t="n"/>
-      <c r="M2" s="14" t="inlineStr">
+      <c r="J2" s="6" t="n"/>
+      <c r="K2" s="6" t="n"/>
+      <c r="L2" s="6" t="n"/>
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>縦軸=写真の謎「ここへ、おいで」を提示。ラスト「この家、知ってる」の引きで第2話へ。手のふるえ・心臓の音など体感描写を密に。</t>
         </is>
       </c>
-      <c r="N2" s="14" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>※台本刷新(旧「空港に着いた」)。旧L-K-001音声は内容不一致＝要再生成。</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="409" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+    <row r="3" ht="409.05" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>L-K-002</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>カイの物語</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>日本生活スタート</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>知らない女の子</t>
         </is>
       </c>
-      <c r="F3" s="14" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="H3" s="14" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>女の子は、写真を見つめたまま、うごかない。
 カイの心ぞうは、はやくなるいっぽうだった。
@@ -2483,60 +2423,60 @@
 三つ目の駅。カイの、あたらしい生活が、はじまる。</t>
         </is>
       </c>
-      <c r="I3" s="14" t="n">
+      <c r="I3" s="6" t="n">
         <v>1477</v>
       </c>
-      <c r="J3" s="14" t="n"/>
-      <c r="K3" s="14" t="n"/>
-      <c r="L3" s="14" t="n"/>
-      <c r="M3" s="14" t="inlineStr">
+      <c r="J3" s="6" t="n"/>
+      <c r="K3" s="6" t="n"/>
+      <c r="L3" s="6" t="n"/>
+      <c r="M3" s="6" t="inlineStr">
         <is>
           <t>第1話の引き(この家、知ってる)を「気のせいかも」に着地＝謎は薄く残す。ひとりぼっち→はじめての繋がりの感情弧。ミナ登場・連絡先交換。</t>
         </is>
       </c>
-      <c r="N3" s="14" t="inlineStr">
+      <c r="N3" s="6" t="inlineStr">
         <is>
           <t>※台本刷新(旧「ゴミ出しでこまった」)。音声は要作成。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="409" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+    <row r="4" ht="409.05" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>L-K-003</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>カイの物語</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>日本生活スタート</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>はじめての部屋</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>三つ目の駅で、電車をおりる。
 ミナの言ったとおり、カイは、また、まいごになった。
@@ -2594,60 +2534,60 @@
 朝八時。ねぼけたカイを、待っていたのは——。</t>
         </is>
       </c>
-      <c r="I4" s="14" t="n">
+      <c r="I4" s="6" t="n">
         <v>1443</v>
       </c>
-      <c r="J4" s="14" t="n"/>
-      <c r="K4" s="14" t="n"/>
-      <c r="L4" s="14" t="n"/>
-      <c r="M4" s="14" t="inlineStr">
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>空っぽの部屋→布団もご飯もない現実を飛ばさず、コンビニ初体験＋はじめての夜(床寝)で埋める。孤独×新しい一歩。翌朝ゴミの日へ自然に接続。</t>
         </is>
       </c>
-      <c r="N4" s="14" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>※台本刷新(旧「はじめての友だち（ミナ）」)。音声は要作成。</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="409" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
+    <row r="5" ht="409.05" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>L-K-004</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>カイの物語</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>日本生活スタート</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>ゴミの日</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="H5" s="14" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>朝。
 まどから、白い光が、さしこんでいた。
@@ -2697,60 +2637,60 @@
 いいにおいの、あたたかい家。カイの知らない、日本の味が、まっている。</t>
         </is>
       </c>
-      <c r="I5" s="14" t="n">
+      <c r="I5" s="6" t="n">
         <v>1210</v>
       </c>
-      <c r="J5" s="14" t="n"/>
-      <c r="K5" s="14" t="n"/>
-      <c r="L5" s="14" t="n"/>
-      <c r="M5" s="14" t="inlineStr">
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="6" t="inlineStr">
         <is>
           <t>はじめてのしっぱい=ゴミ分別(外国人あるある)を、はずかしさ→やさしさで温める。おばあちゃん初登場を事件で(自然に注意する近所の人)。引き=お茶のさそい。</t>
         </is>
       </c>
-      <c r="N5" s="14" t="inlineStr">
+      <c r="N5" s="6" t="inlineStr">
         <is>
           <t>※台本刷新(旧「バイトを始める」)。音声は要作成。</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="409" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+    <row r="6" ht="409.05" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>L-K-005</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>カイの物語</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>日本生活スタート</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>おばあちゃんの家</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>ゴミの しっぱいの、あと。
 カイの一日は、いそがしかった。やることが、山のように、あったのだ。
@@ -2808,60 +2748,60 @@
 生きていくには、お金がいる。カイ、はじめての、しごと探し。</t>
         </is>
       </c>
-      <c r="I6" s="14" t="n">
+      <c r="I6" s="6" t="n">
         <v>1504</v>
       </c>
-      <c r="J6" s="14" t="n"/>
-      <c r="K6" s="14" t="n"/>
-      <c r="L6" s="14" t="n"/>
-      <c r="M6" s="14" t="inlineStr">
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="inlineStr">
         <is>
           <t>ゴミの日と同日に圧縮(布団・買い物で多忙→夕方おばあちゃん)。家庭の味=孤独×温かさ。写真の謎は薄く前進(遠くを見る)。伏線回収=布団/食器。引き=お金が減る→はたらく。※区役所の手続きは別ストーリー用に温存。</t>
         </is>
       </c>
-      <c r="N6" s="14" t="inlineStr">
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>※台本刷新(旧「日本語学校の初日」)。音声は要作成。区役所ネタは別話で使用予定。</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="409" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
+    <row r="7" ht="409.05" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>L-K-006</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>カイの物語</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>日本生活スタート</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>はたらきたい</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>朝。
 やわらかい布団の上で、カイは、目をさました。せなかは、もう、いたくない。
@@ -2916,60 +2856,60 @@
 たくさんの まどぐち、たくさんの 書類。カイの、書類との たたかいが、はじまる。</t>
         </is>
       </c>
-      <c r="I7" s="14" t="n">
+      <c r="I7" s="6" t="n">
         <v>1232</v>
       </c>
-      <c r="J7" s="14" t="n"/>
-      <c r="K7" s="14" t="n"/>
-      <c r="L7" s="14" t="n"/>
-      <c r="M7" s="14" t="inlineStr">
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="inlineStr">
         <is>
           <t>ケンタ初登場=ギャップ採用。伏線回収=初夜のコンビニ=職場。ラストで「働くには在留カード＋区役所の書類」→区役所(ep7)へ必然的に接続。</t>
         </is>
       </c>
-      <c r="N7" s="14" t="inlineStr">
+      <c r="N7" s="6" t="inlineStr">
         <is>
           <t>※新規話(L-K-006)。音声は要作成。</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="409" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+    <row r="8" ht="409.05" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>L-K-007</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>カイの物語</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>日本生活スタート</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>区役所</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>コンビニの しごとが、決まった。うれしい。——でも。
 ケンタの ことばが、頭に、のこっていた。「はたらく前に、在留カードと、区役所の 書類が いる。」
@@ -3023,60 +2963,60 @@
 「いらっしゃいませ」の声が、うわずる。カイの手が、ふるえる——。</t>
         </is>
       </c>
-      <c r="I8" s="14" t="n">
+      <c r="I8" s="6" t="n">
         <v>1301</v>
       </c>
-      <c r="J8" s="14" t="n"/>
-      <c r="K8" s="14" t="n"/>
-      <c r="L8" s="14" t="n"/>
-      <c r="M8" s="14" t="inlineStr">
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="inlineStr">
         <is>
           <t>別の山=区役所(住民登録・在留カード)を「働くために必要」と本筋化。ミナ再登場(第2話「こまったらメッセージして」回収・うさぎスタンプ)。実用フレーズ「やさしい日本語でお願いします」。感情=役所の疲れ→町の人になったしるし。</t>
         </is>
       </c>
-      <c r="N8" s="14" t="inlineStr">
+      <c r="N8" s="6" t="inlineStr">
         <is>
           <t>※新規話(L-K-007)。区役所ネタをここで使用。音声は要作成。</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="409" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+    <row r="9" ht="409.05" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>L-K-008</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>カイの物語</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>日本生活スタート</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>バイト初日</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>夕方、五時。
 カイは、コンビニの前に、立っていた。約束の、十分前。むねが、どき、どき、と、鳴っている。
@@ -3140,60 +3080,60 @@
 カイ、はじめての 教室。そこで、ふしぎな 女の子に、出会う。</t>
         </is>
       </c>
-      <c r="I9" s="14" t="n">
+      <c r="I9" s="6" t="n">
         <v>1662</v>
       </c>
-      <c r="J9" s="14" t="n"/>
-      <c r="K9" s="14" t="n"/>
-      <c r="L9" s="14" t="n"/>
-      <c r="M9" s="14" t="inlineStr">
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="inlineStr">
         <is>
           <t>区役所のpayoff(書類を渡し「えらいぞ」)。ケンタのやさしさ(気にすんな)＋おばあちゃん客登場でキャラが繋がる。引き=字が読めない→学校→第9話(田中さん登場)。</t>
         </is>
       </c>
-      <c r="N9" s="14" t="inlineStr">
+      <c r="N9" s="6" t="inlineStr">
         <is>
           <t>※新規話(L-K-008)。音声は要作成。</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="409" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
+    <row r="10" ht="409.05" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>L-K-009</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>カイの物語</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>日本生活スタート</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>日本語学校</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>数日が、すぎた。
 バイトにも、少しずつ、なれてきた。おつりも、もう、あまり、落とさない。
@@ -3248,60 +3188,60 @@
 ミナ、おばあちゃん、ケンタ、田中さん——ひとりで来たはずのカイの まわりに、いつのまにか。</t>
         </is>
       </c>
-      <c r="I10" s="14" t="n">
+      <c r="I10" s="6" t="n">
         <v>1306</v>
       </c>
-      <c r="J10" s="14" t="n"/>
-      <c r="K10" s="14" t="n"/>
-      <c r="L10" s="14" t="n"/>
-      <c r="M10" s="14" t="inlineStr">
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="n"/>
+      <c r="M10" s="6" t="inlineStr">
         <is>
           <t>田中さん初登場=好きな日本語ノート(こわい言語→きれい・アプリ理念と一致)。学校は来日理由(留学)と整合。田中=学校の親友(恋愛ではない・軸はミナ/写真)。引き=第10話で仲間を回収+写真の裏(次章)へ。</t>
         </is>
       </c>
-      <c r="N10" s="14" t="inlineStr">
+      <c r="N10" s="6" t="inlineStr">
         <is>
           <t>※新規話(L-K-009)。音声は要作成。田中さん=学校の親友(サブ)。</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="409" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
+    <row r="11" ht="409.05" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>L-K-010</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>カイの物語</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>日本生活スタート</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>はじめの一歩</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>日本に来て、二週間。
 カイの毎日は、いそがしくなった。
@@ -3340,18 +3280,18 @@
 写真のうらの、地名。カイとミナの、小さな旅が、動きだす。</t>
         </is>
       </c>
-      <c r="I11" s="14" t="n">
+      <c r="I11" s="6" t="n">
         <v>826</v>
       </c>
-      <c r="J11" s="14" t="n"/>
-      <c r="K11" s="14" t="n"/>
-      <c r="L11" s="14" t="n"/>
-      <c r="M11" s="14" t="inlineStr">
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
+      <c r="M11" s="6" t="inlineStr">
         <is>
           <t>第一章の締め。仲間(横糸)を回収しつつ写真の裏の地名=縦糸を前進。メインヒロイン=ミナを旅の相棒として呼び出し(第2話回収)。次章=カイ&amp;ミナの家探しの旅へ接続。</t>
         </is>
       </c>
-      <c r="N11" s="14" t="inlineStr">
+      <c r="N11" s="6" t="inlineStr">
         <is>
           <t>※新規話(L-K-010・第一章完)。音声は要作成。</t>
         </is>
@@ -3381,236 +3321,234 @@
     <col width="64" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="52" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="13"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="11" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>タブ</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>カテゴリー</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>サブテーマ</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>形式</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>対象レベル(非表示)</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>字数</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>英訳</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>キー表現</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>ポイント</t>
         </is>
       </c>
-      <c r="M1" s="11" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>楽しさ・継続フック</t>
         </is>
       </c>
-      <c r="N1" s="11" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>備考(音声)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="214" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="214.05" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>L-J-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>カイの物語</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>日本一人旅</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>京都へ行く</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>（ナレーション）連休（れんきゅう）、カイは はじめて 一人（ひとり）で 京都（きょうと）へ 来た。古（ふる）い お寺（てら）が 美（うつく）しい。
-カイ：わあ、きれい…。あの、すみません、写真（しゃしん）を 撮（と）って もらえますか。
-通行人（つうこうにん）：いいですよ。はい、チーズ！
-カイ：ありがとうございます！
+男（カイ）：わあ、きれい…。あの、すみません、写真（しゃしん）を 撮（と）って もらえますか。
+女（通行人）：いいですよ。はい、チーズ！
+男（カイ）：ありがとうございます！
 （ナレーション）お昼（ひる）に、小（ちい）さな お店（みせ）に 入（はい）った。
-店員：いらっしゃい。何（なに）に しますか。
-カイ：抹茶（まっちゃ）の アイス、ください。
-店員：はいよ。京都（きょうと）は どう？
-カイ：最高（さいこう）です！ また 来（き）たいなあ。
+女（店員）：いらっしゃい。何（なに）に しますか。
+男（カイ）：抹茶（まっちゃ）の アイス、ください。
+女（店員）：はいよ。京都（きょうと）は どう？
+男（カイ）：最高（さいこう）です！ また 来（き）たいなあ。
 （ナレーション）わすれられない 一日（いちにち）に なった。</t>
         </is>
       </c>
-      <c r="I2" s="3" t="n">
-        <v>159</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="I2" s="6" t="n">
+        <v>183</v>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>(Narration) On the holidays, Kai came to Kyoto alone for the first time. The old temples are beautiful. / Kai: Wow, beautiful... Um, excuse me, could you take a photo? / Passerby: Sure. Okay, cheese! / Kai: Thank you! / (Narration) For lunch, he went into a small shop. / Clerk: Welcome. What'll you have? / Kai: Matcha ice cream, please. / Clerk: Coming up. How's Kyoto? / Kai: It's the best! I want to come again. / (Narration) It became an unforgettable day.</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>撮って もらえますか／また 来たいなあ／〜はどう?</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>旅先の会話。会話表現「わあ/はいよ/〜なあ」。</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>旅情・写真・食。</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/カイ/通行人/店員</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="214" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="229.05" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>L-J-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>カイの物語</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>日本一人旅</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>お祭りに行く</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>（ナレーション）夏（なつ）の 夜（よる）。カイは 友（とも）だちの ミナと お祭（まつ）りに 来た。
-ミナ：カイ、ゆかた 似合（にあ）ってる！
-カイ：本当（ほんとう）？ えへへ、はじめて 着（き）たんだ。
-ミナ：屋台（やたい）、行（い）こうよ。たこ焼（や）き 食（た）べたい！
-カイ：いいね。あ、かき氷（ごおり）も！
+女（ミナ）：カイ、ゆかた 似合（にあ）ってる！
+男（カイ）：本当（ほんとう）？ えへへ、はじめて 着（き）たんだ。
+女（ミナ）：屋台（やたい）、行（い）こうよ。たこ焼（や）き 食（た）べたい！
+男（カイ）：いいね。あ、かき氷（ごおり）も！
 （ナレーション）二人（ふたり）が 食（た）べながら 歩（ある）いていると、空（そら）に 大（おお）きな 花火（はなび）が 上（あ）がった。
-カイ：わあ…！ きれいだね。
-ミナ：うん。来（き）て よかったね。
+男（カイ）：わあ…！ きれいだね。
+女（ミナ）：うん。来（き）て よかったね。
 （ナレーション）大（おお）きな 音（おと）と 光（ひかり）。カイの 胸（むね）は どきどきしていた。</t>
         </is>
       </c>
-      <c r="I3" s="3" t="n">
-        <v>147</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="I3" s="6" t="n">
+        <v>171</v>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>(Narration) A summer night. Kai came to a festival with his friend Mina. / Mina: Kai, the yukata looks good on you! / Kai: Really? Hehe, it's my first time wearing one. / Mina: Let's go to the stalls. I want takoyaki! / Kai: Nice. Oh, shaved ice too! / (Narration) As the two walked while eating, big fireworks rose into the sky. / Kai: Wow...! It's beautiful. / Mina: Yeah. I'm glad we came. / (Narration) The loud sound and light. Kai's heart was racing.</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>似合ってる／〜たんだ／来て よかったね</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>友だちとの祭り会話。会話表現「えへへ/〜よ/〜だね」。</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="6" t="inlineStr">
         <is>
           <t>夏祭りの高揚・友情。</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="6" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/カイ/ミナ</t>
         </is>
@@ -3640,158 +3578,156 @@
     <col width="64" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="52" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="13"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="11" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>タブ</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>カテゴリー</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>サブテーマ</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>形式</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>対象レベル(非表示)</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>字数</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>英訳</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>キー表現</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>ポイント</t>
         </is>
       </c>
-      <c r="M1" s="11" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>楽しさ・継続フック</t>
         </is>
       </c>
-      <c r="N1" s="11" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>備考(音声)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="244" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="244.05" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>L-L-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>カイの物語</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>カイの日常</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>はじめての美容院</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>（ナレーション）カイは はじめて 一人（ひとり）で 美容院（びよういん）に 来た。日本語（にほんご）で 髪型（かみがた）を 言（い）うのは ドキドキする。
-美容師（びようし）：今日（きょう）は どうしますか。
-カイ：えっと、少（すこ）し 短（みじか）く して、軽（かる）く したいんです。
-美容師：前髪（まえがみ）は どうしましょう？
-カイ：前髪は そのままで お願（ねが）いします。
+女（美容師）：今日（きょう）は どうしますか。
+男（カイ）：えっと、少（すこ）し 短（みじか）く して、軽（かる）く したいんです。
+女（美容師）：前髪（まえがみ）は どうしましょう？
+男（カイ）：前髪は そのままで お願（ねが）いします。
 （ナレーション）はさみの 音（おと）が ひびく。終（お）わって 鏡（かがみ）を 見（み）ると…思（おも）ったより ずいぶん 短（みじか）い！
-カイ：（心の声）うわ、短く なりすぎたかな…。
-美容師：うん、似合（にあ）っていますよ。
-カイ：あ、ありがとうございます！
+男（カイ）：（心の声）うわ、短く なりすぎたかな…。
+女（美容師）：うん、似合（にあ）っていますよ。
+男（カイ）：あ、ありがとうございます！
 （ナレーション）少（すこ）し 短すぎたけれど、カイは なんだか うれしかった。</t>
         </is>
       </c>
-      <c r="I2" s="3" t="n">
-        <v>191</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="I2" s="6" t="n">
+        <v>215</v>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>(Narration) Kai came to a hair salon alone for the first time. Saying his hairstyle in Japanese is nerve-racking. / Stylist: What would you like today? / Kai: Um, a bit shorter and lighter, please. / Stylist: What about your bangs? / Kai: Please leave the bangs as they are. / (Narration) The scissors snip away. When it was done and he looked in the mirror... it was much shorter than he expected! / Kai: (inner voice) Whoa, maybe too short... / Stylist: Yeah, it suits you. / Kai: Oh, thank you! / (Narration) A little too short, but Kai felt somehow happy.</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>〜したいんです／どうしましょう／似合っています</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>美容院の会話＋心の声。会話表現「えっと/うわ/なんだか」。</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>カイの小さな挑戦。</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>多声TTS:ナレーター/カイ/美容師</t>
         </is>
@@ -3821,153 +3757,151 @@
     <col width="64" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="52" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="13"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="11" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>タブ</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>カテゴリー</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>サブテーマ</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>形式</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>対象レベル(非表示)</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>字数</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>英訳</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>キー表現</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>ポイント</t>
         </is>
       </c>
-      <c r="M1" s="11" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>楽しさ・継続フック</t>
         </is>
       </c>
-      <c r="N1" s="11" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>備考(音声)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="184" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="184.05" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>L-B-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>カイの物語</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>カイの休憩室</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>好きな食べ物の話</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>物語</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>カイ：みなさん、こんにちは、カイです。ちょっと 休憩（きゅうけい）の 時間（じかん）。今日（きょう）は ぼくの 好（す）きな 食（た）べ物（もの）の 話（はなし）。
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>男（カイ）：みなさん、こんにちは、カイです。ちょっと 休憩（きゅうけい）の 時間（じかん）。今日（きょう）は ぼくの 好（す）きな 食（た）べ物（もの）の 話（はなし）。
 （ナレーション）実（じつ）は カイ、おにぎりが 大好物（だいこうぶつ）。
-カイ：コンビニの おにぎりも おいしいけど、自分（じぶん）で 作（つく）るのも 楽（たの）しいんだよね。この前（まえ）、友（とも）だちに 作（つく）ってあげたら「うまっ！」って 言（い）われて、うれしくて さ。
+男（カイ）：コンビニの おにぎりも おいしいけど、自分（じぶん）で 作（つく）るのも 楽（たの）しいんだよね。この前（まえ）、友（とも）だちに 作（つく）ってあげたら「うまっ！」って 言（い）われて、うれしくて さ。
 （ナレーション）カイは 照（て）れながら 笑（わら）った。
-カイ：みなさんの 好（す）きな 日本（にほん）の 食べ物は 何（なん）ですか？ また 教（おし）えてね。じゃあ、また！</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
+男（カイ）：みなさんの 好（す）きな 日本（にほん）の 食べ物は 何（なん）ですか？ また 教（おし）えてね。じゃあ、また！</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>184</v>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>Kai: Hi everyone, it's Kai. A little break time. Today, a talk about my favorite food. / (Narration) Actually, Kai loves onigiri. / Kai: Convenience-store onigiri are tasty, but making them yourself is fun too, you know. The other day I made some for a friend and they said 'Yum!'—it made me really happy. / (Narration) Kai laughed bashfully. / Kai: What's your favorite Japanese food? Let me know sometime. See you!</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>〜んだよね／うまっ／〜てね</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>カイの語りかけ＋ひとり言。くだけた会話表現「〜だよね/うまっ/さ」。</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>親近感・リスナーへの呼びかけ。</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>多声TTS:カイ/ナレーター</t>
         </is>
@@ -3985,7 +3919,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -3997,343 +3931,341 @@
     <col width="64" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="52" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="11" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>タブ</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>カテゴリー</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>サブテーマ</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>形式</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>対象レベル(非表示)</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>字数</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>英訳</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>キー表現</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>ポイント</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>楽しさ・継続フック</t>
         </is>
       </c>
-      <c r="N1" s="8" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>備考(音声)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="139" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="139.05" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>L-R-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>ニュース</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>桜が満開（国内）</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>ニュース</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>おはようございます。今朝（けさ）の ニュースです。昨日（きのう）、東京（とうきょう）の 公園（こうえん）で 桜（さくら）が 満開（まんかい）に なりました。週末（しゅうまつ）は たくさんの 家族（かぞく）連（づ）れで にぎわいそうです。天気（てんき）も よく、お花見（はなみ）に ぴったりの 一日（いちにち）に なるでしょう。一方（いっぽう）、来週（らいしゅう）からは 少（すこ）し 寒（さむ）く なるという 予報（よほう）も 出（で）ています。体調（たいちょう）に 気（き）を つけて お過（す）ごしください。では、今日（きょう）も よい 一日を。</t>
         </is>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" s="1" t="n">
         <v>142</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Good morning. Here's this morning's news. Yesterday, the cherry blossoms reached full bloom in a Tokyo park. This weekend it should be crowded with families. The weather is good too—a perfect day for hanami. On the other hand, it's forecast to get a bit colder from next week. Please take care of your health. Have a good day.</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>今朝の ニュース／満開／〜そうです／一方</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>ニュースの流れと話題転換「一方」。</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>季節感で“朝の習慣”に。</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>1話者・アナウンサー調</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="109" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="109.05" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>L-R-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>ニュース</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>全国の天気（天気）</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>天気予報</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>全国（ぜんこく）の 天気（てんき）です。今日（きょう）は 西日本（にしにほん）で 晴（は）れますが、東日本（ひがしにほん）は 午後（ごご）から 雲（くも）が 多（おお）く なるでしょう。夜（よる）には 雨（あめ）が 降（ふ）る 所（ところ）も あります。傘（かさ）を 持（も）って 出（で）かけると 安心（あんしん）です。気温（きおん）は 各地（かくち）で 20度（ど）前後（ぜんご）、過（す）ごしやすい 一日（いちにち）に なりそうです。</t>
         </is>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" s="1" t="n">
         <v>97</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>Here's the nationwide weather. Today it's sunny in western Japan, but in eastern Japan clouds will increase from the afternoon. Some areas may see rain at night. It's safer to take an umbrella. Temperatures will be around 20 degrees—a comfortable day.</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>晴れます／雲が 多く なる／傘を 持って</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>全国天気の聞き取り（地域差）。</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>「傘いる?」毎朝役立つ。</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>1話者・予報士調</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="109" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="109.05" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>L-R-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>ニュース</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="D4" s="1" t="n"/>
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>海外のニュース（国際）</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>ニュース</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>こんにちは、国際（こくさい）ニュースです。アメリカで、新（あたら）しい 技術（ぎじゅつ）の 会議（かいぎ）が 開（ひら）かれました。世界中（せかいじゅう）から たくさんの 研究者（けんきゅうしゃ）が 集（あつ）まりました。日本（にほん）からも 多（おお）くの 企業（きぎょう）が 参加（さんか）し、注目（ちゅうもく）を 集（あつ）めています。来年（らいねん）は アジアでも 同（おな）じ 会議が 開かれる 予定（よてい）です。</t>
         </is>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I4" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="1" t="inlineStr">
         <is>
           <t>Hello, international news. In the U.S., a conference on new technology was held. Many researchers gathered from around the world. Many companies from Japan also took part and are drawing attention. Next year, the same conference is scheduled to be held in Asia too.</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="1" t="inlineStr">
         <is>
           <t>国際ニュース／〜が 開かれました／注目を 集めています</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="1" t="inlineStr">
         <is>
           <t>国際ニュースの定型表現。</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="1" t="inlineStr">
         <is>
           <t>世界とつながる話題。</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="1" t="inlineStr">
         <is>
           <t>1話者・アナウンサー調</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="94" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5" ht="94.05" customHeight="1">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>L-R-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>ニュース</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="D5" s="1" t="n"/>
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>サッカーの試合（スポーツ）</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>ニュース</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="1" t="inlineStr">
         <is>
           <t>スポーツの ニュースです。昨日（きのう）、サッカーの 試合（しあい）が ありました。日本（にほん）チームは 2対（たい）1で 勝（か）ちました。最後（さいご）の ゴールは、とても すばらしかったです。スタジアムの ファンは 大（おお）きな 声（こえ）で 応援（おうえん）しました。次（つぎ）の 試合は 来週（らいしゅう）の 土曜日（どようび）です。楽（たの）しみですね。</t>
         </is>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" s="1" t="n">
         <v>109</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="1" t="inlineStr">
         <is>
           <t>Sports news. Yesterday there was a soccer match. The Japan team won 2 to 1. The final goal was wonderful. Fans in the stadium cheered loudly. The next match is next Saturday. Something to look forward to.</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="1" t="inlineStr">
         <is>
           <t>2対1で 勝ちました／応援しました／楽しみですね</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="1" t="inlineStr">
         <is>
           <t>スポーツ結果(点数/勝敗)の聞き取り。</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" s="1" t="inlineStr">
         <is>
           <t>勝利の興奮。</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="1" t="inlineStr">
         <is>
           <t>1話者・アナウンサー調</t>
         </is>
@@ -4351,7 +4283,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -4363,213 +4295,240 @@
     <col width="64" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="52" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="11" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>タブ</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>カテゴリー</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>サブテーマ</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>形式</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>対象レベル(非表示)</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>字数</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>英訳</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>キー表現</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>ポイント</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>楽しさ・継続フック</t>
         </is>
       </c>
-      <c r="N1" s="8" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>備考(音声)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="124" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>L-R-005</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
+    <row r="2" ht="409.05" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>L-O-001</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>お便り相談室</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>勉強が続かない</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>コンビニで、うなずくだけ</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>トーク</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>こんばんは、パーソナリティの ユウキです。今日（きょう）も 一日（いちにち）お疲（つか）れさまでした。さて、リスナーの みなさんから お便（たよ）りを いただきました。「最近（さいきん）、日本語（にほんご）の 勉強（べんきょう）が 続（つづ）かなくて 困（こま）っています」。わかります〜。でも、大丈夫（だいじょうぶ）。毎日（まいにち）5分（ふん）でも いいんです。好（す）きな ドラマや 歌（うた）で 楽（たの）しく 続（つづ）けましょう。それでは、今夜（こんや）の 一曲（いっきょく）です。</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>142</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>こんばんは。パーソナリティのユウキです。今夜も、リスナーのみなさんから、お便りが届いています。
+「ユウキさん、こんばんは。私は、日本語を勉強している者です。
+半年間、毎晩、仕事のあと、三時間、机に向かいました。単語も、文法も、必死に覚えました。
+でも、この前、コンビニで、店員さんに何か聞かれて——その言葉が、一つも、聞き取れなかったんです。頭が真っ白になって、私は、ただ『はい、はい』と、うなずくことしか、できませんでした。
+家に帰って、レシートを見たら、いらないはずのものに、お金を払っていました。
+半年も、勉強したのに。帰り道、悔しくて、涙が止まりませんでした。
+——もう、日本語を話すのが、怖いです。」
+……うん。その涙、すごく、分かります。
+でもね、リスナーさん。一つだけ、言わせてください。
+あなたは、その時、「はい」と、声に出しました。逃げなかった。半年前のあなたなら、きっと、ドアの前で、引き返していたはずです。
+聞き取れなかったのは、あなたが下手だからじゃない。コンビニの日本語は、教科書には無い「生きた速さ」だからです。日本人だって、早口の店員さんに、聞き返すことがあるんですよ。
+今夜、あなたに、魔法の言葉を、一つ、プレゼントします。
+——「すみません、もう一度、お願いします。」
+これだけで、いいんです。この一言が、これからずっと、あなたを守ってくれます。
+怖くて、当たり前。でも、あなたは、もう一歩、踏み出している。大丈夫。あなたのペースで、いきましょう。
+それでは、そんなあなたに、今夜の一曲を。</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>647</v>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>Good evening, this is your host, Yuki. Thanks for your hard work today. Now, a message from a listener: 'Lately I can't keep up my Japanese study and I'm troubled.' I understand! But it's okay. Even 5 minutes a day is fine. Keep it up enjoyably with dramas or songs you like. Now, tonight's song.</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>お疲れさまでした／お便り／〜ましょう</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>相談＋励ましの語り口。</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>共感＝続けたくなる。</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>1話者・パーソナリティ調</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="94" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>L-R-006</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>抽象→具体的な一場面＋感情＋実用的助言。ラジオ「ユウキ」の枠。IDをL-O系にリセット。</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>※台本刷新＋ID刷新(旧L-R-00N)。独話=女（ユウキ）。音声は要作成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="409.05" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>L-O-002</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>お便り相談室</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>漢字が覚えられない</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>逆方向の電車</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>トーク</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>今日（きょう）の お便（たよ）りです。「漢字（かんじ）が なかなか 覚（おぼ）えられません」。わかります。漢字は 数（かず）が 多（おお）いですからね。おすすめは、毎日（まいにち）少（すこ）しずつ、生活（せいかつ）の 中（なか）で 見（み）た 漢字を 覚（おぼ）えることです。看板（かんばん）や メニューも いい 教材（きょうざい）ですよ。あせらず 続（つづ）けましょう。</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>103</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>続いてのお便りです。
+「ユウキさん。私の悩みは、漢字です。
+先週、友だちと、駅で待ち合わせをしました。でも、案内板の漢字が読めなくて、私は、逆方向の電車に、乗ってしまったんです。
+気づいた時には、知らない駅。約束の時間は、とっくに過ぎていました。
+友だちは『大丈夫だよ』と笑ってくれたけど、私は、申し訳なくて、顔を上げられませんでした。
+漢字は、ノートに、何百回も、書いています。でも、次の日には、忘れてしまう。
+私は、頭が悪いのかもしれません。もう、いやになりました。」
+……分かります。その、駅での気持ち。
+でもね。頭が悪いなんて、とんでもない。
+あなたは、生まれた時から使ってきた文字とは、まったく違う、何千もの記号を、大人になってから、覚えようとしているんです。それが、どれだけ、すごいことか。
+忘れるのは、当たり前。人の脳は、そういうふうに、できています。大切なのは「忘れたら、また出会う」こと。
+ノートの中の漢字は、冷たい。でも、駅の漢字、お店の漢字、友だちからのメッセージの漢字は——「生きて」います。
+今度、逆方向に乗った、あの駅の名前。もう、一生、忘れないでしょう?
+失敗した漢字ほど、心に残るんです。あせらないで。あなたは、ちゃんと、前に進んでいます。
+——さあ、次の一曲、いきましょう。</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>540</v>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>Today's listener message: 'I just can't memorize kanji.' I understand—there are so many. My tip: learn a little every day, from kanji you see in daily life. Signs and menus make good study material too. Don't rush—keep at it.</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>なかなか 〜られません／少しずつ／あせらず 続けましょう</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>相談＋アドバイスの語り。</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>共感＆励ましで続く。</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>1話者・パーソナリティ調</t>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>抽象→具体的な一場面＋感情＋実用的助言。ラジオ「ユウキ」の枠。IDをL-O系にリセット。</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>※台本刷新＋ID刷新(旧L-R-00N)。独話=女（ユウキ）。音声は要作成。</t>
         </is>
       </c>
     </row>
@@ -4584,8 +4543,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:N5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -4594,156 +4553,436 @@
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="64" customWidth="1" min="8" max="8"/>
+    <col width="252.21875" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="52" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="11" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>タブ</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>カテゴリー</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>サブテーマ</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>形式</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>対象レベル(非表示)</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>字数</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>英訳</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>キー表現</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>ポイント</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>楽しさ・継続フック</t>
         </is>
       </c>
-      <c r="N1" s="8" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>備考(音声)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="169" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>L-R-007</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
+    <row r="2" ht="409.05" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>L-G-001</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>ゲストインタビュー</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>ゲストのカイさん</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>ブラジルのマルコさん「おつかれさま」</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>対話</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>司会（しかい）：今日（きょう）の ゲストは、日本（にほん）で 勉強（べんきょう）している カイさんです。日本に 来て どのくらいですか。
-カイ：半年（はんとし）くらいです。
-司会：日本で 一番（いちばん）好（す）きな ものは？
-カイ：温泉（おんせん）です。とても 気持（きも）ちが いいです。
-司会：これから 何（なに）を したいですか。
-カイ：日本語（にほんご）を もっと 上手（じょうず）に なりたいです。
-司会：いいですね！ がんばってください。</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>121</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>女（司会）：こんばんは。世界の「日本好き」に、会いに行く。今夜のゲストは、ブラジルから来た、マルコさんです。ようこそ。
+男（ゲスト）：こんばんは。よろしく、お願いします。……少し、きんちょうします。
+女（司会）：ふふ、ゆっくりで大丈夫。マルコさんは、日本に来て、三年だとか。
+男（ゲスト）：はい。工場で、はたらいています。……でも、最初の一年は、本当に、つらかったです。
+女（司会）：つらかった。
+男（ゲスト）：日本語が、ぜんぜん話せなくて。まわりが何を言っているか、分からない。お昼も、ひとりで食べていました。夜、部屋で天じょうを見ながら、「国に帰ろうかな」って、毎晩、思っていました。
+女（司会）：……そうだったんですね。
+男（ゲスト）：それが変わったのが——ある言葉、だったんです。
+女（司会）：それが、今日の「好きな日本語」ですか?
+男（ゲスト）：はい。「おつかれさま」です。
+女（司会）：「おつかれさま」。
+男（ゲスト）：あの日も、仕事が大変で。手も足も、くたくたで。きっと、ひどい顔をしていたと思います。そうしたら、となりの年上のおじさんが——名前も、まだ知らなかった人が——私の肩を、ぽん、とたたいて。「マルコ。今日も、おつかれさま」って。
+女（司会）：……。
+男（ゲスト）：私の国の言葉に、この「おつかれさま」に、ぴったり合う言葉は、ないんです。「がんばったね」でも「ありがとう」でもない。もっと、あたたかい。「あなたの一日を、私は、ちゃんと見ていたよ」って。……そう言われた気がして。私、その場で、涙がこぼれました。工場の、まん中で。
+女（司会）：……マルコさん。
+男（ゲスト）：はずかしかった。でも、おじさんは、何も言わずに、ただ、うん、うん、ってうなずいてくれました。……あの日から、この国で生きていこう、って、決めたんです。
+女（司会）：……たった一言が、人を、そこまで。
+男（ゲスト）：だから今は、私が言います。新しく入った、外国人の子に。「おつかれさま」って。あの日の、おじさんみたいに。
+女（司会）：……すてきな、恩返しですね。では、もう一つ。日本に来て、いちばん驚いたことは?
+男（ゲスト）：ああ、それは……朝の、電車です。こんでいて、体も動かせないのに——だれも、話さない。しーん、として。私の国なら、みんな大声で、しゃべって、笑って、歌って（笑）。はじめて乗った時、こわかったです。「みんな、おこってるのかな」って。
+女（司会）：あはは。今は、なれましたか?
+男（ゲスト）：なれました。……でも、正直に言うと、今でも、たまに、さびしいです。あの、にぎやかな電車が、なつかしくて。
+女（司会）：……そうですよね。
+男（ゲスト）：日本の静かさが、いい、悪い、じゃないんです。ただ、ちがう。それだけ。私は、私の国の、うるさい電車も好きだし——この、静かな電車も、少しずつ、好きになってきました。両方、あっていいんだ、って。
+女（司会）：……うん。そのままの、マルコさんで、いいんですよね。
+男（ゲスト）：はい。無理に、日本人になろうとしなくて、いい。ちがうまま、ここにいていい。……それが分かってから、私、楽になりました。
+女（司会）：……マルコさん。今日は、あたたかいお話を、ありがとうございました。
+男（ゲスト）：こちらこそ。ユウキさん、今日も——おつかれさま、でした。
+女（司会）：……ふふ。おつかれさま、でした。</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>1209</v>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>Host: Today's guest is Kai, who is studying in Japan. How long have you been in Japan? / Kai: About half a year. / Host: What's your favorite thing in Japan? / Kai: Hot springs. They feel so good. / Host: What do you want to do from now on? / Kai: I want to get better at Japanese. / Host: Nice! Keep it up.</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>どのくらいですか／一番 好きな ものは？／がんばってください</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>インタビューの定番質問。</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>多様な人の声・人間味。</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>多声TTS:司会/ゲスト</t>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>看板=世界の日本好きに会う番組。2テーマ(好きな日本語＋驚いたこと)。美化しない(ただ違う/同化しなくていい)＝共感感動。司会=ユウキでお便りと世界観統一。</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>※新シリーズ(旧L-R-007ゲストのカイさんを置換)。ID刷新L-G系。対話=女(司会)・男(ゲスト)。音声要作成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="409" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>L-G-002</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>ゲストインタビュー</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>インドのプリヤさん「いただきます」</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>対話</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>女（司会）：こんばんは。世界の「日本好き」に会いに行く、この時間。今夜のゲストは、インドから来た、プリヤさんです。
+女（ゲスト）：こんばんは! プリヤです。よろしくお願いします!
+女（司会）：わあ、元気ですね（笑）。
+女（ゲスト）：はい! 私、声が大きいんです。インドでは、ふつう。でも日本に来て、電車で友だちに、しーっ! って、注意されました（笑）。
+女（司会）：あはは! さっそく。プリヤさんは、日本に来て、二年ですね。さっそくですが、好きな日本語は?
+女（ゲスト）：「いただきます」です。
+女（司会）：食事の前の。どうして、その言葉を?
+女（ゲスト）：最初はね、意味を、ぜんぜん知りませんでした。みんなが手を合わせるから、私も、まねして——お寺みたいに、拝んでいました（笑）。「日本人は、ごはんに、お祈りするのね!」って。
+女（司会）：あはは、ちがう（笑）。
+女（ゲスト）：ちがった（笑）。でも、ある人が、教えてくれたんです。「いただきます」は、作った人だけじゃなくて、野菜や、お肉——「命」に、ありがとうを言う言葉だ、って。……私、はっとしました。私の国にも、食べ物に感謝する心は、あります。でも、毎日、声に出して言う言葉は、なかった。
+女（司会）：ええ。
+女（ゲスト）：……日本に来て、半年くらいの時。すごく、ホームシックだった夜が、あって。何を食べても、おいしくない。ふるさとの、母の、あのスパイスのにおいが、恋しくて。私、スーパーで、あるだけのスパイスを買って、母の料理を思い出しながら、作ったんです。一人の、せまい部屋で。
+女（司会）：……。
+女（ゲスト）：できあがって、テーブルに置いて。いつものように、「いただきます」って、言いました。……そうしたら、急に、涙が、ぽろぽろ、出て。
+女（司会）：……。
+女（ゲスト）：その「いただきます」の中に、母がいて、故郷があって、命があって。……ああ、私は、一人じゃないんだ、って。たった五文字が、遠くから、私を、ぎゅっと、抱きしめてくれた気がしました。
+女（司会）：……プリヤさん。
+女（ゲスト）：だから今も、一人でも、必ず言います。「いただきます」。……あ、でも、その日の料理、辛すぎて、汗だくで食べました（笑）。
+女（司会）：あはは! せっかくの感動が（笑）。
+女（ゲスト）：台無し（笑）。
+女（司会）：では、もう一つ。日本に来て、驚いたことは?
+女（ゲスト）：ああ……「すみません」の、多さ、です!
+女（司会）：あはは、来た。
+女（ゲスト）：みんな、何回も言うでしょう。すみません、すみませんって。最初は、「この国の人は、なんで、こんなに、あやまってばかり? 悲しくないのかな」って、本気で、心配しました。
+女（司会）：（笑）。
+女（ゲスト）：この前もね、駅で、人とぶつかったんです。そうしたら、その人が「あ、すみません! すみません!」って、何回も、おじぎ。私、びっくりしました。だって、私は、ぜんぜん、おこってないのに（笑）。
+女（司会）：あはは。
+女（ゲスト）：私の国なら、「大丈夫?」「うん!」で、おしまい。だから私、その人の手を取って、言ったんです。「大丈夫、大丈夫! どこも、いたくない?」って。
+女（司会）：おお。
+女（ゲスト）：そうしたら、その人、きょとん、として。それから、ふふって、笑ってくれました。……私は、「すみません」じゃなくて、「大丈夫?」って、言いたいんです。それが、私だから。
+女（司会）：……。
+女（ゲスト）：正直、日本の「すみません」は、今でも、多すぎると思います。でも、いい、悪い、じゃない。ただ、私は、私のやり方で、いたい。ぜんぶ、まねしなくていい、って。ありがとうは、ありがとう。うれしい時は、大きな声で、笑いたい。
+女（司会）：……うん。そのままの、プリヤさんが、すてきです。
+女（ゲスト）：ふふ、ありがとうございます! ……ほら、ありがとうは、ちゃんと、大きな声で（笑）。</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>1379</v>
+      </c>
+      <c r="J3" s="6" t="n"/>
+      <c r="K3" s="6" t="n"/>
+      <c r="L3" s="6" t="n"/>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>看板=世界の日本好きに会う番組。2テーマ(好きな日本語＋驚いたこと)。美化しない(ただ違う/同化しなくていい)＝共感感動。司会=ユウキでお便りと世界観統一。</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>※新シリーズL-G-002。対話=女(司会)・女(ゲスト)。音声要作成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="409" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>L-G-003</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>ゲストインタビュー</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>エジプトのハーレドさん「もったいない」</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>対話</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>女（司会）：こんばんは。今夜のゲストは、エジプトから来た、ハーレドさんです。ようこそ。
+男（ゲスト）：こんばんは。よろしくお願いします。……あ、司会さん。そのペン、まだ、使えますよ?
+女（司会）：え?（笑） このペン、インク、切れてますけど。
+男（ゲスト）：もったいない! ふって、あたためると、もう少し、書けます!
+女（司会）：あはは! いきなり、今日のテーマ（笑）。
+男（ゲスト）：あ……そうでした（笑）。私の好きな日本語、「もったいない」です。
+女（司会）：もう、体で、表現してくれました（笑）。どうして、その言葉を?
+男（ゲスト）：この言葉、私の国の言葉に、訳せないんです。「捨てるな」でも、「安くしろ」でもない。物にも、時間にも、命がある。それを大切にしなさい、っていう、心。
+男（ゲスト）：私、子どもの時、貧しくて。祖母が、いつも言っていました。「パンのかけらも、捨てるな。神さまからの、おくりものだから」って。日本で「もったいない」を聞いた時、私、祖母の顔を、思い出しました。ああ、こんな遠い国なのに、同じ心が、ここにもある、って。
+女（司会）：……。
+男（ゲスト）：祖母は、料理も、じょうずでした。かたくなった、古いパンも、牛乳につけて、あまくして、私に、食べさせてくれた。「ほら、まだ、おいしいでしょう?」って。……あれが、私の、いちばんの、ごちそうでした。
+女（司会）：……。
+男（ゲスト）：祖母は、もう、いません。でも、「もったいない」と言うたびに、祖母が、となりで、笑っている気が、するんです。
+女（司会）：……あたたかいですね。
+男（ゲスト）：……でも、こまったことも、あって。
+女（司会）：こまったこと?
+男（ゲスト）：私、もう、何にも、捨てられないんです。コンビニの、わりばし。ビニールぶくろ。きれいな、おかしの箱。ぜんぶ「もったいない」。……気づいたら、私の部屋、ものだらけ（笑）。
+女（司会）：あはは! それは、もったいなさすぎ（笑）。
+男（ゲスト）：妻に、おこられます。「もったいないの、意味が、ちがう!」って（笑）。
+女（司会）：あはは! では、もう一つ。日本に来て、驚いたことは?
+男（ゲスト）：ああ……働き方、です。
+女（司会）：働き方。
+男（ゲスト）：みんな、本当に、よく働く。おそくまで。最初、びっくりしたのは——電車で、みんな、ねているのに、ちゃんと、自分の駅で、起きる! あれは、すごい。特技です（笑）。
+女（司会）：あはは、たしかに（笑）。
+男（ゲスト）：あ、でも、私も、よく働きますよ。お金、必要ですから（笑）。だから、分かるんです。「休みたい」って、なかなか、言えない。まわりに、悪いなあ、って、思ってしまう。
+女（司会）：……。
+男（ゲスト）：でも、だからこそ、正直に言うと、心配に、なることも、あります。つかれた顔で、電車で、ねむっている人を見ると。「この人、ちゃんと、休めていますか?」って。
+女（司会）：……。
+男（ゲスト）：日本は、すばらしい国です。でも、完璧じゃない。どこの国も、そう。いいところも、しんどいところも、ある。……私は、日本の「もったいない」の心が、大好きです。でも、一つだけ。
+女（司会）：はい。
+男（ゲスト）：「自分の体や、心を——もったいなく、しないで」。休むことも、大切ですから。それも、神さまからの、おくりものだから。
+女（司会）：……ハーレドさん。それ、日本人が、いちばん、聞かなきゃいけない言葉かもしれません。
+男（ゲスト）：ふふ。おせっかい、でした?
+女（司会）：いいえ。……ありがとうございます。あ、このペン、大事に、使いますね。
+男（ゲスト）：はい! ふって、あたためて（笑）。</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1271</v>
+      </c>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>看板=世界の日本好きに会う番組。2テーマ(好きな日本語＋驚いたこと)。美化しない(ただ違う/同化しなくていい)＝共感感動。司会=ユウキでお便りと世界観統一。</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>※新シリーズL-G-003。対話=女(司会)・男(ゲスト)。音声要作成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="409" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>L-G-004</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>長文</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>ゲストインタビュー</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>モンゴルのバトさん「おかげさま」</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>対話</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>N4</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>女（司会）：こんばんは。世界の「日本好き」に会いに行く、この時間。今夜のゲストは、モンゴルから来た、バトさんです。ようこそ。
+男（ゲスト）：こんばんは。よろしく、お願いします。……あの、このスタジオ、天じょうが、近いですね。
+女（司会）：え?（笑） せまいですか?
+男（ゲスト）：いえ、日本は、どこも、天じょうが、近い（笑）。私の国の家は、まん中に、大きな穴が、あって、そこから、空が、見えるんです。
+女（司会）：ゲルですね。すてき。バトさんは、日本に来て、二年。好きな日本語は?
+男（ゲスト）：「おかげさま」です。
+女（司会）：おかげさま。「元気?」「おかげさまで」の。
+男（ゲスト）：はい。いいでしょう、この言葉。「私が元気なのは、あなたや、まわりの、みんなのおかげ」。……一人で、生きてる、じゃない、って。
+男（ゲスト）：私の国は、冬が、とても、きびしいんです。マイナス、四十度。一人では、生きられない。だから、みんなで、助け合う。旅の人が来たら、知らない人でも、家に入れて、あたたかいスープを、出すんです。
+女（司会）：……。
+男（ゲスト）：子どもの時、雪の中で、羊が、いなくなって。近所の人たちが、みんな、馬で、さがしに来てくれました。夜通し。……次の朝、羊を見つけた時、祖父が、言ったんです。「バト、これは、みんなの、おかげだ。わすれるな」って。
+女（司会）：……。
+男（ゲスト）：日本で、はじめて「おかげさまで」を聞いた時、私、その、雪の朝を、思い出しました。ああ、この国の人も、同じことを、知っているんだ、って。「一人じゃない」って。
+女（司会）：……。
+男（ゲスト）：日本に来て、すぐ、私、道に、まよいました。日本語も、下手で。そうしたら、通りがかりの、おばあさんが、わざわざ、目的地まで、いっしょに、歩いて、連れて行って、くれたんです。何も、言わずに。……私、その時、また、思いました。「ああ、これも、おかげさま、だ」って。国が、ちがっても、こういう、やさしさは、あるんだ、って。
+女（司会）：……バトさん。
+男（ゲスト）：……あ、でも、最初は、意味が、分からなくて。「おかげさまで」って言われて、私、「おかげ様? それ、どこの、神様ですか?」って、聞きました（笑）。
+女（司会）：あはは! 神様（笑）。では、もう一つ。日本に来て、驚いたことは?
+男（ゲスト）：……空が、ないこと、です。
+女（司会）：空?
+男（ゲスト）：東京に来た日。私、駅を出て、空を、さがしました。でも——ビル、ビル、ビル! 空が、こんなに、小さい! 私の国では、空は、地面まで、ぜんぶ、空。三百六十度。……はじめて、こわくなりました。「私の、空は、どこ?」って。
+女（司会）：……。
+男（ゲスト）：正直に言うと、今でも、たまに、くるしくなります。人が、多くて。部屋が、せまくて。……私の家に、馬は、入りません（笑）。
+女（司会）：あはは! 馬（笑）。
+男（ゲスト）：本当ですよ。私の国では、馬は、家族です。子どもの時から、ずっと、いっしょ。日本の電車も、はやくて、すごいけど……私は、やっぱり、馬の背中が、いちばん、好きです（笑）。
+女（司会）：ふふ、いいですね。
+男（ゲスト）：でも、見つけたんです。近くの、川の、土手。そこに、ねころぶと——東京にも、ちゃんと、空が、ある。せまいけど、同じ、青い空。
+女（司会）：……。
+男（ゲスト）：日本の空も、モンゴルの空も、つながっている。だから、さびしくない。……いや、少しは、さびしい（笑）。でも、大丈夫。空を、心の中に、持っているから。
+女（司会）：……バトさん。今日は、本当に、ありがとうございました。
+男（ゲスト）：おかげさまで、楽しかったです。
+女（司会）：……ふふ。こちらこそ、おかげさまで。</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>1326</v>
+      </c>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>好きな日本語=おかげさま(助け合い)／驚いた=空がない東京の圧迫を正直に。感動(雪の朝・羊・祖父)＋笑い(天じょう近い/神様/馬)＋美化なし(東京くるしい)。</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>※新シリーズL-G-004。対話=女(司会)・男(ゲスト)。音声要作成。</t>
         </is>
       </c>
     </row>
@@ -4759,7 +4998,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -4771,150 +5010,148 @@
     <col width="64" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="52" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="11" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>タブ</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>カテゴリー</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>サブテーマ</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>形式</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>対象レベル(非表示)</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>字数</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>英訳</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>キー表現</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>ポイント</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>楽しさ・継続フック</t>
         </is>
       </c>
-      <c r="N1" s="8" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>備考(音声)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="139" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="139.05" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>L-R-008</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>長文</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>2人のフリートーク</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>週末どうだった？</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>対話</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>ケンタ：週末（しゅうまつ）、どうだった？
-カイ：友（とも）だちの ミナと 海（うみ）に 行（い）ったよ。すごく きれいだった！
-ケンタ：いいなあ。おれは 一日中（いちにちじゅう）、家（いえ）で ドラマを 見（み）てた。
-カイ：それも いいね。何（なに）の ドラマ？
-ケンタ：日本（にほん）の 恋愛（れんあい）ドラマ。じつは 日本語の 勉強（べんきょう）にも なるんだぜ。
-カイ：へえ、いいね！</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="n">
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>男（ケンタ）：週末（しゅうまつ）、どうだった？
+男（カイ）：友（とも）だちの ミナと 海（うみ）に 行（い）ったよ。すごく きれいだった！
+男（ケンタ）：いいなあ。おれは 一日中（いちにちじゅう）、家（いえ）で ドラマを 見（み）てた。
+男（カイ）：それも いいね。何（なに）の ドラマ？
+男（ケンタ）：日本（にほん）の 恋愛（れんあい）ドラマ。じつは 日本語の 勉強（べんきょう）にも なるんだぜ。
+男（カイ）：へえ、いいね！</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="n">
         <v>101</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>Kenta: How was your weekend? / Kai: I went to the beach with my friend Mina. It was so beautiful! / Kenta: Nice. I watched dramas at home all day. / Kai: That's good too. What drama? / Kenta: A Japanese romance drama. Actually it's good Japanese study too. / Kai: Oh, nice!</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>どうだった?／〜に 行ったよ／勉強にも なる</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>相棒ケンタとカイのゆるい雑談(再登場)。</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>くだけた会話＝多聴に最適。</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>多声TTS:ケンタ/カイ</t>
         </is>
